--- a/output/2024-04-01.xlsx
+++ b/output/2024-04-01.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>246.19</v>
+        <v>-48.11</v>
       </c>
       <c r="K14" t="n">
-        <v>-191.18</v>
+        <v>-115.25</v>
       </c>
       <c r="L14" t="n">
-        <v>311.7</v>
+        <v>124.89</v>
       </c>
     </row>
     <row r="15">
@@ -667,28 +667,28 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.28</v>
+        <v>5.21</v>
       </c>
       <c r="F15" t="n">
-        <v>12.44</v>
+        <v>12.14</v>
       </c>
       <c r="G15" t="n">
-        <v>184.4</v>
+        <v>190.8</v>
       </c>
       <c r="H15" t="n">
-        <v>90.59999999999999</v>
+        <v>87</v>
       </c>
       <c r="I15" t="n">
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-277.15</v>
+        <v>-50.59</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.49</v>
+        <v>88.87</v>
       </c>
       <c r="L15" t="n">
-        <v>277.17</v>
+        <v>102.26</v>
       </c>
     </row>
     <row r="16">
@@ -709,28 +709,28 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.31</v>
+        <v>5.2</v>
       </c>
       <c r="F16" t="n">
-        <v>12.67</v>
+        <v>12.28</v>
       </c>
       <c r="G16" t="n">
-        <v>183</v>
+        <v>169.3</v>
       </c>
       <c r="H16" t="n">
-        <v>87.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-39.78</v>
+        <v>-266.75</v>
       </c>
       <c r="K16" t="n">
-        <v>119.06</v>
+        <v>-201.63</v>
       </c>
       <c r="L16" t="n">
-        <v>125.53</v>
+        <v>334.38</v>
       </c>
     </row>
     <row r="17">
@@ -751,28 +751,28 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.89</v>
+        <v>4.54</v>
       </c>
       <c r="F17" t="n">
-        <v>12.4</v>
+        <v>12.17</v>
       </c>
       <c r="G17" t="n">
-        <v>183.9</v>
+        <v>181.8</v>
       </c>
       <c r="H17" t="n">
-        <v>87.8</v>
+        <v>90.7</v>
       </c>
       <c r="I17" t="n">
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>35.69</v>
+        <v>122.89</v>
       </c>
       <c r="K17" t="n">
-        <v>517.34</v>
+        <v>293.62</v>
       </c>
       <c r="L17" t="n">
-        <v>518.5700000000001</v>
+        <v>318.3</v>
       </c>
     </row>
     <row r="18">
@@ -793,28 +793,28 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>5.42</v>
+        <v>4.63</v>
       </c>
       <c r="F18" t="n">
-        <v>12.06</v>
+        <v>12.37</v>
       </c>
       <c r="G18" t="n">
-        <v>174</v>
+        <v>187.6</v>
       </c>
       <c r="H18" t="n">
-        <v>89.5</v>
+        <v>89.7</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>-154.76</v>
+        <v>31.33</v>
       </c>
       <c r="K18" t="n">
-        <v>-569.8200000000001</v>
+        <v>64.87</v>
       </c>
       <c r="L18" t="n">
-        <v>590.47</v>
+        <v>72.04000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -835,28 +835,28 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.64</v>
+        <v>5.69</v>
       </c>
       <c r="F19" t="n">
-        <v>11.95</v>
+        <v>12.06</v>
       </c>
       <c r="G19" t="n">
-        <v>181.5</v>
+        <v>174</v>
       </c>
       <c r="H19" t="n">
-        <v>99.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>365.51</v>
+        <v>338.95</v>
       </c>
       <c r="K19" t="n">
-        <v>-244.12</v>
+        <v>-223.16</v>
       </c>
       <c r="L19" t="n">
-        <v>439.54</v>
+        <v>405.82</v>
       </c>
     </row>
     <row r="20">
@@ -877,28 +877,28 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.3</v>
+        <v>4.47</v>
       </c>
       <c r="F20" t="n">
-        <v>12.15</v>
+        <v>12.09</v>
       </c>
       <c r="G20" t="n">
-        <v>176.3</v>
+        <v>177.2</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I20" t="n">
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-37.67</v>
+        <v>337.18</v>
       </c>
       <c r="K20" t="n">
-        <v>172.06</v>
+        <v>-60.96</v>
       </c>
       <c r="L20" t="n">
-        <v>176.14</v>
+        <v>342.64</v>
       </c>
     </row>
     <row r="21">
@@ -919,28 +919,28 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.91</v>
+        <v>4.05</v>
       </c>
       <c r="F21" t="n">
-        <v>12.19</v>
+        <v>13.03</v>
       </c>
       <c r="G21" t="n">
-        <v>183.8</v>
+        <v>176.9</v>
       </c>
       <c r="H21" t="n">
-        <v>85.09999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>260.43</v>
+        <v>-342.44</v>
       </c>
       <c r="K21" t="n">
-        <v>46.36</v>
+        <v>-137.37</v>
       </c>
       <c r="L21" t="n">
-        <v>264.52</v>
+        <v>368.96</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>4.89</v>
       </c>
       <c r="F22" t="n">
-        <v>12.43</v>
+        <v>12.61</v>
       </c>
       <c r="G22" t="n">
-        <v>179.9</v>
+        <v>183.7</v>
       </c>
       <c r="H22" t="n">
-        <v>90.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="I22" t="n">
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>460.94</v>
+        <v>-155.79</v>
       </c>
       <c r="K22" t="n">
-        <v>130.93</v>
+        <v>-103.05</v>
       </c>
       <c r="L22" t="n">
-        <v>479.18</v>
+        <v>186.79</v>
       </c>
     </row>
     <row r="23">
@@ -1003,28 +1003,28 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.48</v>
+        <v>4.58</v>
       </c>
       <c r="F23" t="n">
-        <v>12.41</v>
+        <v>12.71</v>
       </c>
       <c r="G23" t="n">
-        <v>195.2</v>
+        <v>189.5</v>
       </c>
       <c r="H23" t="n">
-        <v>86.2</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>121.98</v>
+        <v>186.98</v>
       </c>
       <c r="K23" t="n">
-        <v>-355.8</v>
+        <v>-65.61</v>
       </c>
       <c r="L23" t="n">
-        <v>376.13</v>
+        <v>198.15</v>
       </c>
     </row>
     <row r="24">
@@ -1045,28 +1045,28 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.61</v>
+        <v>4.8</v>
       </c>
       <c r="F24" t="n">
-        <v>12.26</v>
+        <v>13.14</v>
       </c>
       <c r="G24" t="n">
-        <v>183.4</v>
+        <v>184.9</v>
       </c>
       <c r="H24" t="n">
-        <v>90.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I24" t="n">
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-886.61</v>
+        <v>174.11</v>
       </c>
       <c r="K24" t="n">
-        <v>-57.94</v>
+        <v>-441.33</v>
       </c>
       <c r="L24" t="n">
-        <v>888.5</v>
+        <v>474.43</v>
       </c>
     </row>
     <row r="25">
@@ -1087,28 +1087,28 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.87</v>
+        <v>4.37</v>
       </c>
       <c r="F25" t="n">
-        <v>12.99</v>
+        <v>12.67</v>
       </c>
       <c r="G25" t="n">
-        <v>188.3</v>
+        <v>171.7</v>
       </c>
       <c r="H25" t="n">
-        <v>83.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="I25" t="n">
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.56</v>
+        <v>-456.97</v>
       </c>
       <c r="K25" t="n">
-        <v>-375.88</v>
+        <v>-265.31</v>
       </c>
       <c r="L25" t="n">
-        <v>375.94</v>
+        <v>528.41</v>
       </c>
     </row>
     <row r="26">
@@ -1129,28 +1129,28 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.69</v>
+        <v>4.93</v>
       </c>
       <c r="F26" t="n">
-        <v>12.77</v>
+        <v>12.2</v>
       </c>
       <c r="G26" t="n">
-        <v>199.6</v>
+        <v>184.9</v>
       </c>
       <c r="H26" t="n">
-        <v>92.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I26" t="n">
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>369.81</v>
+        <v>797.98</v>
       </c>
       <c r="K26" t="n">
-        <v>-112.93</v>
+        <v>-1544.79</v>
       </c>
       <c r="L26" t="n">
-        <v>386.67</v>
+        <v>1738.72</v>
       </c>
     </row>
     <row r="27">
@@ -1171,28 +1171,28 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.86</v>
+        <v>4.74</v>
       </c>
       <c r="F27" t="n">
-        <v>12.22</v>
+        <v>12.43</v>
       </c>
       <c r="G27" t="n">
-        <v>192</v>
+        <v>171.6</v>
       </c>
       <c r="H27" t="n">
-        <v>85.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I27" t="n">
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>311.21</v>
+        <v>-841.6900000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>-602.5700000000001</v>
+        <v>355.24</v>
       </c>
       <c r="L27" t="n">
-        <v>678.1900000000001</v>
+        <v>913.59</v>
       </c>
     </row>
     <row r="28">
@@ -1213,28 +1213,28 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.82</v>
+        <v>4.71</v>
       </c>
       <c r="F28" t="n">
-        <v>12.56</v>
+        <v>12.82</v>
       </c>
       <c r="G28" t="n">
-        <v>197.8</v>
+        <v>183</v>
       </c>
       <c r="H28" t="n">
-        <v>88.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-511.3</v>
+        <v>945.61</v>
       </c>
       <c r="K28" t="n">
-        <v>-271.65</v>
+        <v>519.95</v>
       </c>
       <c r="L28" t="n">
-        <v>578.99</v>
+        <v>1079.14</v>
       </c>
     </row>
     <row r="29">
@@ -1255,28 +1255,28 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>5.01</v>
+        <v>5.06</v>
       </c>
       <c r="F29" t="n">
         <v>12.33</v>
       </c>
       <c r="G29" t="n">
-        <v>188.1</v>
+        <v>183.3</v>
       </c>
       <c r="H29" t="n">
-        <v>81.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I29" t="n">
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-78.93000000000001</v>
+        <v>205.77</v>
       </c>
       <c r="K29" t="n">
-        <v>75.09999999999999</v>
+        <v>-253.32</v>
       </c>
       <c r="L29" t="n">
-        <v>108.95</v>
+        <v>326.37</v>
       </c>
     </row>
     <row r="30">
@@ -1297,28 +1297,28 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.27</v>
+        <v>5.21</v>
       </c>
       <c r="F30" t="n">
-        <v>12.07</v>
+        <v>12.6</v>
       </c>
       <c r="G30" t="n">
-        <v>192.5</v>
+        <v>195.1</v>
       </c>
       <c r="H30" t="n">
-        <v>92.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I30" t="n">
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>36.55</v>
+        <v>149.4</v>
       </c>
       <c r="K30" t="n">
-        <v>35.62</v>
+        <v>-333.56</v>
       </c>
       <c r="L30" t="n">
-        <v>51.04</v>
+        <v>365.49</v>
       </c>
     </row>
     <row r="31">
@@ -1339,28 +1339,28 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.57</v>
+        <v>4.88</v>
       </c>
       <c r="F31" t="n">
-        <v>11.88</v>
+        <v>12.02</v>
       </c>
       <c r="G31" t="n">
-        <v>193.7</v>
+        <v>190.8</v>
       </c>
       <c r="H31" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I31" t="n">
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-102.81</v>
+        <v>5.38</v>
       </c>
       <c r="K31" t="n">
-        <v>22.41</v>
+        <v>-258.68</v>
       </c>
       <c r="L31" t="n">
-        <v>105.23</v>
+        <v>258.74</v>
       </c>
     </row>
     <row r="32">
@@ -1381,28 +1381,28 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>5.27</v>
+        <v>4.67</v>
       </c>
       <c r="F32" t="n">
-        <v>12.64</v>
+        <v>12.54</v>
       </c>
       <c r="G32" t="n">
-        <v>192.6</v>
+        <v>194.9</v>
       </c>
       <c r="H32" t="n">
-        <v>95.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-409.74</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>345.48</v>
+        <v>5.12</v>
       </c>
       <c r="L32" t="n">
-        <v>535.95</v>
+        <v>90.13</v>
       </c>
     </row>
     <row r="33">
@@ -1423,28 +1423,28 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>5.36</v>
+        <v>5.11</v>
       </c>
       <c r="F33" t="n">
-        <v>11.98</v>
+        <v>11.67</v>
       </c>
       <c r="G33" t="n">
-        <v>172.9</v>
+        <v>190.4</v>
       </c>
       <c r="H33" t="n">
-        <v>85.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="I33" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-291</v>
+        <v>95.11</v>
       </c>
       <c r="K33" t="n">
-        <v>-482.56</v>
+        <v>209.07</v>
       </c>
       <c r="L33" t="n">
-        <v>563.51</v>
+        <v>229.68</v>
       </c>
     </row>
     <row r="34">
@@ -1465,28 +1465,28 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.97</v>
+        <v>4.73</v>
       </c>
       <c r="F34" t="n">
-        <v>12.36</v>
+        <v>12.39</v>
       </c>
       <c r="G34" t="n">
-        <v>191.3</v>
+        <v>187.6</v>
       </c>
       <c r="H34" t="n">
-        <v>92.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-134.49</v>
+        <v>-209.79</v>
       </c>
       <c r="K34" t="n">
-        <v>-30.17</v>
+        <v>-49.43</v>
       </c>
       <c r="L34" t="n">
-        <v>137.83</v>
+        <v>215.54</v>
       </c>
     </row>
     <row r="35">
@@ -1507,28 +1507,28 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.05</v>
+        <v>4.91</v>
       </c>
       <c r="F35" t="n">
-        <v>12.25</v>
+        <v>12.89</v>
       </c>
       <c r="G35" t="n">
-        <v>183.6</v>
+        <v>184.7</v>
       </c>
       <c r="H35" t="n">
-        <v>92.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I35" t="n">
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-429.59</v>
+        <v>-289.61</v>
       </c>
       <c r="K35" t="n">
-        <v>-652.28</v>
+        <v>28.49</v>
       </c>
       <c r="L35" t="n">
-        <v>781.04</v>
+        <v>291.01</v>
       </c>
     </row>
     <row r="36">
@@ -1549,28 +1549,28 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.72</v>
+        <v>5.32</v>
       </c>
       <c r="F36" t="n">
-        <v>12.74</v>
+        <v>12.64</v>
       </c>
       <c r="G36" t="n">
-        <v>187.3</v>
+        <v>192.6</v>
       </c>
       <c r="H36" t="n">
-        <v>89.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I36" t="n">
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>21.14</v>
+        <v>710.08</v>
       </c>
       <c r="K36" t="n">
-        <v>-185.52</v>
+        <v>-102.84</v>
       </c>
       <c r="L36" t="n">
-        <v>186.72</v>
+        <v>717.48</v>
       </c>
     </row>
     <row r="37">
@@ -1591,28 +1591,28 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.76</v>
+        <v>4.21</v>
       </c>
       <c r="F37" t="n">
-        <v>12.99</v>
+        <v>11.66</v>
       </c>
       <c r="G37" t="n">
-        <v>192.1</v>
+        <v>196.2</v>
       </c>
       <c r="H37" t="n">
-        <v>89.2</v>
+        <v>91</v>
       </c>
       <c r="I37" t="n">
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>127.75</v>
+        <v>-460.31</v>
       </c>
       <c r="K37" t="n">
-        <v>-48.33</v>
+        <v>-252.34</v>
       </c>
       <c r="L37" t="n">
-        <v>136.58</v>
+        <v>524.9400000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1633,28 +1633,28 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.3</v>
+        <v>5.19</v>
       </c>
       <c r="F38" t="n">
-        <v>11.87</v>
+        <v>11.38</v>
       </c>
       <c r="G38" t="n">
-        <v>181.4</v>
+        <v>174.4</v>
       </c>
       <c r="H38" t="n">
-        <v>88.2</v>
+        <v>91.7</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>119.1</v>
+        <v>-246.28</v>
       </c>
       <c r="K38" t="n">
-        <v>118.66</v>
+        <v>146.04</v>
       </c>
       <c r="L38" t="n">
-        <v>168.13</v>
+        <v>286.32</v>
       </c>
     </row>
     <row r="39">
@@ -1675,28 +1675,28 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>5.55</v>
+        <v>5.3</v>
       </c>
       <c r="F39" t="n">
-        <v>12.75</v>
+        <v>12.39</v>
       </c>
       <c r="G39" t="n">
-        <v>183</v>
+        <v>191.8</v>
       </c>
       <c r="H39" t="n">
-        <v>94.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="I39" t="n">
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>696.51</v>
+        <v>-382.98</v>
       </c>
       <c r="K39" t="n">
-        <v>748.65</v>
+        <v>-190.88</v>
       </c>
       <c r="L39" t="n">
-        <v>1022.55</v>
+        <v>427.91</v>
       </c>
     </row>
     <row r="40">
@@ -1717,28 +1717,28 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.06</v>
+        <v>5.11</v>
       </c>
       <c r="F40" t="n">
-        <v>12.43</v>
+        <v>12.19</v>
       </c>
       <c r="G40" t="n">
-        <v>178.9</v>
+        <v>189.9</v>
       </c>
       <c r="H40" t="n">
-        <v>94.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="I40" t="n">
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>-548.48</v>
+        <v>433.25</v>
       </c>
       <c r="K40" t="n">
-        <v>-738.5</v>
+        <v>-1184.34</v>
       </c>
       <c r="L40" t="n">
-        <v>919.9</v>
+        <v>1261.1</v>
       </c>
     </row>
     <row r="41">
@@ -1759,28 +1759,28 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.2</v>
+        <v>4.56</v>
       </c>
       <c r="F41" t="n">
-        <v>12.44</v>
+        <v>12.19</v>
       </c>
       <c r="G41" t="n">
-        <v>178</v>
+        <v>191.7</v>
       </c>
       <c r="H41" t="n">
-        <v>95</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I41" t="n">
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>245.87</v>
+        <v>559.1799999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>-136.16</v>
+        <v>593.55</v>
       </c>
       <c r="L41" t="n">
-        <v>281.05</v>
+        <v>815.47</v>
       </c>
     </row>
     <row r="42">
@@ -1801,28 +1801,28 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5.49</v>
+        <v>5.05</v>
       </c>
       <c r="F42" t="n">
-        <v>12.39</v>
+        <v>12.34</v>
       </c>
       <c r="G42" t="n">
-        <v>206.5</v>
+        <v>196.5</v>
       </c>
       <c r="H42" t="n">
-        <v>90.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-22.24</v>
+        <v>-359.79</v>
       </c>
       <c r="K42" t="n">
-        <v>-59.54</v>
+        <v>-929.98</v>
       </c>
       <c r="L42" t="n">
-        <v>63.56</v>
+        <v>997.15</v>
       </c>
     </row>
     <row r="43">
@@ -1843,28 +1843,28 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.77</v>
+        <v>4.73</v>
       </c>
       <c r="F43" t="n">
-        <v>12.45</v>
+        <v>12.46</v>
       </c>
       <c r="G43" t="n">
-        <v>194.4</v>
+        <v>174.6</v>
       </c>
       <c r="H43" t="n">
-        <v>93.3</v>
+        <v>97.5</v>
       </c>
       <c r="I43" t="n">
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>386.95</v>
+        <v>313.34</v>
       </c>
       <c r="K43" t="n">
-        <v>-748.53</v>
+        <v>-228.98</v>
       </c>
       <c r="L43" t="n">
-        <v>842.63</v>
+        <v>388.09</v>
       </c>
     </row>
     <row r="44">
@@ -1885,28 +1885,28 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.01</v>
+        <v>4.42</v>
       </c>
       <c r="F44" t="n">
-        <v>12.66</v>
+        <v>11.87</v>
       </c>
       <c r="G44" t="n">
-        <v>196.6</v>
+        <v>181.4</v>
       </c>
       <c r="H44" t="n">
-        <v>84.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-88.19</v>
+        <v>92.73</v>
       </c>
       <c r="K44" t="n">
-        <v>323.32</v>
+        <v>-48.17</v>
       </c>
       <c r="L44" t="n">
-        <v>335.14</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="45">
@@ -1927,28 +1927,28 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
       <c r="F45" t="n">
-        <v>12.34</v>
+        <v>12.73</v>
       </c>
       <c r="G45" t="n">
-        <v>183.3</v>
+        <v>173.9</v>
       </c>
       <c r="H45" t="n">
-        <v>84.40000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>140.28</v>
+        <v>246.54</v>
       </c>
       <c r="K45" t="n">
-        <v>-133.34</v>
+        <v>75.94</v>
       </c>
       <c r="L45" t="n">
-        <v>193.54</v>
+        <v>257.97</v>
       </c>
     </row>
     <row r="46">
@@ -1969,28 +1969,28 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>5.51</v>
+        <v>5.1</v>
       </c>
       <c r="F46" t="n">
-        <v>12.83</v>
+        <v>12.33</v>
       </c>
       <c r="G46" t="n">
-        <v>178.6</v>
+        <v>202.3</v>
       </c>
       <c r="H46" t="n">
-        <v>86.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>260.8</v>
+        <v>208.41</v>
       </c>
       <c r="K46" t="n">
-        <v>18.37</v>
+        <v>-172.8</v>
       </c>
       <c r="L46" t="n">
-        <v>261.45</v>
+        <v>270.73</v>
       </c>
     </row>
     <row r="47">
@@ -2011,28 +2011,28 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5.28</v>
+        <v>5.31</v>
       </c>
       <c r="F47" t="n">
-        <v>12.48</v>
+        <v>11.47</v>
       </c>
       <c r="G47" t="n">
-        <v>182.1</v>
+        <v>173</v>
       </c>
       <c r="H47" t="n">
-        <v>86.8</v>
+        <v>87.3</v>
       </c>
       <c r="I47" t="n">
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>234.24</v>
+        <v>-123.86</v>
       </c>
       <c r="K47" t="n">
-        <v>-481.33</v>
+        <v>-98.40000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>535.3</v>
+        <v>158.19</v>
       </c>
     </row>
     <row r="48">
@@ -2053,28 +2053,28 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.88</v>
+        <v>5.95</v>
       </c>
       <c r="F48" t="n">
-        <v>12.23</v>
+        <v>12.14</v>
       </c>
       <c r="G48" t="n">
-        <v>187.7</v>
+        <v>188.5</v>
       </c>
       <c r="H48" t="n">
-        <v>87.3</v>
+        <v>86.8</v>
       </c>
       <c r="I48" t="n">
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-201.63</v>
+        <v>56.34</v>
       </c>
       <c r="K48" t="n">
-        <v>141.7</v>
+        <v>176.51</v>
       </c>
       <c r="L48" t="n">
-        <v>246.44</v>
+        <v>185.28</v>
       </c>
     </row>
     <row r="49">
@@ -2095,28 +2095,28 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>5.46</v>
+        <v>5.06</v>
       </c>
       <c r="F49" t="n">
-        <v>12.27</v>
+        <v>12.39</v>
       </c>
       <c r="G49" t="n">
-        <v>202</v>
+        <v>206.5</v>
       </c>
       <c r="H49" t="n">
-        <v>91.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I49" t="n">
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-284.49</v>
+        <v>18.28</v>
       </c>
       <c r="K49" t="n">
-        <v>-209.02</v>
+        <v>150.61</v>
       </c>
       <c r="L49" t="n">
-        <v>353.02</v>
+        <v>151.71</v>
       </c>
     </row>
     <row r="50">
@@ -2137,28 +2137,28 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5.19</v>
+        <v>5.2</v>
       </c>
       <c r="F50" t="n">
-        <v>12.66</v>
+        <v>11.96</v>
       </c>
       <c r="G50" t="n">
-        <v>179.6</v>
+        <v>189.1</v>
       </c>
       <c r="H50" t="n">
-        <v>90.8</v>
+        <v>87.5</v>
       </c>
       <c r="I50" t="n">
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>148.42</v>
+        <v>213.31</v>
       </c>
       <c r="K50" t="n">
-        <v>41.62</v>
+        <v>194.2</v>
       </c>
       <c r="L50" t="n">
-        <v>154.15</v>
+        <v>288.47</v>
       </c>
     </row>
     <row r="51">
@@ -2179,28 +2179,28 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>5.14</v>
+        <v>5.65</v>
       </c>
       <c r="F51" t="n">
-        <v>12.83</v>
+        <v>12.67</v>
       </c>
       <c r="G51" t="n">
-        <v>174.1</v>
+        <v>183.2</v>
       </c>
       <c r="H51" t="n">
-        <v>91.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I51" t="n">
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-660.5599999999999</v>
+        <v>-117.21</v>
       </c>
       <c r="K51" t="n">
-        <v>-311.42</v>
+        <v>-726.9400000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>730.29</v>
+        <v>736.33</v>
       </c>
     </row>
     <row r="52">
@@ -2221,28 +2221,28 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.12</v>
+        <v>4.64</v>
       </c>
       <c r="F52" t="n">
-        <v>11.83</v>
+        <v>11.7</v>
       </c>
       <c r="G52" t="n">
-        <v>201.7</v>
+        <v>179.9</v>
       </c>
       <c r="H52" t="n">
-        <v>93.5</v>
+        <v>94.2</v>
       </c>
       <c r="I52" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-323.27</v>
+        <v>-158.95</v>
       </c>
       <c r="K52" t="n">
-        <v>86.95999999999999</v>
+        <v>674.73</v>
       </c>
       <c r="L52" t="n">
-        <v>334.76</v>
+        <v>693.2</v>
       </c>
     </row>
     <row r="53">
@@ -2263,28 +2263,28 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.97</v>
+        <v>5.42</v>
       </c>
       <c r="F53" t="n">
-        <v>12.13</v>
+        <v>12.34</v>
       </c>
       <c r="G53" t="n">
-        <v>175.5</v>
+        <v>183.3</v>
       </c>
       <c r="H53" t="n">
-        <v>84</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>-623.84</v>
+        <v>485.68</v>
       </c>
       <c r="K53" t="n">
-        <v>188</v>
+        <v>90.28</v>
       </c>
       <c r="L53" t="n">
-        <v>651.55</v>
+        <v>494</v>
       </c>
     </row>
     <row r="54">
@@ -2305,28 +2305,28 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>5.03</v>
+        <v>5.53</v>
       </c>
       <c r="F54" t="n">
-        <v>12.52</v>
+        <v>11.91</v>
       </c>
       <c r="G54" t="n">
-        <v>180.6</v>
+        <v>198.7</v>
       </c>
       <c r="H54" t="n">
-        <v>88.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>195.89</v>
+        <v>611.39</v>
       </c>
       <c r="K54" t="n">
-        <v>-392.51</v>
+        <v>-185.18</v>
       </c>
       <c r="L54" t="n">
-        <v>438.68</v>
+        <v>638.8200000000001</v>
       </c>
     </row>
     <row r="55">
@@ -2347,28 +2347,28 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>5.36</v>
+        <v>5.82</v>
       </c>
       <c r="F55" t="n">
-        <v>12.59</v>
+        <v>12.93</v>
       </c>
       <c r="G55" t="n">
-        <v>175.4</v>
+        <v>187.8</v>
       </c>
       <c r="H55" t="n">
-        <v>87.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-165.95</v>
+        <v>-505.98</v>
       </c>
       <c r="K55" t="n">
-        <v>35.28</v>
+        <v>-344.94</v>
       </c>
       <c r="L55" t="n">
-        <v>169.66</v>
+        <v>612.37</v>
       </c>
     </row>
     <row r="56">
@@ -2389,28 +2389,28 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.4</v>
+        <v>5.48</v>
       </c>
       <c r="F56" t="n">
-        <v>12.14</v>
+        <v>12.76</v>
       </c>
       <c r="G56" t="n">
         <v>181.4</v>
       </c>
       <c r="H56" t="n">
-        <v>92.5</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>630.97</v>
+        <v>-467.84</v>
       </c>
       <c r="K56" t="n">
-        <v>980.9299999999999</v>
+        <v>-1142.87</v>
       </c>
       <c r="L56" t="n">
-        <v>1166.34</v>
+        <v>1234.92</v>
       </c>
     </row>
     <row r="57">
@@ -2431,28 +2431,28 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.15</v>
+        <v>4.98</v>
       </c>
       <c r="F57" t="n">
-        <v>11.85</v>
+        <v>12.38</v>
       </c>
       <c r="G57" t="n">
-        <v>184.2</v>
+        <v>184.4</v>
       </c>
       <c r="H57" t="n">
-        <v>89.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I57" t="n">
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>294.15</v>
+        <v>420</v>
       </c>
       <c r="K57" t="n">
-        <v>800.41</v>
+        <v>255.29</v>
       </c>
       <c r="L57" t="n">
-        <v>852.75</v>
+        <v>491.5</v>
       </c>
     </row>
     <row r="58">
@@ -2473,28 +2473,28 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>5.38</v>
+        <v>5.47</v>
       </c>
       <c r="F58" t="n">
-        <v>11.61</v>
+        <v>12.27</v>
       </c>
       <c r="G58" t="n">
-        <v>190.6</v>
+        <v>202</v>
       </c>
       <c r="H58" t="n">
-        <v>90</v>
+        <v>91.8</v>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-79.15000000000001</v>
+        <v>-502.62</v>
       </c>
       <c r="K58" t="n">
-        <v>713.59</v>
+        <v>-749.95</v>
       </c>
       <c r="L58" t="n">
-        <v>717.96</v>
+        <v>902.8</v>
       </c>
     </row>
     <row r="59">
@@ -2515,28 +2515,28 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.92</v>
+        <v>4.86</v>
       </c>
       <c r="F59" t="n">
-        <v>12.79</v>
+        <v>12.43</v>
       </c>
       <c r="G59" t="n">
-        <v>187.1</v>
+        <v>185.1</v>
       </c>
       <c r="H59" t="n">
-        <v>87.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-151.04</v>
+        <v>-156.54</v>
       </c>
       <c r="K59" t="n">
-        <v>-52.8</v>
+        <v>176.03</v>
       </c>
       <c r="L59" t="n">
-        <v>160</v>
+        <v>235.57</v>
       </c>
     </row>
     <row r="60">
@@ -2557,28 +2557,28 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.33</v>
+        <v>6.56</v>
       </c>
       <c r="F60" t="n">
-        <v>12.09</v>
+        <v>11.72</v>
       </c>
       <c r="G60" t="n">
-        <v>189.6</v>
+        <v>187.2</v>
       </c>
       <c r="H60" t="n">
-        <v>84.09999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="I60" t="n">
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-117.11</v>
+        <v>91.83</v>
       </c>
       <c r="K60" t="n">
-        <v>-226.43</v>
+        <v>-340.03</v>
       </c>
       <c r="L60" t="n">
-        <v>254.92</v>
+        <v>352.21</v>
       </c>
     </row>
     <row r="61">
@@ -2599,28 +2599,28 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>5.7</v>
+        <v>5.44</v>
       </c>
       <c r="F61" t="n">
-        <v>12.46</v>
+        <v>12.45</v>
       </c>
       <c r="G61" t="n">
-        <v>189.1</v>
+        <v>183.7</v>
       </c>
       <c r="H61" t="n">
-        <v>92.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>245.04</v>
+        <v>-260.34</v>
       </c>
       <c r="K61" t="n">
-        <v>-93.26000000000001</v>
+        <v>-75</v>
       </c>
       <c r="L61" t="n">
-        <v>262.19</v>
+        <v>270.93</v>
       </c>
     </row>
     <row r="62">
@@ -2641,28 +2641,28 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>5.22</v>
+        <v>4.97</v>
       </c>
       <c r="F62" t="n">
-        <v>12.12</v>
+        <v>11.97</v>
       </c>
       <c r="G62" t="n">
-        <v>197.7</v>
+        <v>176.3</v>
       </c>
       <c r="H62" t="n">
-        <v>93.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>195.35</v>
+        <v>379.01</v>
       </c>
       <c r="K62" t="n">
-        <v>-457.88</v>
+        <v>-301.18</v>
       </c>
       <c r="L62" t="n">
-        <v>497.81</v>
+        <v>484.11</v>
       </c>
     </row>
     <row r="63">
@@ -2683,28 +2683,28 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>5.07</v>
+        <v>5.5</v>
       </c>
       <c r="F63" t="n">
-        <v>12.22</v>
+        <v>11.79</v>
       </c>
       <c r="G63" t="n">
-        <v>178.4</v>
+        <v>172.5</v>
       </c>
       <c r="H63" t="n">
-        <v>86.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-14.68</v>
+        <v>-137.91</v>
       </c>
       <c r="K63" t="n">
-        <v>211.34</v>
+        <v>200.89</v>
       </c>
       <c r="L63" t="n">
-        <v>211.85</v>
+        <v>243.67</v>
       </c>
     </row>
     <row r="64">
@@ -2725,28 +2725,28 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>5.02</v>
+        <v>5.5</v>
       </c>
       <c r="F64" t="n">
-        <v>12.56</v>
+        <v>12.81</v>
       </c>
       <c r="G64" t="n">
-        <v>183.9</v>
+        <v>181.1</v>
       </c>
       <c r="H64" t="n">
-        <v>92.8</v>
+        <v>92.7</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>5.69</v>
+        <v>-179.59</v>
       </c>
       <c r="K64" t="n">
-        <v>-65.8</v>
+        <v>133.29</v>
       </c>
       <c r="L64" t="n">
-        <v>66.04000000000001</v>
+        <v>223.65</v>
       </c>
     </row>
     <row r="65">
@@ -2767,28 +2767,28 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.95</v>
+        <v>6.27</v>
       </c>
       <c r="F65" t="n">
-        <v>12.26</v>
+        <v>11.73</v>
       </c>
       <c r="G65" t="n">
-        <v>177.5</v>
+        <v>187.6</v>
       </c>
       <c r="H65" t="n">
-        <v>89.2</v>
+        <v>86.5</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-280.68</v>
+        <v>-304.74</v>
       </c>
       <c r="K65" t="n">
-        <v>374.33</v>
+        <v>-529</v>
       </c>
       <c r="L65" t="n">
-        <v>467.87</v>
+        <v>610.49</v>
       </c>
     </row>
     <row r="66">
@@ -2809,28 +2809,28 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.54</v>
+        <v>5.71</v>
       </c>
       <c r="F66" t="n">
-        <v>12.48</v>
+        <v>12.12</v>
       </c>
       <c r="G66" t="n">
-        <v>176.7</v>
+        <v>197.3</v>
       </c>
       <c r="H66" t="n">
-        <v>86</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I66" t="n">
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>89.03</v>
+        <v>114.42</v>
       </c>
       <c r="K66" t="n">
-        <v>42.2</v>
+        <v>-379.8</v>
       </c>
       <c r="L66" t="n">
-        <v>98.52</v>
+        <v>396.67</v>
       </c>
     </row>
     <row r="67">
@@ -2851,28 +2851,28 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>6.11</v>
+        <v>5.62</v>
       </c>
       <c r="F67" t="n">
-        <v>11.89</v>
+        <v>11.33</v>
       </c>
       <c r="G67" t="n">
-        <v>195.2</v>
+        <v>177.4</v>
       </c>
       <c r="H67" t="n">
-        <v>94.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I67" t="n">
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>542.3099999999999</v>
+        <v>872.16</v>
       </c>
       <c r="K67" t="n">
-        <v>168.26</v>
+        <v>-185.47</v>
       </c>
       <c r="L67" t="n">
-        <v>567.8099999999999</v>
+        <v>891.66</v>
       </c>
     </row>
     <row r="68">
@@ -2893,28 +2893,28 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.31</v>
+        <v>4.69</v>
       </c>
       <c r="F68" t="n">
-        <v>11.89</v>
+        <v>11.85</v>
       </c>
       <c r="G68" t="n">
-        <v>183.3</v>
+        <v>184.2</v>
       </c>
       <c r="H68" t="n">
-        <v>90.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="I68" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-294.8</v>
+        <v>206.34</v>
       </c>
       <c r="K68" t="n">
-        <v>321.55</v>
+        <v>-672.09</v>
       </c>
       <c r="L68" t="n">
-        <v>436.23</v>
+        <v>703.05</v>
       </c>
     </row>
     <row r="69">
@@ -2935,28 +2935,28 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.72</v>
+        <v>5.74</v>
       </c>
       <c r="F69" t="n">
         <v>12.55</v>
       </c>
       <c r="G69" t="n">
-        <v>191.6</v>
+        <v>184.6</v>
       </c>
       <c r="H69" t="n">
-        <v>93.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>-233.37</v>
+        <v>-632.17</v>
       </c>
       <c r="K69" t="n">
-        <v>-462.28</v>
+        <v>-953.29</v>
       </c>
       <c r="L69" t="n">
-        <v>517.85</v>
+        <v>1143.85</v>
       </c>
     </row>
     <row r="70">
@@ -2977,28 +2977,28 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>6.13</v>
+        <v>5.54</v>
       </c>
       <c r="F70" t="n">
-        <v>12.84</v>
+        <v>12.97</v>
       </c>
       <c r="G70" t="n">
-        <v>187.7</v>
+        <v>184.3</v>
       </c>
       <c r="H70" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I70" t="n">
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>147.97</v>
+        <v>334.94</v>
       </c>
       <c r="K70" t="n">
-        <v>0.26</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="L70" t="n">
-        <v>147.97</v>
+        <v>341.69</v>
       </c>
     </row>
     <row r="71">
@@ -3019,28 +3019,28 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.29</v>
+        <v>5.15</v>
       </c>
       <c r="F71" t="n">
-        <v>12.4</v>
+        <v>12.29</v>
       </c>
       <c r="G71" t="n">
-        <v>185.8</v>
+        <v>172.2</v>
       </c>
       <c r="H71" t="n">
-        <v>94.2</v>
+        <v>89.3</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-65.84</v>
+        <v>-213.66</v>
       </c>
       <c r="K71" t="n">
-        <v>-327.86</v>
+        <v>-228.11</v>
       </c>
       <c r="L71" t="n">
-        <v>334.41</v>
+        <v>312.55</v>
       </c>
     </row>
     <row r="72">
@@ -3061,28 +3061,28 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>5.01</v>
+        <v>4.83</v>
       </c>
       <c r="F72" t="n">
-        <v>12.25</v>
+        <v>11.27</v>
       </c>
       <c r="G72" t="n">
-        <v>171.4</v>
+        <v>181.5</v>
       </c>
       <c r="H72" t="n">
-        <v>92.2</v>
+        <v>92.5</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>37.28</v>
+        <v>159.83</v>
       </c>
       <c r="K72" t="n">
-        <v>-321.51</v>
+        <v>-571.47</v>
       </c>
       <c r="L72" t="n">
-        <v>323.67</v>
+        <v>593.4</v>
       </c>
     </row>
     <row r="73">
@@ -3103,28 +3103,28 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>5.08</v>
+        <v>4.99</v>
       </c>
       <c r="F73" t="n">
-        <v>12.25</v>
+        <v>12.46</v>
       </c>
       <c r="G73" t="n">
-        <v>194.5</v>
+        <v>189.1</v>
       </c>
       <c r="H73" t="n">
-        <v>95.7</v>
+        <v>100</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-88.68000000000001</v>
+        <v>487.74</v>
       </c>
       <c r="K73" t="n">
-        <v>-231.27</v>
+        <v>239.83</v>
       </c>
       <c r="L73" t="n">
-        <v>247.69</v>
+        <v>543.51</v>
       </c>
     </row>
     <row r="74">
@@ -3145,28 +3145,28 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.65</v>
+        <v>6.05</v>
       </c>
       <c r="F74" t="n">
-        <v>12.14</v>
+        <v>12.62</v>
       </c>
       <c r="G74" t="n">
-        <v>188.2</v>
+        <v>181.9</v>
       </c>
       <c r="H74" t="n">
-        <v>88.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-84.23999999999999</v>
+        <v>-129.26</v>
       </c>
       <c r="K74" t="n">
-        <v>248.29</v>
+        <v>-131.82</v>
       </c>
       <c r="L74" t="n">
-        <v>262.19</v>
+        <v>184.62</v>
       </c>
     </row>
     <row r="75">
@@ -3187,28 +3187,28 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.1</v>
+        <v>5.68</v>
       </c>
       <c r="F75" t="n">
-        <v>12.25</v>
+        <v>11.99</v>
       </c>
       <c r="G75" t="n">
-        <v>185.9</v>
+        <v>179.1</v>
       </c>
       <c r="H75" t="n">
-        <v>90.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>206.37</v>
+        <v>-227.84</v>
       </c>
       <c r="K75" t="n">
-        <v>-160.47</v>
+        <v>-226.45</v>
       </c>
       <c r="L75" t="n">
-        <v>261.42</v>
+        <v>321.23</v>
       </c>
     </row>
     <row r="76">
@@ -3229,28 +3229,28 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.42</v>
+        <v>5.49</v>
       </c>
       <c r="F76" t="n">
-        <v>12.87</v>
+        <v>12.28</v>
       </c>
       <c r="G76" t="n">
-        <v>183.1</v>
+        <v>177.5</v>
       </c>
       <c r="H76" t="n">
-        <v>87</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>3.08</v>
+        <v>-223.27</v>
       </c>
       <c r="K76" t="n">
-        <v>304.46</v>
+        <v>-217.97</v>
       </c>
       <c r="L76" t="n">
-        <v>304.48</v>
+        <v>312.02</v>
       </c>
     </row>
     <row r="77">
@@ -3271,28 +3271,28 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.55</v>
+        <v>5.81</v>
       </c>
       <c r="F77" t="n">
-        <v>12.02</v>
+        <v>11.89</v>
       </c>
       <c r="G77" t="n">
-        <v>192.5</v>
+        <v>191.3</v>
       </c>
       <c r="H77" t="n">
-        <v>100</v>
+        <v>90.5</v>
       </c>
       <c r="I77" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>198.41</v>
+        <v>-79.09</v>
       </c>
       <c r="K77" t="n">
-        <v>0.93</v>
+        <v>-452.66</v>
       </c>
       <c r="L77" t="n">
-        <v>198.41</v>
+        <v>459.52</v>
       </c>
     </row>
     <row r="78">
@@ -3313,28 +3313,28 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.7</v>
+        <v>4.98</v>
       </c>
       <c r="F78" t="n">
-        <v>11.53</v>
+        <v>12.26</v>
       </c>
       <c r="G78" t="n">
-        <v>189.1</v>
+        <v>177.5</v>
       </c>
       <c r="H78" t="n">
-        <v>91.90000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="I78" t="n">
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-25.11</v>
+        <v>-527.54</v>
       </c>
       <c r="K78" t="n">
-        <v>2.2</v>
+        <v>-360.76</v>
       </c>
       <c r="L78" t="n">
-        <v>25.21</v>
+        <v>639.1</v>
       </c>
     </row>
     <row r="79">
@@ -3355,28 +3355,28 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.33</v>
+        <v>5.24</v>
       </c>
       <c r="F79" t="n">
-        <v>12.28</v>
+        <v>11.85</v>
       </c>
       <c r="G79" t="n">
-        <v>181</v>
+        <v>176.6</v>
       </c>
       <c r="H79" t="n">
-        <v>89</v>
+        <v>93.7</v>
       </c>
       <c r="I79" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>2.56</v>
+        <v>18.34</v>
       </c>
       <c r="K79" t="n">
-        <v>-378.76</v>
+        <v>143.07</v>
       </c>
       <c r="L79" t="n">
-        <v>378.77</v>
+        <v>144.24</v>
       </c>
     </row>
     <row r="80">
@@ -3397,28 +3397,28 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.85</v>
+        <v>5.55</v>
       </c>
       <c r="F80" t="n">
-        <v>12.29</v>
+        <v>12.62</v>
       </c>
       <c r="G80" t="n">
-        <v>184.9</v>
+        <v>191.9</v>
       </c>
       <c r="H80" t="n">
-        <v>89.7</v>
+        <v>91.2</v>
       </c>
       <c r="I80" t="n">
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-296.79</v>
+        <v>-775.87</v>
       </c>
       <c r="K80" t="n">
-        <v>-304.08</v>
+        <v>295.99</v>
       </c>
       <c r="L80" t="n">
-        <v>424.91</v>
+        <v>830.41</v>
       </c>
     </row>
     <row r="81">
@@ -3439,28 +3439,28 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>5.74</v>
+        <v>6.09</v>
       </c>
       <c r="F81" t="n">
-        <v>11.97</v>
+        <v>13.02</v>
       </c>
       <c r="G81" t="n">
-        <v>172.1</v>
+        <v>193.1</v>
       </c>
       <c r="H81" t="n">
-        <v>80.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-97.67</v>
+        <v>-156.88</v>
       </c>
       <c r="K81" t="n">
-        <v>308.47</v>
+        <v>-401.82</v>
       </c>
       <c r="L81" t="n">
-        <v>323.57</v>
+        <v>431.36</v>
       </c>
     </row>
     <row r="82">
@@ -3481,28 +3481,28 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.36</v>
+        <v>5.63</v>
       </c>
       <c r="F82" t="n">
-        <v>12.46</v>
+        <v>13.01</v>
       </c>
       <c r="G82" t="n">
-        <v>173.4</v>
+        <v>202.1</v>
       </c>
       <c r="H82" t="n">
-        <v>92.5</v>
+        <v>86.5</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-178.38</v>
+        <v>-342.65</v>
       </c>
       <c r="K82" t="n">
-        <v>605.6</v>
+        <v>255.89</v>
       </c>
       <c r="L82" t="n">
-        <v>631.33</v>
+        <v>427.66</v>
       </c>
     </row>
     <row r="83">
@@ -3523,28 +3523,28 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.56</v>
+        <v>5.9</v>
       </c>
       <c r="F83" t="n">
-        <v>12.46</v>
+        <v>12.55</v>
       </c>
       <c r="G83" t="n">
-        <v>179.7</v>
+        <v>191.6</v>
       </c>
       <c r="H83" t="n">
-        <v>86.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I83" t="n">
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>403.99</v>
+        <v>-940.1</v>
       </c>
       <c r="K83" t="n">
-        <v>531.17</v>
+        <v>-66.76000000000001</v>
       </c>
       <c r="L83" t="n">
-        <v>667.34</v>
+        <v>942.47</v>
       </c>
     </row>
     <row r="84">
@@ -3565,28 +3565,28 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>5.86</v>
+        <v>5.44</v>
       </c>
       <c r="F84" t="n">
-        <v>11.95</v>
+        <v>12.84</v>
       </c>
       <c r="G84" t="n">
-        <v>183.2</v>
+        <v>199.5</v>
       </c>
       <c r="H84" t="n">
-        <v>83.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="I84" t="n">
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>669.98</v>
+        <v>637.13</v>
       </c>
       <c r="K84" t="n">
-        <v>-66.11</v>
+        <v>-88</v>
       </c>
       <c r="L84" t="n">
-        <v>673.23</v>
+        <v>643.1799999999999</v>
       </c>
     </row>
     <row r="85">
@@ -3607,28 +3607,28 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.83</v>
+        <v>5.74</v>
       </c>
       <c r="F85" t="n">
-        <v>12.77</v>
+        <v>12.28</v>
       </c>
       <c r="G85" t="n">
-        <v>189.3</v>
+        <v>175.3</v>
       </c>
       <c r="H85" t="n">
-        <v>90.59999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="I85" t="n">
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-410.44</v>
+        <v>907.15</v>
       </c>
       <c r="K85" t="n">
-        <v>-22.82</v>
+        <v>341.38</v>
       </c>
       <c r="L85" t="n">
-        <v>411.07</v>
+        <v>969.26</v>
       </c>
     </row>
     <row r="86">
@@ -3649,28 +3649,28 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>6.05</v>
+        <v>5.68</v>
       </c>
       <c r="F86" t="n">
-        <v>12.5</v>
+        <v>11.87</v>
       </c>
       <c r="G86" t="n">
-        <v>192.8</v>
+        <v>184.1</v>
       </c>
       <c r="H86" t="n">
-        <v>91.40000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="I86" t="n">
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>142.57</v>
+        <v>-484.53</v>
       </c>
       <c r="K86" t="n">
-        <v>-1206.85</v>
+        <v>-951.14</v>
       </c>
       <c r="L86" t="n">
-        <v>1215.24</v>
+        <v>1067.44</v>
       </c>
     </row>
     <row r="87">
@@ -3691,28 +3691,28 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.83</v>
+        <v>5.88</v>
       </c>
       <c r="F87" t="n">
-        <v>11.84</v>
+        <v>12.72</v>
       </c>
       <c r="G87" t="n">
-        <v>189.5</v>
+        <v>193.7</v>
       </c>
       <c r="H87" t="n">
-        <v>92.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>943.01</v>
+        <v>-13.09</v>
       </c>
       <c r="K87" t="n">
-        <v>-12.96</v>
+        <v>-701.45</v>
       </c>
       <c r="L87" t="n">
-        <v>943.1</v>
+        <v>701.5700000000001</v>
       </c>
     </row>
     <row r="88">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.85</v>
+        <v>5.26</v>
       </c>
       <c r="F88" t="n">
-        <v>12.26</v>
+        <v>12.74</v>
       </c>
       <c r="G88" t="n">
-        <v>177.7</v>
+        <v>196</v>
       </c>
       <c r="H88" t="n">
-        <v>91.09999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-332.05</v>
+        <v>-756.8099999999999</v>
       </c>
       <c r="K88" t="n">
-        <v>371.26</v>
+        <v>-322.42</v>
       </c>
       <c r="L88" t="n">
-        <v>498.09</v>
+        <v>822.63</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-01.xlsx
+++ b/output/2024-04-01.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-48.11</v>
+        <v>-96.33</v>
       </c>
       <c r="K14" t="n">
-        <v>-115.25</v>
+        <v>-230.75</v>
       </c>
       <c r="L14" t="n">
-        <v>124.89</v>
+        <v>250.05</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-50.59</v>
+        <v>-113.3</v>
       </c>
       <c r="K15" t="n">
-        <v>88.87</v>
+        <v>199.04</v>
       </c>
       <c r="L15" t="n">
-        <v>102.26</v>
+        <v>229.03</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-266.75</v>
+        <v>-348.12</v>
       </c>
       <c r="K16" t="n">
-        <v>-201.63</v>
+        <v>-263.14</v>
       </c>
       <c r="L16" t="n">
-        <v>334.38</v>
+        <v>436.39</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>122.89</v>
+        <v>162.96</v>
       </c>
       <c r="K17" t="n">
-        <v>293.62</v>
+        <v>389.38</v>
       </c>
       <c r="L17" t="n">
-        <v>318.3</v>
+        <v>422.1</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>31.33</v>
+        <v>84.8</v>
       </c>
       <c r="K18" t="n">
-        <v>64.87</v>
+        <v>175.56</v>
       </c>
       <c r="L18" t="n">
-        <v>72.04000000000001</v>
+        <v>194.97</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>338.95</v>
+        <v>464.54</v>
       </c>
       <c r="K19" t="n">
-        <v>-223.16</v>
+        <v>-305.84</v>
       </c>
       <c r="L19" t="n">
-        <v>405.82</v>
+        <v>556.1799999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>337.18</v>
+        <v>476.75</v>
       </c>
       <c r="K20" t="n">
-        <v>-60.96</v>
+        <v>-86.19</v>
       </c>
       <c r="L20" t="n">
-        <v>342.64</v>
+        <v>484.48</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-342.44</v>
+        <v>-479.75</v>
       </c>
       <c r="K21" t="n">
-        <v>-137.37</v>
+        <v>-192.44</v>
       </c>
       <c r="L21" t="n">
-        <v>368.96</v>
+        <v>516.91</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-155.79</v>
+        <v>-333.02</v>
       </c>
       <c r="K22" t="n">
-        <v>-103.05</v>
+        <v>-220.27</v>
       </c>
       <c r="L22" t="n">
-        <v>186.79</v>
+        <v>399.28</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>186.98</v>
+        <v>475.15</v>
       </c>
       <c r="K23" t="n">
-        <v>-65.61</v>
+        <v>-166.72</v>
       </c>
       <c r="L23" t="n">
-        <v>198.15</v>
+        <v>503.55</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>174.11</v>
+        <v>295.11</v>
       </c>
       <c r="K24" t="n">
-        <v>-441.33</v>
+        <v>-748.03</v>
       </c>
       <c r="L24" t="n">
-        <v>474.43</v>
+        <v>804.14</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-456.97</v>
+        <v>-706.17</v>
       </c>
       <c r="K25" t="n">
-        <v>-265.31</v>
+        <v>-410</v>
       </c>
       <c r="L25" t="n">
-        <v>528.41</v>
+        <v>816.5599999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>797.98</v>
+        <v>1061.94</v>
       </c>
       <c r="K26" t="n">
-        <v>-1544.79</v>
+        <v>-2055.77</v>
       </c>
       <c r="L26" t="n">
-        <v>1738.72</v>
+        <v>2313.85</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-841.6900000000001</v>
+        <v>-1276.8</v>
       </c>
       <c r="K27" t="n">
-        <v>355.24</v>
+        <v>538.87</v>
       </c>
       <c r="L27" t="n">
-        <v>913.59</v>
+        <v>1385.86</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>945.61</v>
+        <v>1362.57</v>
       </c>
       <c r="K28" t="n">
-        <v>519.95</v>
+        <v>749.22</v>
       </c>
       <c r="L28" t="n">
-        <v>1079.14</v>
+        <v>1554.96</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>205.77</v>
+        <v>265.57</v>
       </c>
       <c r="K29" t="n">
-        <v>-253.32</v>
+        <v>-326.93</v>
       </c>
       <c r="L29" t="n">
-        <v>326.37</v>
+        <v>421.2</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>149.4</v>
+        <v>185.47</v>
       </c>
       <c r="K30" t="n">
-        <v>-333.56</v>
+        <v>-414.08</v>
       </c>
       <c r="L30" t="n">
-        <v>365.49</v>
+        <v>453.72</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>5.38</v>
+        <v>7.33</v>
       </c>
       <c r="K31" t="n">
-        <v>-258.68</v>
+        <v>-352.65</v>
       </c>
       <c r="L31" t="n">
-        <v>258.74</v>
+        <v>352.72</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>89.98999999999999</v>
+        <v>209.16</v>
       </c>
       <c r="K32" t="n">
-        <v>5.12</v>
+        <v>11.91</v>
       </c>
       <c r="L32" t="n">
-        <v>90.13</v>
+        <v>209.5</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>95.11</v>
+        <v>151.02</v>
       </c>
       <c r="K33" t="n">
-        <v>209.07</v>
+        <v>331.95</v>
       </c>
       <c r="L33" t="n">
-        <v>229.68</v>
+        <v>364.69</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-209.79</v>
+        <v>-319.94</v>
       </c>
       <c r="K34" t="n">
-        <v>-49.43</v>
+        <v>-75.38</v>
       </c>
       <c r="L34" t="n">
-        <v>215.54</v>
+        <v>328.7</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-289.61</v>
+        <v>-494.94</v>
       </c>
       <c r="K35" t="n">
-        <v>28.49</v>
+        <v>48.68</v>
       </c>
       <c r="L35" t="n">
-        <v>291.01</v>
+        <v>497.33</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>710.08</v>
+        <v>874.64</v>
       </c>
       <c r="K36" t="n">
-        <v>-102.84</v>
+        <v>-126.67</v>
       </c>
       <c r="L36" t="n">
-        <v>717.48</v>
+        <v>883.76</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-460.31</v>
+        <v>-587.49</v>
       </c>
       <c r="K37" t="n">
-        <v>-252.34</v>
+        <v>-322.06</v>
       </c>
       <c r="L37" t="n">
-        <v>524.9400000000001</v>
+        <v>669.97</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-246.28</v>
+        <v>-535.24</v>
       </c>
       <c r="K38" t="n">
-        <v>146.04</v>
+        <v>317.39</v>
       </c>
       <c r="L38" t="n">
-        <v>286.32</v>
+        <v>622.28</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-382.98</v>
+        <v>-713.59</v>
       </c>
       <c r="K39" t="n">
-        <v>-190.88</v>
+        <v>-355.67</v>
       </c>
       <c r="L39" t="n">
-        <v>427.91</v>
+        <v>797.3099999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>433.25</v>
+        <v>559.42</v>
       </c>
       <c r="K40" t="n">
-        <v>-1184.34</v>
+        <v>-1529.25</v>
       </c>
       <c r="L40" t="n">
-        <v>1261.1</v>
+        <v>1628.36</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>559.1799999999999</v>
+        <v>853.03</v>
       </c>
       <c r="K41" t="n">
-        <v>593.55</v>
+        <v>905.47</v>
       </c>
       <c r="L41" t="n">
-        <v>815.47</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-359.79</v>
+        <v>-529.7</v>
       </c>
       <c r="K42" t="n">
-        <v>-929.98</v>
+        <v>-1369.17</v>
       </c>
       <c r="L42" t="n">
-        <v>997.15</v>
+        <v>1468.07</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>313.34</v>
+        <v>662.53</v>
       </c>
       <c r="K43" t="n">
-        <v>-228.98</v>
+        <v>-484.17</v>
       </c>
       <c r="L43" t="n">
-        <v>388.09</v>
+        <v>820.59</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>92.73</v>
+        <v>171.28</v>
       </c>
       <c r="K44" t="n">
-        <v>-48.17</v>
+        <v>-88.98</v>
       </c>
       <c r="L44" t="n">
-        <v>104.5</v>
+        <v>193.01</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>246.54</v>
+        <v>352.46</v>
       </c>
       <c r="K45" t="n">
-        <v>75.94</v>
+        <v>108.57</v>
       </c>
       <c r="L45" t="n">
-        <v>257.97</v>
+        <v>368.8</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>208.41</v>
+        <v>267.15</v>
       </c>
       <c r="K46" t="n">
-        <v>-172.8</v>
+        <v>-221.5</v>
       </c>
       <c r="L46" t="n">
-        <v>270.73</v>
+        <v>347.03</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-123.86</v>
+        <v>-220.98</v>
       </c>
       <c r="K47" t="n">
-        <v>-98.40000000000001</v>
+        <v>-175.55</v>
       </c>
       <c r="L47" t="n">
-        <v>158.19</v>
+        <v>282.23</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>56.34</v>
+        <v>108.71</v>
       </c>
       <c r="K48" t="n">
-        <v>176.51</v>
+        <v>340.6</v>
       </c>
       <c r="L48" t="n">
-        <v>185.28</v>
+        <v>357.53</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>18.28</v>
+        <v>35.01</v>
       </c>
       <c r="K49" t="n">
-        <v>150.61</v>
+        <v>288.43</v>
       </c>
       <c r="L49" t="n">
-        <v>151.71</v>
+        <v>290.55</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>213.31</v>
+        <v>377.28</v>
       </c>
       <c r="K50" t="n">
-        <v>194.2</v>
+        <v>343.49</v>
       </c>
       <c r="L50" t="n">
-        <v>288.47</v>
+        <v>510.22</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-117.21</v>
+        <v>-156.96</v>
       </c>
       <c r="K51" t="n">
-        <v>-726.9400000000001</v>
+        <v>-973.52</v>
       </c>
       <c r="L51" t="n">
-        <v>736.33</v>
+        <v>986.09</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-158.95</v>
+        <v>-197.8</v>
       </c>
       <c r="K52" t="n">
-        <v>674.73</v>
+        <v>839.63</v>
       </c>
       <c r="L52" t="n">
-        <v>693.2</v>
+        <v>862.62</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>485.68</v>
+        <v>864.34</v>
       </c>
       <c r="K53" t="n">
-        <v>90.28</v>
+        <v>160.66</v>
       </c>
       <c r="L53" t="n">
-        <v>494</v>
+        <v>879.15</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>611.39</v>
+        <v>973.51</v>
       </c>
       <c r="K54" t="n">
-        <v>-185.18</v>
+        <v>-294.85</v>
       </c>
       <c r="L54" t="n">
-        <v>638.8200000000001</v>
+        <v>1017.19</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-505.98</v>
+        <v>-860.24</v>
       </c>
       <c r="K55" t="n">
-        <v>-344.94</v>
+        <v>-586.45</v>
       </c>
       <c r="L55" t="n">
-        <v>612.37</v>
+        <v>1041.12</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-467.84</v>
+        <v>-708.01</v>
       </c>
       <c r="K56" t="n">
-        <v>-1142.87</v>
+        <v>-1729.58</v>
       </c>
       <c r="L56" t="n">
-        <v>1234.92</v>
+        <v>1868.88</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>420</v>
+        <v>824.1</v>
       </c>
       <c r="K57" t="n">
-        <v>255.29</v>
+        <v>500.92</v>
       </c>
       <c r="L57" t="n">
-        <v>491.5</v>
+        <v>964.4</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-502.62</v>
+        <v>-813.11</v>
       </c>
       <c r="K58" t="n">
-        <v>-749.95</v>
+        <v>-1213.23</v>
       </c>
       <c r="L58" t="n">
-        <v>902.8</v>
+        <v>1460.51</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-156.54</v>
+        <v>-210.83</v>
       </c>
       <c r="K59" t="n">
-        <v>176.03</v>
+        <v>237.08</v>
       </c>
       <c r="L59" t="n">
-        <v>235.57</v>
+        <v>317.26</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>91.83</v>
+        <v>139.79</v>
       </c>
       <c r="K60" t="n">
-        <v>-340.03</v>
+        <v>-517.59</v>
       </c>
       <c r="L60" t="n">
-        <v>352.21</v>
+        <v>536.13</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-260.34</v>
+        <v>-357.41</v>
       </c>
       <c r="K61" t="n">
-        <v>-75</v>
+        <v>-102.96</v>
       </c>
       <c r="L61" t="n">
-        <v>270.93</v>
+        <v>371.95</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>379.01</v>
+        <v>452.29</v>
       </c>
       <c r="K62" t="n">
-        <v>-301.18</v>
+        <v>-359.41</v>
       </c>
       <c r="L62" t="n">
-        <v>484.11</v>
+        <v>577.7</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-137.91</v>
+        <v>-208.07</v>
       </c>
       <c r="K63" t="n">
-        <v>200.89</v>
+        <v>303.11</v>
       </c>
       <c r="L63" t="n">
-        <v>243.67</v>
+        <v>367.65</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-179.59</v>
+        <v>-288.81</v>
       </c>
       <c r="K64" t="n">
-        <v>133.29</v>
+        <v>214.35</v>
       </c>
       <c r="L64" t="n">
-        <v>223.65</v>
+        <v>359.66</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-304.74</v>
+        <v>-422.19</v>
       </c>
       <c r="K65" t="n">
-        <v>-529</v>
+        <v>-732.88</v>
       </c>
       <c r="L65" t="n">
-        <v>610.49</v>
+        <v>845.79</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>114.42</v>
+        <v>198.61</v>
       </c>
       <c r="K66" t="n">
-        <v>-379.8</v>
+        <v>-659.24</v>
       </c>
       <c r="L66" t="n">
-        <v>396.67</v>
+        <v>688.51</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>872.16</v>
+        <v>1093.54</v>
       </c>
       <c r="K67" t="n">
-        <v>-185.47</v>
+        <v>-232.55</v>
       </c>
       <c r="L67" t="n">
-        <v>891.66</v>
+        <v>1117.99</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>206.34</v>
+        <v>281.46</v>
       </c>
       <c r="K68" t="n">
-        <v>-672.09</v>
+        <v>-916.77</v>
       </c>
       <c r="L68" t="n">
-        <v>703.05</v>
+        <v>959.01</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>-632.17</v>
+        <v>-870.25</v>
       </c>
       <c r="K69" t="n">
-        <v>-953.29</v>
+        <v>-1312.31</v>
       </c>
       <c r="L69" t="n">
-        <v>1143.85</v>
+        <v>1574.64</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>334.94</v>
+        <v>718.42</v>
       </c>
       <c r="K70" t="n">
-        <v>67.59999999999999</v>
+        <v>144.99</v>
       </c>
       <c r="L70" t="n">
-        <v>341.69</v>
+        <v>732.91</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-213.66</v>
+        <v>-503.13</v>
       </c>
       <c r="K71" t="n">
-        <v>-228.11</v>
+        <v>-537.16</v>
       </c>
       <c r="L71" t="n">
-        <v>312.55</v>
+        <v>735.99</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>159.83</v>
+        <v>285.5</v>
       </c>
       <c r="K72" t="n">
-        <v>-571.47</v>
+        <v>-1020.77</v>
       </c>
       <c r="L72" t="n">
-        <v>593.4</v>
+        <v>1059.94</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>487.74</v>
+        <v>925.66</v>
       </c>
       <c r="K73" t="n">
-        <v>239.83</v>
+        <v>455.16</v>
       </c>
       <c r="L73" t="n">
-        <v>543.51</v>
+        <v>1031.52</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-129.26</v>
+        <v>-233.69</v>
       </c>
       <c r="K74" t="n">
-        <v>-131.82</v>
+        <v>-238.31</v>
       </c>
       <c r="L74" t="n">
-        <v>184.62</v>
+        <v>333.77</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-227.84</v>
+        <v>-315.82</v>
       </c>
       <c r="K75" t="n">
-        <v>-226.45</v>
+        <v>-313.89</v>
       </c>
       <c r="L75" t="n">
-        <v>321.23</v>
+        <v>445.28</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-223.27</v>
+        <v>-306.54</v>
       </c>
       <c r="K76" t="n">
-        <v>-217.97</v>
+        <v>-299.26</v>
       </c>
       <c r="L76" t="n">
-        <v>312.02</v>
+        <v>428.4</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-79.09</v>
+        <v>-108.42</v>
       </c>
       <c r="K77" t="n">
-        <v>-452.66</v>
+        <v>-620.51</v>
       </c>
       <c r="L77" t="n">
-        <v>459.52</v>
+        <v>629.91</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-527.54</v>
+        <v>-602.27</v>
       </c>
       <c r="K78" t="n">
-        <v>-360.76</v>
+        <v>-411.87</v>
       </c>
       <c r="L78" t="n">
-        <v>639.1</v>
+        <v>729.64</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>18.34</v>
+        <v>35.27</v>
       </c>
       <c r="K79" t="n">
-        <v>143.07</v>
+        <v>275.06</v>
       </c>
       <c r="L79" t="n">
-        <v>144.24</v>
+        <v>277.31</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-775.87</v>
+        <v>-1002.7</v>
       </c>
       <c r="K80" t="n">
-        <v>295.99</v>
+        <v>382.52</v>
       </c>
       <c r="L80" t="n">
-        <v>830.41</v>
+        <v>1073.19</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-156.88</v>
+        <v>-252.06</v>
       </c>
       <c r="K81" t="n">
-        <v>-401.82</v>
+        <v>-645.63</v>
       </c>
       <c r="L81" t="n">
-        <v>431.36</v>
+        <v>693.09</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-342.65</v>
+        <v>-517.53</v>
       </c>
       <c r="K82" t="n">
-        <v>255.89</v>
+        <v>386.48</v>
       </c>
       <c r="L82" t="n">
-        <v>427.66</v>
+        <v>645.91</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-940.1</v>
+        <v>-1405.04</v>
       </c>
       <c r="K83" t="n">
-        <v>-66.76000000000001</v>
+        <v>-99.78</v>
       </c>
       <c r="L83" t="n">
-        <v>942.47</v>
+        <v>1408.58</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>637.13</v>
+        <v>1029.18</v>
       </c>
       <c r="K84" t="n">
-        <v>-88</v>
+        <v>-142.15</v>
       </c>
       <c r="L84" t="n">
-        <v>643.1799999999999</v>
+        <v>1038.95</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>907.15</v>
+        <v>1328.01</v>
       </c>
       <c r="K85" t="n">
-        <v>341.38</v>
+        <v>499.75</v>
       </c>
       <c r="L85" t="n">
-        <v>969.26</v>
+        <v>1418.93</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-484.53</v>
+        <v>-778.13</v>
       </c>
       <c r="K86" t="n">
-        <v>-951.14</v>
+        <v>-1527.47</v>
       </c>
       <c r="L86" t="n">
-        <v>1067.44</v>
+        <v>1714.25</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>-13.09</v>
+        <v>-22.99</v>
       </c>
       <c r="K87" t="n">
-        <v>-701.45</v>
+        <v>-1232.43</v>
       </c>
       <c r="L87" t="n">
-        <v>701.5700000000001</v>
+        <v>1232.64</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-756.8099999999999</v>
+        <v>-1209.59</v>
       </c>
       <c r="K88" t="n">
-        <v>-322.42</v>
+        <v>-515.3200000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>822.63</v>
+        <v>1314.79</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-01.xlsx
+++ b/output/2024-04-01.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-96.33</v>
+        <v>-56.23</v>
       </c>
       <c r="K14" t="n">
-        <v>-230.75</v>
+        <v>-134.69</v>
       </c>
       <c r="L14" t="n">
-        <v>250.05</v>
+        <v>145.95</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-113.3</v>
+        <v>-66.17</v>
       </c>
       <c r="K15" t="n">
-        <v>199.04</v>
+        <v>116.24</v>
       </c>
       <c r="L15" t="n">
-        <v>229.03</v>
+        <v>133.76</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-348.12</v>
+        <v>-203.36</v>
       </c>
       <c r="K16" t="n">
-        <v>-263.14</v>
+        <v>-153.72</v>
       </c>
       <c r="L16" t="n">
-        <v>436.39</v>
+        <v>254.92</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>162.96</v>
+        <v>92.8</v>
       </c>
       <c r="K17" t="n">
-        <v>389.38</v>
+        <v>221.72</v>
       </c>
       <c r="L17" t="n">
-        <v>422.1</v>
+        <v>240.36</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>84.8</v>
+        <v>50.6</v>
       </c>
       <c r="K18" t="n">
-        <v>175.56</v>
+        <v>104.77</v>
       </c>
       <c r="L18" t="n">
-        <v>194.97</v>
+        <v>116.35</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>464.54</v>
+        <v>258.06</v>
       </c>
       <c r="K19" t="n">
-        <v>-305.84</v>
+        <v>-169.9</v>
       </c>
       <c r="L19" t="n">
-        <v>556.1799999999999</v>
+        <v>308.97</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>476.75</v>
+        <v>256.2</v>
       </c>
       <c r="K20" t="n">
-        <v>-86.19</v>
+        <v>-46.32</v>
       </c>
       <c r="L20" t="n">
-        <v>484.48</v>
+        <v>260.35</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-479.75</v>
+        <v>-243.54</v>
       </c>
       <c r="K21" t="n">
-        <v>-192.44</v>
+        <v>-97.69</v>
       </c>
       <c r="L21" t="n">
-        <v>516.91</v>
+        <v>262.4</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-333.02</v>
+        <v>-164.22</v>
       </c>
       <c r="K22" t="n">
-        <v>-220.27</v>
+        <v>-108.62</v>
       </c>
       <c r="L22" t="n">
-        <v>399.28</v>
+        <v>196.9</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>475.15</v>
+        <v>209.33</v>
       </c>
       <c r="K23" t="n">
-        <v>-166.72</v>
+        <v>-73.45</v>
       </c>
       <c r="L23" t="n">
-        <v>503.55</v>
+        <v>221.85</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>295.11</v>
+        <v>129.52</v>
       </c>
       <c r="K24" t="n">
-        <v>-748.03</v>
+        <v>-328.29</v>
       </c>
       <c r="L24" t="n">
-        <v>804.14</v>
+        <v>352.91</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-706.17</v>
+        <v>-312.67</v>
       </c>
       <c r="K25" t="n">
-        <v>-410</v>
+        <v>-181.54</v>
       </c>
       <c r="L25" t="n">
-        <v>816.5599999999999</v>
+        <v>361.55</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>1061.94</v>
+        <v>421.77</v>
       </c>
       <c r="K26" t="n">
-        <v>-2055.77</v>
+        <v>-816.5</v>
       </c>
       <c r="L26" t="n">
-        <v>2313.85</v>
+        <v>919</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-1276.8</v>
+        <v>-510.19</v>
       </c>
       <c r="K27" t="n">
-        <v>538.87</v>
+        <v>215.33</v>
       </c>
       <c r="L27" t="n">
-        <v>1385.86</v>
+        <v>553.77</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>1362.57</v>
+        <v>545.6900000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>749.22</v>
+        <v>300.05</v>
       </c>
       <c r="L28" t="n">
-        <v>1554.96</v>
+        <v>622.74</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>265.57</v>
+        <v>155.74</v>
       </c>
       <c r="K29" t="n">
-        <v>-326.93</v>
+        <v>-191.73</v>
       </c>
       <c r="L29" t="n">
-        <v>421.2</v>
+        <v>247.01</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>185.47</v>
+        <v>110.82</v>
       </c>
       <c r="K30" t="n">
-        <v>-414.08</v>
+        <v>-247.43</v>
       </c>
       <c r="L30" t="n">
-        <v>453.72</v>
+        <v>271.11</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>7.33</v>
+        <v>4.32</v>
       </c>
       <c r="K31" t="n">
-        <v>-352.65</v>
+        <v>-207.92</v>
       </c>
       <c r="L31" t="n">
-        <v>352.72</v>
+        <v>207.97</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>209.16</v>
+        <v>124.82</v>
       </c>
       <c r="K32" t="n">
-        <v>11.91</v>
+        <v>7.11</v>
       </c>
       <c r="L32" t="n">
-        <v>209.5</v>
+        <v>125.02</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>151.02</v>
+        <v>85.08</v>
       </c>
       <c r="K33" t="n">
-        <v>331.95</v>
+        <v>187.02</v>
       </c>
       <c r="L33" t="n">
-        <v>364.69</v>
+        <v>205.46</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-319.94</v>
+        <v>-186.38</v>
       </c>
       <c r="K34" t="n">
-        <v>-75.38</v>
+        <v>-43.91</v>
       </c>
       <c r="L34" t="n">
-        <v>328.7</v>
+        <v>191.48</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-494.94</v>
+        <v>-243.93</v>
       </c>
       <c r="K35" t="n">
-        <v>48.68</v>
+        <v>23.99</v>
       </c>
       <c r="L35" t="n">
-        <v>497.33</v>
+        <v>245.11</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>874.64</v>
+        <v>458.47</v>
       </c>
       <c r="K36" t="n">
-        <v>-126.67</v>
+        <v>-66.40000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>883.76</v>
+        <v>463.25</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-587.49</v>
+        <v>-296.4</v>
       </c>
       <c r="K37" t="n">
-        <v>-322.06</v>
+        <v>-162.48</v>
       </c>
       <c r="L37" t="n">
-        <v>669.97</v>
+        <v>338.01</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-535.24</v>
+        <v>-237.83</v>
       </c>
       <c r="K38" t="n">
-        <v>317.39</v>
+        <v>141.03</v>
       </c>
       <c r="L38" t="n">
-        <v>622.28</v>
+        <v>276.5</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-713.59</v>
+        <v>-309.07</v>
       </c>
       <c r="K39" t="n">
-        <v>-355.67</v>
+        <v>-154.04</v>
       </c>
       <c r="L39" t="n">
-        <v>797.3099999999999</v>
+        <v>345.33</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>559.42</v>
+        <v>249.08</v>
       </c>
       <c r="K40" t="n">
-        <v>-1529.25</v>
+        <v>-680.89</v>
       </c>
       <c r="L40" t="n">
-        <v>1628.36</v>
+        <v>725.02</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>853.03</v>
+        <v>345.63</v>
       </c>
       <c r="K41" t="n">
-        <v>905.47</v>
+        <v>366.87</v>
       </c>
       <c r="L41" t="n">
-        <v>1244</v>
+        <v>504.04</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-529.7</v>
+        <v>-219.77</v>
       </c>
       <c r="K42" t="n">
-        <v>-1369.17</v>
+        <v>-568.05</v>
       </c>
       <c r="L42" t="n">
-        <v>1468.07</v>
+        <v>609.08</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>662.53</v>
+        <v>264.94</v>
       </c>
       <c r="K43" t="n">
-        <v>-484.17</v>
+        <v>-193.61</v>
       </c>
       <c r="L43" t="n">
-        <v>820.59</v>
+        <v>328.14</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>171.28</v>
+        <v>105.08</v>
       </c>
       <c r="K44" t="n">
-        <v>-88.98</v>
+        <v>-54.59</v>
       </c>
       <c r="L44" t="n">
-        <v>193.01</v>
+        <v>118.41</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>352.46</v>
+        <v>205.46</v>
       </c>
       <c r="K45" t="n">
-        <v>108.57</v>
+        <v>63.29</v>
       </c>
       <c r="L45" t="n">
-        <v>368.8</v>
+        <v>214.99</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>267.15</v>
+        <v>168.23</v>
       </c>
       <c r="K46" t="n">
-        <v>-221.5</v>
+        <v>-139.48</v>
       </c>
       <c r="L46" t="n">
-        <v>347.03</v>
+        <v>218.53</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-220.98</v>
+        <v>-133.14</v>
       </c>
       <c r="K47" t="n">
-        <v>-175.55</v>
+        <v>-105.77</v>
       </c>
       <c r="L47" t="n">
-        <v>282.23</v>
+        <v>170.04</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>108.71</v>
+        <v>60.06</v>
       </c>
       <c r="K48" t="n">
-        <v>340.6</v>
+        <v>188.19</v>
       </c>
       <c r="L48" t="n">
-        <v>357.53</v>
+        <v>197.55</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>35.01</v>
+        <v>19.75</v>
       </c>
       <c r="K49" t="n">
-        <v>288.43</v>
+        <v>162.72</v>
       </c>
       <c r="L49" t="n">
-        <v>290.55</v>
+        <v>163.91</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>377.28</v>
+        <v>184.51</v>
       </c>
       <c r="K50" t="n">
-        <v>343.49</v>
+        <v>167.99</v>
       </c>
       <c r="L50" t="n">
-        <v>510.22</v>
+        <v>249.53</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-156.96</v>
+        <v>-75.95999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-973.52</v>
+        <v>-471.13</v>
       </c>
       <c r="L51" t="n">
-        <v>986.09</v>
+        <v>477.22</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-197.8</v>
+        <v>-98.3</v>
       </c>
       <c r="K52" t="n">
-        <v>839.63</v>
+        <v>417.25</v>
       </c>
       <c r="L52" t="n">
-        <v>862.62</v>
+        <v>428.67</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>864.34</v>
+        <v>391.25</v>
       </c>
       <c r="K53" t="n">
-        <v>160.66</v>
+        <v>72.73</v>
       </c>
       <c r="L53" t="n">
-        <v>879.15</v>
+        <v>397.95</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>973.51</v>
+        <v>429.11</v>
       </c>
       <c r="K54" t="n">
-        <v>-294.85</v>
+        <v>-129.97</v>
       </c>
       <c r="L54" t="n">
-        <v>1017.19</v>
+        <v>448.36</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-860.24</v>
+        <v>-368.33</v>
       </c>
       <c r="K55" t="n">
-        <v>-586.45</v>
+        <v>-251.1</v>
       </c>
       <c r="L55" t="n">
-        <v>1041.12</v>
+        <v>445.78</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-708.01</v>
+        <v>-277.27</v>
       </c>
       <c r="K56" t="n">
-        <v>-1729.58</v>
+        <v>-677.33</v>
       </c>
       <c r="L56" t="n">
-        <v>1868.88</v>
+        <v>731.89</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>824.1</v>
+        <v>326.85</v>
       </c>
       <c r="K57" t="n">
-        <v>500.92</v>
+        <v>198.67</v>
       </c>
       <c r="L57" t="n">
-        <v>964.4</v>
+        <v>382.5</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-813.11</v>
+        <v>-325.88</v>
       </c>
       <c r="K58" t="n">
-        <v>-1213.23</v>
+        <v>-486.23</v>
       </c>
       <c r="L58" t="n">
-        <v>1460.51</v>
+        <v>585.33</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-210.83</v>
+        <v>-130.36</v>
       </c>
       <c r="K59" t="n">
-        <v>237.08</v>
+        <v>146.59</v>
       </c>
       <c r="L59" t="n">
-        <v>317.26</v>
+        <v>196.17</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>139.79</v>
+        <v>79.39</v>
       </c>
       <c r="K60" t="n">
-        <v>-517.59</v>
+        <v>-293.94</v>
       </c>
       <c r="L60" t="n">
-        <v>536.13</v>
+        <v>304.47</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-357.41</v>
+        <v>-217.49</v>
       </c>
       <c r="K61" t="n">
-        <v>-102.96</v>
+        <v>-62.65</v>
       </c>
       <c r="L61" t="n">
-        <v>371.95</v>
+        <v>226.33</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>452.29</v>
+        <v>261.73</v>
       </c>
       <c r="K62" t="n">
-        <v>-359.41</v>
+        <v>-207.99</v>
       </c>
       <c r="L62" t="n">
-        <v>577.7</v>
+        <v>334.31</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-208.07</v>
+        <v>-124.79</v>
       </c>
       <c r="K63" t="n">
-        <v>303.11</v>
+        <v>181.78</v>
       </c>
       <c r="L63" t="n">
-        <v>367.65</v>
+        <v>220.49</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-288.81</v>
+        <v>-168.87</v>
       </c>
       <c r="K64" t="n">
-        <v>214.35</v>
+        <v>125.33</v>
       </c>
       <c r="L64" t="n">
-        <v>359.66</v>
+        <v>210.3</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-422.19</v>
+        <v>-217</v>
       </c>
       <c r="K65" t="n">
-        <v>-732.88</v>
+        <v>-376.69</v>
       </c>
       <c r="L65" t="n">
-        <v>845.79</v>
+        <v>434.72</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>198.61</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>-659.24</v>
+        <v>-318.63</v>
       </c>
       <c r="L66" t="n">
-        <v>688.51</v>
+        <v>332.77</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>1093.54</v>
+        <v>541.8200000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-232.55</v>
+        <v>-115.22</v>
       </c>
       <c r="L67" t="n">
-        <v>1117.99</v>
+        <v>553.9299999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>281.46</v>
+        <v>133.09</v>
       </c>
       <c r="K68" t="n">
-        <v>-916.77</v>
+        <v>-433.51</v>
       </c>
       <c r="L68" t="n">
-        <v>959.01</v>
+        <v>453.48</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>-870.25</v>
+        <v>-381.87</v>
       </c>
       <c r="K69" t="n">
-        <v>-1312.31</v>
+        <v>-575.85</v>
       </c>
       <c r="L69" t="n">
-        <v>1574.64</v>
+        <v>690.96</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>718.42</v>
+        <v>309.44</v>
       </c>
       <c r="K70" t="n">
-        <v>144.99</v>
+        <v>62.45</v>
       </c>
       <c r="L70" t="n">
-        <v>732.91</v>
+        <v>315.68</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-503.13</v>
+        <v>-213.53</v>
       </c>
       <c r="K71" t="n">
-        <v>-537.16</v>
+        <v>-227.98</v>
       </c>
       <c r="L71" t="n">
-        <v>735.99</v>
+        <v>312.36</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>285.5</v>
+        <v>113.72</v>
       </c>
       <c r="K72" t="n">
-        <v>-1020.77</v>
+        <v>-406.6</v>
       </c>
       <c r="L72" t="n">
-        <v>1059.94</v>
+        <v>422.2</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>925.66</v>
+        <v>367.03</v>
       </c>
       <c r="K73" t="n">
-        <v>455.16</v>
+        <v>180.47</v>
       </c>
       <c r="L73" t="n">
-        <v>1031.52</v>
+        <v>409</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-233.69</v>
+        <v>-133.9</v>
       </c>
       <c r="K74" t="n">
-        <v>-238.31</v>
+        <v>-136.55</v>
       </c>
       <c r="L74" t="n">
-        <v>333.77</v>
+        <v>191.25</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-315.82</v>
+        <v>-182.35</v>
       </c>
       <c r="K75" t="n">
-        <v>-313.89</v>
+        <v>-181.24</v>
       </c>
       <c r="L75" t="n">
-        <v>445.28</v>
+        <v>257.1</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-306.54</v>
+        <v>-177.76</v>
       </c>
       <c r="K76" t="n">
-        <v>-299.26</v>
+        <v>-173.54</v>
       </c>
       <c r="L76" t="n">
-        <v>428.4</v>
+        <v>248.43</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-108.42</v>
+        <v>-60.08</v>
       </c>
       <c r="K77" t="n">
-        <v>-620.51</v>
+        <v>-343.82</v>
       </c>
       <c r="L77" t="n">
-        <v>629.91</v>
+        <v>349.03</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-602.27</v>
+        <v>-340.55</v>
       </c>
       <c r="K78" t="n">
-        <v>-411.87</v>
+        <v>-232.88</v>
       </c>
       <c r="L78" t="n">
-        <v>729.64</v>
+        <v>412.56</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>35.27</v>
+        <v>20.75</v>
       </c>
       <c r="K79" t="n">
-        <v>275.06</v>
+        <v>161.86</v>
       </c>
       <c r="L79" t="n">
-        <v>277.31</v>
+        <v>163.18</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-1002.7</v>
+        <v>-486.32</v>
       </c>
       <c r="K80" t="n">
-        <v>382.52</v>
+        <v>185.53</v>
       </c>
       <c r="L80" t="n">
-        <v>1073.19</v>
+        <v>520.51</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-252.06</v>
+        <v>-123.71</v>
       </c>
       <c r="K81" t="n">
-        <v>-645.63</v>
+        <v>-316.87</v>
       </c>
       <c r="L81" t="n">
-        <v>693.09</v>
+        <v>340.17</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-517.53</v>
+        <v>-262.61</v>
       </c>
       <c r="K82" t="n">
-        <v>386.48</v>
+        <v>196.11</v>
       </c>
       <c r="L82" t="n">
-        <v>645.91</v>
+        <v>327.76</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-1405.04</v>
+        <v>-600.64</v>
       </c>
       <c r="K83" t="n">
-        <v>-99.78</v>
+        <v>-42.65</v>
       </c>
       <c r="L83" t="n">
-        <v>1408.58</v>
+        <v>602.15</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>1029.18</v>
+        <v>444.29</v>
       </c>
       <c r="K84" t="n">
-        <v>-142.15</v>
+        <v>-61.37</v>
       </c>
       <c r="L84" t="n">
-        <v>1038.95</v>
+        <v>448.51</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>1328.01</v>
+        <v>569.55</v>
       </c>
       <c r="K85" t="n">
-        <v>499.75</v>
+        <v>214.33</v>
       </c>
       <c r="L85" t="n">
-        <v>1418.93</v>
+        <v>608.54</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-778.13</v>
+        <v>-303.37</v>
       </c>
       <c r="K86" t="n">
-        <v>-1527.47</v>
+        <v>-595.52</v>
       </c>
       <c r="L86" t="n">
-        <v>1714.25</v>
+        <v>668.34</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>-22.99</v>
+        <v>-9.6</v>
       </c>
       <c r="K87" t="n">
-        <v>-1232.43</v>
+        <v>-514.38</v>
       </c>
       <c r="L87" t="n">
-        <v>1232.64</v>
+        <v>514.47</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-1209.59</v>
+        <v>-499.11</v>
       </c>
       <c r="K88" t="n">
-        <v>-515.3200000000001</v>
+        <v>-212.63</v>
       </c>
       <c r="L88" t="n">
-        <v>1314.79</v>
+        <v>542.51</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-01.xlsx
+++ b/output/2024-04-01.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-56.23</v>
+        <v>-62.4</v>
       </c>
       <c r="K14" t="n">
-        <v>-134.69</v>
+        <v>-149.47</v>
       </c>
       <c r="L14" t="n">
-        <v>145.95</v>
+        <v>161.97</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-66.17</v>
+        <v>-73.55</v>
       </c>
       <c r="K15" t="n">
-        <v>116.24</v>
+        <v>129.2</v>
       </c>
       <c r="L15" t="n">
-        <v>133.76</v>
+        <v>148.66</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-203.36</v>
+        <v>-227.85</v>
       </c>
       <c r="K16" t="n">
-        <v>-153.72</v>
+        <v>-172.23</v>
       </c>
       <c r="L16" t="n">
-        <v>254.92</v>
+        <v>285.62</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>92.8</v>
+        <v>103.49</v>
       </c>
       <c r="K17" t="n">
-        <v>221.72</v>
+        <v>247.27</v>
       </c>
       <c r="L17" t="n">
-        <v>240.36</v>
+        <v>268.06</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>50.6</v>
+        <v>55.89</v>
       </c>
       <c r="K18" t="n">
-        <v>104.77</v>
+        <v>115.71</v>
       </c>
       <c r="L18" t="n">
-        <v>116.35</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>258.06</v>
+        <v>289.43</v>
       </c>
       <c r="K19" t="n">
-        <v>-169.9</v>
+        <v>-190.55</v>
       </c>
       <c r="L19" t="n">
-        <v>308.97</v>
+        <v>346.52</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>256.2</v>
+        <v>293.43</v>
       </c>
       <c r="K20" t="n">
-        <v>-46.32</v>
+        <v>-53.05</v>
       </c>
       <c r="L20" t="n">
-        <v>260.35</v>
+        <v>298.18</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-243.54</v>
+        <v>-280.69</v>
       </c>
       <c r="K21" t="n">
-        <v>-97.69</v>
+        <v>-112.6</v>
       </c>
       <c r="L21" t="n">
-        <v>262.4</v>
+        <v>302.43</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-164.22</v>
+        <v>-189.58</v>
       </c>
       <c r="K22" t="n">
-        <v>-108.62</v>
+        <v>-125.39</v>
       </c>
       <c r="L22" t="n">
-        <v>196.9</v>
+        <v>227.3</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>209.33</v>
+        <v>249.55</v>
       </c>
       <c r="K23" t="n">
-        <v>-73.45</v>
+        <v>-87.56</v>
       </c>
       <c r="L23" t="n">
-        <v>221.85</v>
+        <v>264.47</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>129.52</v>
+        <v>155.21</v>
       </c>
       <c r="K24" t="n">
-        <v>-328.29</v>
+        <v>-393.41</v>
       </c>
       <c r="L24" t="n">
-        <v>352.91</v>
+        <v>422.92</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-312.67</v>
+        <v>-374.27</v>
       </c>
       <c r="K25" t="n">
-        <v>-181.54</v>
+        <v>-217.3</v>
       </c>
       <c r="L25" t="n">
-        <v>361.55</v>
+        <v>432.78</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>421.77</v>
+        <v>516.83</v>
       </c>
       <c r="K26" t="n">
-        <v>-816.5</v>
+        <v>-1000.51</v>
       </c>
       <c r="L26" t="n">
-        <v>919</v>
+        <v>1126.11</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-510.19</v>
+        <v>-626.37</v>
       </c>
       <c r="K27" t="n">
-        <v>215.33</v>
+        <v>264.36</v>
       </c>
       <c r="L27" t="n">
-        <v>553.77</v>
+        <v>679.88</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>545.6900000000001</v>
+        <v>667.29</v>
       </c>
       <c r="K28" t="n">
-        <v>300.05</v>
+        <v>366.92</v>
       </c>
       <c r="L28" t="n">
-        <v>622.74</v>
+        <v>761.51</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>155.74</v>
+        <v>174.38</v>
       </c>
       <c r="K29" t="n">
-        <v>-191.73</v>
+        <v>-214.68</v>
       </c>
       <c r="L29" t="n">
-        <v>247.01</v>
+        <v>276.58</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>110.82</v>
+        <v>123.33</v>
       </c>
       <c r="K30" t="n">
-        <v>-247.43</v>
+        <v>-275.34</v>
       </c>
       <c r="L30" t="n">
-        <v>271.11</v>
+        <v>301.7</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>4.32</v>
+        <v>4.85</v>
       </c>
       <c r="K31" t="n">
-        <v>-207.92</v>
+        <v>-233.13</v>
       </c>
       <c r="L31" t="n">
-        <v>207.97</v>
+        <v>233.18</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>124.82</v>
+        <v>137.51</v>
       </c>
       <c r="K32" t="n">
-        <v>7.11</v>
+        <v>7.83</v>
       </c>
       <c r="L32" t="n">
-        <v>125.02</v>
+        <v>137.73</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>85.08</v>
+        <v>94.8</v>
       </c>
       <c r="K33" t="n">
-        <v>187.02</v>
+        <v>208.39</v>
       </c>
       <c r="L33" t="n">
-        <v>205.46</v>
+        <v>228.94</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-186.38</v>
+        <v>-207.97</v>
       </c>
       <c r="K34" t="n">
-        <v>-43.91</v>
+        <v>-49</v>
       </c>
       <c r="L34" t="n">
-        <v>191.48</v>
+        <v>213.66</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-243.93</v>
+        <v>-281.48</v>
       </c>
       <c r="K35" t="n">
-        <v>23.99</v>
+        <v>27.69</v>
       </c>
       <c r="L35" t="n">
-        <v>245.11</v>
+        <v>282.84</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>458.47</v>
+        <v>529.24</v>
       </c>
       <c r="K36" t="n">
-        <v>-66.40000000000001</v>
+        <v>-76.65000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>463.25</v>
+        <v>534.76</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-296.4</v>
+        <v>-344.1</v>
       </c>
       <c r="K37" t="n">
-        <v>-162.48</v>
+        <v>-188.63</v>
       </c>
       <c r="L37" t="n">
-        <v>338.01</v>
+        <v>392.41</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-237.83</v>
+        <v>-283.1</v>
       </c>
       <c r="K38" t="n">
-        <v>141.03</v>
+        <v>167.87</v>
       </c>
       <c r="L38" t="n">
-        <v>276.5</v>
+        <v>329.13</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-309.07</v>
+        <v>-368.84</v>
       </c>
       <c r="K39" t="n">
-        <v>-154.04</v>
+        <v>-183.84</v>
       </c>
       <c r="L39" t="n">
-        <v>345.33</v>
+        <v>412.12</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>249.08</v>
+        <v>295.58</v>
       </c>
       <c r="K40" t="n">
-        <v>-680.89</v>
+        <v>-808.01</v>
       </c>
       <c r="L40" t="n">
-        <v>725.02</v>
+        <v>860.38</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>345.63</v>
+        <v>422.58</v>
       </c>
       <c r="K41" t="n">
-        <v>366.87</v>
+        <v>448.55</v>
       </c>
       <c r="L41" t="n">
-        <v>504.04</v>
+        <v>616.26</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-219.77</v>
+        <v>-267.03</v>
       </c>
       <c r="K42" t="n">
-        <v>-568.05</v>
+        <v>-690.22</v>
       </c>
       <c r="L42" t="n">
-        <v>609.08</v>
+        <v>740.0700000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>264.94</v>
+        <v>328.82</v>
       </c>
       <c r="K43" t="n">
-        <v>-193.61</v>
+        <v>-240.3</v>
       </c>
       <c r="L43" t="n">
-        <v>328.14</v>
+        <v>407.27</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>105.08</v>
+        <v>115.34</v>
       </c>
       <c r="K44" t="n">
-        <v>-54.59</v>
+        <v>-59.92</v>
       </c>
       <c r="L44" t="n">
-        <v>118.41</v>
+        <v>129.98</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>205.46</v>
+        <v>229.19</v>
       </c>
       <c r="K45" t="n">
-        <v>63.29</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>214.99</v>
+        <v>239.82</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>168.23</v>
+        <v>187.28</v>
       </c>
       <c r="K46" t="n">
-        <v>-139.48</v>
+        <v>-155.28</v>
       </c>
       <c r="L46" t="n">
-        <v>218.53</v>
+        <v>243.28</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-133.14</v>
+        <v>-146.65</v>
       </c>
       <c r="K47" t="n">
-        <v>-105.77</v>
+        <v>-116.51</v>
       </c>
       <c r="L47" t="n">
-        <v>170.04</v>
+        <v>187.3</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>60.06</v>
+        <v>67.25</v>
       </c>
       <c r="K48" t="n">
-        <v>188.19</v>
+        <v>210.71</v>
       </c>
       <c r="L48" t="n">
-        <v>197.55</v>
+        <v>221.18</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>19.75</v>
+        <v>22.07</v>
       </c>
       <c r="K49" t="n">
-        <v>162.72</v>
+        <v>181.8</v>
       </c>
       <c r="L49" t="n">
-        <v>163.91</v>
+        <v>183.14</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>184.51</v>
+        <v>213.22</v>
       </c>
       <c r="K50" t="n">
-        <v>167.99</v>
+        <v>194.12</v>
       </c>
       <c r="L50" t="n">
-        <v>249.53</v>
+        <v>288.35</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-75.95999999999999</v>
+        <v>-88.34999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-471.13</v>
+        <v>-547.97</v>
       </c>
       <c r="L51" t="n">
-        <v>477.22</v>
+        <v>555.04</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-98.3</v>
+        <v>-114.6</v>
       </c>
       <c r="K52" t="n">
-        <v>417.25</v>
+        <v>486.44</v>
       </c>
       <c r="L52" t="n">
-        <v>428.67</v>
+        <v>499.76</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>391.25</v>
+        <v>458.76</v>
       </c>
       <c r="K53" t="n">
-        <v>72.73</v>
+        <v>85.28</v>
       </c>
       <c r="L53" t="n">
-        <v>397.95</v>
+        <v>466.62</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>429.11</v>
+        <v>511.44</v>
       </c>
       <c r="K54" t="n">
-        <v>-129.97</v>
+        <v>-154.9</v>
       </c>
       <c r="L54" t="n">
-        <v>448.36</v>
+        <v>534.39</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-368.33</v>
+        <v>-438.26</v>
       </c>
       <c r="K55" t="n">
-        <v>-251.1</v>
+        <v>-298.77</v>
       </c>
       <c r="L55" t="n">
-        <v>445.78</v>
+        <v>530.41</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-277.27</v>
+        <v>-339.16</v>
       </c>
       <c r="K56" t="n">
-        <v>-677.33</v>
+        <v>-828.52</v>
       </c>
       <c r="L56" t="n">
-        <v>731.89</v>
+        <v>895.25</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>326.85</v>
+        <v>400.35</v>
       </c>
       <c r="K57" t="n">
-        <v>198.67</v>
+        <v>243.35</v>
       </c>
       <c r="L57" t="n">
-        <v>382.5</v>
+        <v>468.51</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-325.88</v>
+        <v>-396.43</v>
       </c>
       <c r="K58" t="n">
-        <v>-486.23</v>
+        <v>-591.5</v>
       </c>
       <c r="L58" t="n">
-        <v>585.33</v>
+        <v>712.05</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-130.36</v>
+        <v>-143.16</v>
       </c>
       <c r="K59" t="n">
-        <v>146.59</v>
+        <v>160.98</v>
       </c>
       <c r="L59" t="n">
-        <v>196.17</v>
+        <v>215.43</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>79.39</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>-293.94</v>
+        <v>-332.97</v>
       </c>
       <c r="L60" t="n">
-        <v>304.47</v>
+        <v>344.9</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-217.49</v>
+        <v>-243.12</v>
       </c>
       <c r="K61" t="n">
-        <v>-62.65</v>
+        <v>-70.04000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>226.33</v>
+        <v>253</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>261.73</v>
+        <v>294.1</v>
       </c>
       <c r="K62" t="n">
-        <v>-207.99</v>
+        <v>-233.7</v>
       </c>
       <c r="L62" t="n">
-        <v>334.31</v>
+        <v>375.65</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-124.79</v>
+        <v>-137.96</v>
       </c>
       <c r="K63" t="n">
-        <v>181.78</v>
+        <v>200.97</v>
       </c>
       <c r="L63" t="n">
-        <v>220.49</v>
+        <v>243.77</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-168.87</v>
+        <v>-188.42</v>
       </c>
       <c r="K64" t="n">
-        <v>125.33</v>
+        <v>139.84</v>
       </c>
       <c r="L64" t="n">
-        <v>210.3</v>
+        <v>234.64</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-217</v>
+        <v>-247.42</v>
       </c>
       <c r="K65" t="n">
-        <v>-376.69</v>
+        <v>-429.5</v>
       </c>
       <c r="L65" t="n">
-        <v>434.72</v>
+        <v>495.67</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>95.98999999999999</v>
+        <v>111.02</v>
       </c>
       <c r="K66" t="n">
-        <v>-318.63</v>
+        <v>-368.5</v>
       </c>
       <c r="L66" t="n">
-        <v>332.77</v>
+        <v>384.86</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>541.8200000000001</v>
+        <v>630.77</v>
       </c>
       <c r="K67" t="n">
-        <v>-115.22</v>
+        <v>-134.14</v>
       </c>
       <c r="L67" t="n">
-        <v>553.9299999999999</v>
+        <v>644.87</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>133.09</v>
+        <v>157.08</v>
       </c>
       <c r="K68" t="n">
-        <v>-433.51</v>
+        <v>-511.65</v>
       </c>
       <c r="L68" t="n">
-        <v>453.48</v>
+        <v>535.22</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>-381.87</v>
+        <v>-451.71</v>
       </c>
       <c r="K69" t="n">
-        <v>-575.85</v>
+        <v>-681.16</v>
       </c>
       <c r="L69" t="n">
-        <v>690.96</v>
+        <v>817.3200000000001</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>309.44</v>
+        <v>372.08</v>
       </c>
       <c r="K70" t="n">
-        <v>62.45</v>
+        <v>75.09</v>
       </c>
       <c r="L70" t="n">
-        <v>315.68</v>
+        <v>379.58</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-213.53</v>
+        <v>-257.75</v>
       </c>
       <c r="K71" t="n">
-        <v>-227.98</v>
+        <v>-275.19</v>
       </c>
       <c r="L71" t="n">
-        <v>312.36</v>
+        <v>377.05</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>113.72</v>
+        <v>140.11</v>
       </c>
       <c r="K72" t="n">
-        <v>-406.6</v>
+        <v>-500.94</v>
       </c>
       <c r="L72" t="n">
-        <v>422.2</v>
+        <v>520.17</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>367.03</v>
+        <v>455.67</v>
       </c>
       <c r="K73" t="n">
-        <v>180.47</v>
+        <v>224.06</v>
       </c>
       <c r="L73" t="n">
-        <v>409</v>
+        <v>507.78</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-133.9</v>
+        <v>-150.36</v>
       </c>
       <c r="K74" t="n">
-        <v>-136.55</v>
+        <v>-153.33</v>
       </c>
       <c r="L74" t="n">
-        <v>191.25</v>
+        <v>214.75</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-182.35</v>
+        <v>-202.16</v>
       </c>
       <c r="K75" t="n">
-        <v>-181.24</v>
+        <v>-200.92</v>
       </c>
       <c r="L75" t="n">
-        <v>257.1</v>
+        <v>285.02</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-177.76</v>
+        <v>-198.82</v>
       </c>
       <c r="K76" t="n">
-        <v>-173.54</v>
+        <v>-194.1</v>
       </c>
       <c r="L76" t="n">
-        <v>248.43</v>
+        <v>277.85</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-60.08</v>
+        <v>-67.53</v>
       </c>
       <c r="K77" t="n">
-        <v>-343.82</v>
+        <v>-386.46</v>
       </c>
       <c r="L77" t="n">
-        <v>349.03</v>
+        <v>392.32</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-340.55</v>
+        <v>-379.49</v>
       </c>
       <c r="K78" t="n">
-        <v>-232.88</v>
+        <v>-259.52</v>
       </c>
       <c r="L78" t="n">
-        <v>412.56</v>
+        <v>459.74</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>20.75</v>
+        <v>23.13</v>
       </c>
       <c r="K79" t="n">
-        <v>161.86</v>
+        <v>180.44</v>
       </c>
       <c r="L79" t="n">
-        <v>163.18</v>
+        <v>181.91</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-486.32</v>
+        <v>-564.74</v>
       </c>
       <c r="K80" t="n">
-        <v>185.53</v>
+        <v>215.44</v>
       </c>
       <c r="L80" t="n">
-        <v>520.51</v>
+        <v>604.4400000000001</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-123.71</v>
+        <v>-143.06</v>
       </c>
       <c r="K81" t="n">
-        <v>-316.87</v>
+        <v>-366.44</v>
       </c>
       <c r="L81" t="n">
-        <v>340.17</v>
+        <v>393.37</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-262.61</v>
+        <v>-300.68</v>
       </c>
       <c r="K82" t="n">
-        <v>196.11</v>
+        <v>224.54</v>
       </c>
       <c r="L82" t="n">
-        <v>327.76</v>
+        <v>375.27</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-600.64</v>
+        <v>-716.26</v>
       </c>
       <c r="K83" t="n">
-        <v>-42.65</v>
+        <v>-50.87</v>
       </c>
       <c r="L83" t="n">
-        <v>602.15</v>
+        <v>718.0599999999999</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>444.29</v>
+        <v>534.03</v>
       </c>
       <c r="K84" t="n">
-        <v>-61.37</v>
+        <v>-73.76000000000001</v>
       </c>
       <c r="L84" t="n">
-        <v>448.51</v>
+        <v>539.1</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>569.55</v>
+        <v>677.6900000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>214.33</v>
+        <v>255.03</v>
       </c>
       <c r="L85" t="n">
-        <v>608.54</v>
+        <v>724.08</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-303.37</v>
+        <v>-369.19</v>
       </c>
       <c r="K86" t="n">
-        <v>-595.52</v>
+        <v>-724.71</v>
       </c>
       <c r="L86" t="n">
-        <v>668.34</v>
+        <v>813.33</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>-9.6</v>
+        <v>-11.5</v>
       </c>
       <c r="K87" t="n">
-        <v>-514.38</v>
+        <v>-616.64</v>
       </c>
       <c r="L87" t="n">
-        <v>514.47</v>
+        <v>616.74</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-499.11</v>
+        <v>-606.4</v>
       </c>
       <c r="K88" t="n">
-        <v>-212.63</v>
+        <v>-258.34</v>
       </c>
       <c r="L88" t="n">
-        <v>542.51</v>
+        <v>659.14</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-01.xlsx
+++ b/output/2024-04-01.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-62.4</v>
+        <v>-25.06</v>
       </c>
       <c r="K14" t="n">
-        <v>-149.47</v>
+        <v>-60.03</v>
       </c>
       <c r="L14" t="n">
-        <v>161.97</v>
+        <v>65.05</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-73.55</v>
+        <v>-29.52</v>
       </c>
       <c r="K15" t="n">
-        <v>129.2</v>
+        <v>51.86</v>
       </c>
       <c r="L15" t="n">
-        <v>148.66</v>
+        <v>59.67</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-227.85</v>
+        <v>-91.44</v>
       </c>
       <c r="K16" t="n">
-        <v>-172.23</v>
+        <v>-69.12</v>
       </c>
       <c r="L16" t="n">
-        <v>285.62</v>
+        <v>114.63</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>103.49</v>
+        <v>44.15</v>
       </c>
       <c r="K17" t="n">
-        <v>247.27</v>
+        <v>105.49</v>
       </c>
       <c r="L17" t="n">
-        <v>268.06</v>
+        <v>114.36</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>55.89</v>
+        <v>16.55</v>
       </c>
       <c r="K18" t="n">
-        <v>115.71</v>
+        <v>34.26</v>
       </c>
       <c r="L18" t="n">
-        <v>128.5</v>
+        <v>38.05</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>289.43</v>
+        <v>124.44</v>
       </c>
       <c r="K19" t="n">
-        <v>-190.55</v>
+        <v>-81.93000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>346.52</v>
+        <v>148.99</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>293.43</v>
+        <v>141.65</v>
       </c>
       <c r="K20" t="n">
-        <v>-53.05</v>
+        <v>-25.61</v>
       </c>
       <c r="L20" t="n">
-        <v>298.18</v>
+        <v>143.95</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-280.69</v>
+        <v>-138.15</v>
       </c>
       <c r="K21" t="n">
-        <v>-112.6</v>
+        <v>-55.42</v>
       </c>
       <c r="L21" t="n">
-        <v>302.43</v>
+        <v>148.85</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-189.58</v>
+        <v>-90.52</v>
       </c>
       <c r="K22" t="n">
-        <v>-125.39</v>
+        <v>-59.87</v>
       </c>
       <c r="L22" t="n">
-        <v>227.3</v>
+        <v>108.53</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>249.55</v>
+        <v>111.5</v>
       </c>
       <c r="K23" t="n">
-        <v>-87.56</v>
+        <v>-39.12</v>
       </c>
       <c r="L23" t="n">
-        <v>264.47</v>
+        <v>118.16</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>155.21</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>-393.41</v>
+        <v>-171.7</v>
       </c>
       <c r="L24" t="n">
-        <v>422.92</v>
+        <v>184.58</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-374.27</v>
+        <v>-173.12</v>
       </c>
       <c r="K25" t="n">
-        <v>-217.3</v>
+        <v>-100.51</v>
       </c>
       <c r="L25" t="n">
-        <v>432.78</v>
+        <v>200.18</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>516.83</v>
+        <v>274.51</v>
       </c>
       <c r="K26" t="n">
-        <v>-1000.51</v>
+        <v>-531.42</v>
       </c>
       <c r="L26" t="n">
-        <v>1126.11</v>
+        <v>598.14</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-626.37</v>
+        <v>-330.71</v>
       </c>
       <c r="K27" t="n">
-        <v>264.36</v>
+        <v>139.58</v>
       </c>
       <c r="L27" t="n">
-        <v>679.88</v>
+        <v>358.96</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>667.29</v>
+        <v>352.72</v>
       </c>
       <c r="K28" t="n">
-        <v>366.92</v>
+        <v>193.94</v>
       </c>
       <c r="L28" t="n">
-        <v>761.51</v>
+        <v>402.52</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>174.38</v>
+        <v>69.77</v>
       </c>
       <c r="K29" t="n">
-        <v>-214.68</v>
+        <v>-85.89</v>
       </c>
       <c r="L29" t="n">
-        <v>276.58</v>
+        <v>110.66</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>123.33</v>
+        <v>49.5</v>
       </c>
       <c r="K30" t="n">
-        <v>-275.34</v>
+        <v>-110.53</v>
       </c>
       <c r="L30" t="n">
-        <v>301.7</v>
+        <v>121.11</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>4.85</v>
+        <v>1.93</v>
       </c>
       <c r="K31" t="n">
-        <v>-233.13</v>
+        <v>-92.88</v>
       </c>
       <c r="L31" t="n">
-        <v>233.18</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>137.51</v>
+        <v>57.61</v>
       </c>
       <c r="K32" t="n">
-        <v>7.83</v>
+        <v>3.28</v>
       </c>
       <c r="L32" t="n">
-        <v>137.73</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>94.8</v>
+        <v>39.92</v>
       </c>
       <c r="K33" t="n">
-        <v>208.39</v>
+        <v>87.75</v>
       </c>
       <c r="L33" t="n">
-        <v>228.94</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-207.97</v>
+        <v>-86.43000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-49</v>
+        <v>-20.36</v>
       </c>
       <c r="L34" t="n">
-        <v>213.66</v>
+        <v>88.79000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-281.48</v>
+        <v>-134.41</v>
       </c>
       <c r="K35" t="n">
-        <v>27.69</v>
+        <v>13.22</v>
       </c>
       <c r="L35" t="n">
-        <v>282.84</v>
+        <v>135.06</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>529.24</v>
+        <v>252.99</v>
       </c>
       <c r="K36" t="n">
-        <v>-76.65000000000001</v>
+        <v>-36.64</v>
       </c>
       <c r="L36" t="n">
-        <v>534.76</v>
+        <v>255.63</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-344.1</v>
+        <v>-168.06</v>
       </c>
       <c r="K37" t="n">
-        <v>-188.63</v>
+        <v>-92.13</v>
       </c>
       <c r="L37" t="n">
-        <v>392.41</v>
+        <v>191.66</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-283.1</v>
+        <v>-126.51</v>
       </c>
       <c r="K38" t="n">
-        <v>167.87</v>
+        <v>75.02</v>
       </c>
       <c r="L38" t="n">
-        <v>329.13</v>
+        <v>147.08</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-368.84</v>
+        <v>-165.82</v>
       </c>
       <c r="K39" t="n">
-        <v>-183.84</v>
+        <v>-82.65000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>412.12</v>
+        <v>185.28</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>295.58</v>
+        <v>131.48</v>
       </c>
       <c r="K40" t="n">
-        <v>-808.01</v>
+        <v>-359.43</v>
       </c>
       <c r="L40" t="n">
-        <v>860.38</v>
+        <v>382.72</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>422.58</v>
+        <v>224.67</v>
       </c>
       <c r="K41" t="n">
-        <v>448.55</v>
+        <v>238.49</v>
       </c>
       <c r="L41" t="n">
-        <v>616.26</v>
+        <v>327.65</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-267.03</v>
+        <v>-142.41</v>
       </c>
       <c r="K42" t="n">
-        <v>-690.22</v>
+        <v>-368.09</v>
       </c>
       <c r="L42" t="n">
-        <v>740.0700000000001</v>
+        <v>394.67</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>328.82</v>
+        <v>173.68</v>
       </c>
       <c r="K43" t="n">
-        <v>-240.3</v>
+        <v>-126.92</v>
       </c>
       <c r="L43" t="n">
-        <v>407.27</v>
+        <v>215.11</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>115.34</v>
+        <v>48.44</v>
       </c>
       <c r="K44" t="n">
-        <v>-59.92</v>
+        <v>-25.16</v>
       </c>
       <c r="L44" t="n">
-        <v>129.98</v>
+        <v>54.59</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>229.19</v>
+        <v>92.14</v>
       </c>
       <c r="K45" t="n">
-        <v>70.59999999999999</v>
+        <v>28.38</v>
       </c>
       <c r="L45" t="n">
-        <v>239.82</v>
+        <v>96.41</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>187.28</v>
+        <v>75</v>
       </c>
       <c r="K46" t="n">
-        <v>-155.28</v>
+        <v>-62.18</v>
       </c>
       <c r="L46" t="n">
-        <v>243.28</v>
+        <v>97.42</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-146.65</v>
+        <v>-62.24</v>
       </c>
       <c r="K47" t="n">
-        <v>-116.51</v>
+        <v>-49.44</v>
       </c>
       <c r="L47" t="n">
-        <v>187.3</v>
+        <v>79.48</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>67.25</v>
+        <v>29.15</v>
       </c>
       <c r="K48" t="n">
-        <v>210.71</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>221.18</v>
+        <v>95.86</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>22.07</v>
+        <v>9.27</v>
       </c>
       <c r="K49" t="n">
-        <v>181.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>183.14</v>
+        <v>76.95999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>213.22</v>
+        <v>101.9</v>
       </c>
       <c r="K50" t="n">
-        <v>194.12</v>
+        <v>92.77</v>
       </c>
       <c r="L50" t="n">
-        <v>288.35</v>
+        <v>137.8</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-88.34999999999999</v>
+        <v>-42.27</v>
       </c>
       <c r="K51" t="n">
-        <v>-547.97</v>
+        <v>-262.15</v>
       </c>
       <c r="L51" t="n">
-        <v>555.04</v>
+        <v>265.54</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-114.6</v>
+        <v>-54.93</v>
       </c>
       <c r="K52" t="n">
-        <v>486.44</v>
+        <v>233.18</v>
       </c>
       <c r="L52" t="n">
-        <v>499.76</v>
+        <v>239.57</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>458.76</v>
+        <v>207.56</v>
       </c>
       <c r="K53" t="n">
-        <v>85.28</v>
+        <v>38.58</v>
       </c>
       <c r="L53" t="n">
-        <v>466.62</v>
+        <v>211.11</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>511.44</v>
+        <v>232.68</v>
       </c>
       <c r="K54" t="n">
-        <v>-154.9</v>
+        <v>-70.47</v>
       </c>
       <c r="L54" t="n">
-        <v>534.39</v>
+        <v>243.12</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-438.26</v>
+        <v>-202.13</v>
       </c>
       <c r="K55" t="n">
-        <v>-298.77</v>
+        <v>-137.8</v>
       </c>
       <c r="L55" t="n">
-        <v>530.41</v>
+        <v>244.63</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-339.16</v>
+        <v>-183.24</v>
       </c>
       <c r="K56" t="n">
-        <v>-828.52</v>
+        <v>-447.64</v>
       </c>
       <c r="L56" t="n">
-        <v>895.25</v>
+        <v>483.7</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>400.35</v>
+        <v>213.01</v>
       </c>
       <c r="K57" t="n">
-        <v>243.35</v>
+        <v>129.48</v>
       </c>
       <c r="L57" t="n">
-        <v>468.51</v>
+        <v>249.27</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-396.43</v>
+        <v>-214.13</v>
       </c>
       <c r="K58" t="n">
-        <v>-591.5</v>
+        <v>-319.49</v>
       </c>
       <c r="L58" t="n">
-        <v>712.05</v>
+        <v>384.61</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-143.16</v>
+        <v>-57</v>
       </c>
       <c r="K59" t="n">
-        <v>160.98</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>215.43</v>
+        <v>85.78</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>89.93000000000001</v>
+        <v>36.9</v>
       </c>
       <c r="K60" t="n">
-        <v>-332.97</v>
+        <v>-136.63</v>
       </c>
       <c r="L60" t="n">
-        <v>344.9</v>
+        <v>141.53</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-243.12</v>
+        <v>-98.04000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>-70.04000000000001</v>
+        <v>-28.24</v>
       </c>
       <c r="L61" t="n">
-        <v>253</v>
+        <v>102.03</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>294.1</v>
+        <v>123.12</v>
       </c>
       <c r="K62" t="n">
-        <v>-233.7</v>
+        <v>-97.84</v>
       </c>
       <c r="L62" t="n">
-        <v>375.65</v>
+        <v>157.26</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-137.96</v>
+        <v>-58.95</v>
       </c>
       <c r="K63" t="n">
-        <v>200.97</v>
+        <v>85.87</v>
       </c>
       <c r="L63" t="n">
-        <v>243.77</v>
+        <v>104.16</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-188.42</v>
+        <v>-80.5</v>
       </c>
       <c r="K64" t="n">
-        <v>139.84</v>
+        <v>59.75</v>
       </c>
       <c r="L64" t="n">
-        <v>234.64</v>
+        <v>100.25</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-247.42</v>
+        <v>-118.52</v>
       </c>
       <c r="K65" t="n">
-        <v>-429.5</v>
+        <v>-205.74</v>
       </c>
       <c r="L65" t="n">
-        <v>495.67</v>
+        <v>237.44</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>111.02</v>
+        <v>53.12</v>
       </c>
       <c r="K66" t="n">
-        <v>-368.5</v>
+        <v>-176.32</v>
       </c>
       <c r="L66" t="n">
-        <v>384.86</v>
+        <v>184.15</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>630.77</v>
+        <v>301.75</v>
       </c>
       <c r="K67" t="n">
-        <v>-134.14</v>
+        <v>-64.17</v>
       </c>
       <c r="L67" t="n">
-        <v>644.87</v>
+        <v>308.49</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>157.08</v>
+        <v>68.97</v>
       </c>
       <c r="K68" t="n">
-        <v>-511.65</v>
+        <v>-224.65</v>
       </c>
       <c r="L68" t="n">
-        <v>535.22</v>
+        <v>235</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>-451.71</v>
+        <v>-207.58</v>
       </c>
       <c r="K69" t="n">
-        <v>-681.16</v>
+        <v>-313.02</v>
       </c>
       <c r="L69" t="n">
-        <v>817.3200000000001</v>
+        <v>375.6</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>372.08</v>
+        <v>169.36</v>
       </c>
       <c r="K70" t="n">
-        <v>75.09</v>
+        <v>34.18</v>
       </c>
       <c r="L70" t="n">
-        <v>379.58</v>
+        <v>172.77</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-257.75</v>
+        <v>-137.9</v>
       </c>
       <c r="K71" t="n">
-        <v>-275.19</v>
+        <v>-147.23</v>
       </c>
       <c r="L71" t="n">
-        <v>377.05</v>
+        <v>201.72</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>140.11</v>
+        <v>74.16</v>
       </c>
       <c r="K72" t="n">
-        <v>-500.94</v>
+        <v>-265.15</v>
       </c>
       <c r="L72" t="n">
-        <v>520.17</v>
+        <v>275.33</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>455.67</v>
+        <v>242.52</v>
       </c>
       <c r="K73" t="n">
-        <v>224.06</v>
+        <v>119.25</v>
       </c>
       <c r="L73" t="n">
-        <v>507.78</v>
+        <v>270.26</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-150.36</v>
+        <v>-61.27</v>
       </c>
       <c r="K74" t="n">
-        <v>-153.33</v>
+        <v>-62.48</v>
       </c>
       <c r="L74" t="n">
-        <v>214.75</v>
+        <v>87.51000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-202.16</v>
+        <v>-81.89</v>
       </c>
       <c r="K75" t="n">
-        <v>-200.92</v>
+        <v>-81.38</v>
       </c>
       <c r="L75" t="n">
-        <v>285.02</v>
+        <v>115.45</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-198.82</v>
+        <v>-80.26000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>-194.1</v>
+        <v>-78.34999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>277.85</v>
+        <v>112.16</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-67.53</v>
+        <v>-29.14</v>
       </c>
       <c r="K77" t="n">
-        <v>-386.46</v>
+        <v>-166.79</v>
       </c>
       <c r="L77" t="n">
-        <v>392.32</v>
+        <v>169.32</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-379.49</v>
+        <v>-158.93</v>
       </c>
       <c r="K78" t="n">
-        <v>-259.52</v>
+        <v>-108.69</v>
       </c>
       <c r="L78" t="n">
-        <v>459.74</v>
+        <v>192.54</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>23.13</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>180.44</v>
+        <v>76.37</v>
       </c>
       <c r="L79" t="n">
-        <v>181.91</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-564.74</v>
+        <v>-270.12</v>
       </c>
       <c r="K80" t="n">
-        <v>215.44</v>
+        <v>103.05</v>
       </c>
       <c r="L80" t="n">
-        <v>604.4400000000001</v>
+        <v>289.1</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-143.06</v>
+        <v>-68.51000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>-366.44</v>
+        <v>-175.47</v>
       </c>
       <c r="L81" t="n">
-        <v>393.37</v>
+        <v>188.37</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-300.68</v>
+        <v>-143.84</v>
       </c>
       <c r="K82" t="n">
-        <v>224.54</v>
+        <v>107.42</v>
       </c>
       <c r="L82" t="n">
-        <v>375.27</v>
+        <v>179.52</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-716.26</v>
+        <v>-331.53</v>
       </c>
       <c r="K83" t="n">
-        <v>-50.87</v>
+        <v>-23.54</v>
       </c>
       <c r="L83" t="n">
-        <v>718.0599999999999</v>
+        <v>332.36</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>534.03</v>
+        <v>241.86</v>
       </c>
       <c r="K84" t="n">
-        <v>-73.76000000000001</v>
+        <v>-33.41</v>
       </c>
       <c r="L84" t="n">
-        <v>539.1</v>
+        <v>244.16</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>677.6900000000001</v>
+        <v>311.43</v>
       </c>
       <c r="K85" t="n">
-        <v>255.03</v>
+        <v>117.2</v>
       </c>
       <c r="L85" t="n">
-        <v>724.08</v>
+        <v>332.75</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-369.19</v>
+        <v>-200.56</v>
       </c>
       <c r="K86" t="n">
-        <v>-724.71</v>
+        <v>-393.69</v>
       </c>
       <c r="L86" t="n">
-        <v>813.33</v>
+        <v>441.83</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>-11.5</v>
+        <v>-6.28</v>
       </c>
       <c r="K87" t="n">
-        <v>-616.64</v>
+        <v>-336.69</v>
       </c>
       <c r="L87" t="n">
-        <v>616.74</v>
+        <v>336.75</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-606.4</v>
+        <v>-325.54</v>
       </c>
       <c r="K88" t="n">
-        <v>-258.34</v>
+        <v>-138.69</v>
       </c>
       <c r="L88" t="n">
-        <v>659.14</v>
+        <v>353.85</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-01.xlsx
+++ b/output/2024-04-01.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-25.06</v>
+        <v>-23.24</v>
       </c>
       <c r="K14" t="n">
-        <v>-60.03</v>
+        <v>-55.66</v>
       </c>
       <c r="L14" t="n">
-        <v>65.05</v>
+        <v>60.32</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-29.52</v>
+        <v>-27.91</v>
       </c>
       <c r="K15" t="n">
-        <v>51.86</v>
+        <v>49.03</v>
       </c>
       <c r="L15" t="n">
-        <v>59.67</v>
+        <v>56.41</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-91.44</v>
+        <v>-78.66</v>
       </c>
       <c r="K16" t="n">
-        <v>-69.12</v>
+        <v>-59.46</v>
       </c>
       <c r="L16" t="n">
-        <v>114.63</v>
+        <v>98.61</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>44.15</v>
+        <v>42.15</v>
       </c>
       <c r="K17" t="n">
-        <v>105.49</v>
+        <v>100.72</v>
       </c>
       <c r="L17" t="n">
-        <v>114.36</v>
+        <v>109.19</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>16.55</v>
+        <v>15.52</v>
       </c>
       <c r="K18" t="n">
-        <v>34.26</v>
+        <v>32.13</v>
       </c>
       <c r="L18" t="n">
-        <v>38.05</v>
+        <v>35.68</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>124.44</v>
+        <v>103.92</v>
       </c>
       <c r="K19" t="n">
-        <v>-81.93000000000001</v>
+        <v>-68.42</v>
       </c>
       <c r="L19" t="n">
-        <v>148.99</v>
+        <v>124.42</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>141.65</v>
+        <v>140.71</v>
       </c>
       <c r="K20" t="n">
-        <v>-25.61</v>
+        <v>-25.44</v>
       </c>
       <c r="L20" t="n">
-        <v>143.95</v>
+        <v>142.99</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-138.15</v>
+        <v>-136.89</v>
       </c>
       <c r="K21" t="n">
-        <v>-55.42</v>
+        <v>-54.91</v>
       </c>
       <c r="L21" t="n">
-        <v>148.85</v>
+        <v>147.49</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-90.52</v>
+        <v>-94.75</v>
       </c>
       <c r="K22" t="n">
-        <v>-59.87</v>
+        <v>-62.67</v>
       </c>
       <c r="L22" t="n">
-        <v>108.53</v>
+        <v>113.6</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>111.5</v>
+        <v>123.55</v>
       </c>
       <c r="K23" t="n">
-        <v>-39.12</v>
+        <v>-43.35</v>
       </c>
       <c r="L23" t="n">
-        <v>118.16</v>
+        <v>130.93</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>67.73999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-171.7</v>
+        <v>-184.79</v>
       </c>
       <c r="L24" t="n">
-        <v>184.58</v>
+        <v>198.65</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-173.12</v>
+        <v>-174.58</v>
       </c>
       <c r="K25" t="n">
-        <v>-100.51</v>
+        <v>-101.36</v>
       </c>
       <c r="L25" t="n">
-        <v>200.18</v>
+        <v>201.87</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>274.51</v>
+        <v>294.54</v>
       </c>
       <c r="K26" t="n">
-        <v>-531.42</v>
+        <v>-570.1900000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>598.14</v>
+        <v>641.78</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-330.71</v>
+        <v>-365.8</v>
       </c>
       <c r="K27" t="n">
-        <v>139.58</v>
+        <v>154.38</v>
       </c>
       <c r="L27" t="n">
-        <v>358.96</v>
+        <v>397.04</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>352.72</v>
+        <v>383.68</v>
       </c>
       <c r="K28" t="n">
-        <v>193.94</v>
+        <v>210.97</v>
       </c>
       <c r="L28" t="n">
-        <v>402.52</v>
+        <v>437.86</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>69.77</v>
+        <v>61.55</v>
       </c>
       <c r="K29" t="n">
-        <v>-85.89</v>
+        <v>-75.77</v>
       </c>
       <c r="L29" t="n">
-        <v>110.66</v>
+        <v>97.62</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>49.5</v>
+        <v>42.08</v>
       </c>
       <c r="K30" t="n">
-        <v>-110.53</v>
+        <v>-93.95</v>
       </c>
       <c r="L30" t="n">
-        <v>121.11</v>
+        <v>102.94</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="K31" t="n">
-        <v>-92.88</v>
+        <v>-86.31999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>92.90000000000001</v>
+        <v>86.34</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>57.61</v>
+        <v>60.49</v>
       </c>
       <c r="K32" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="L32" t="n">
-        <v>57.7</v>
+        <v>60.59</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>39.92</v>
+        <v>36.72</v>
       </c>
       <c r="K33" t="n">
-        <v>87.75</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>96.40000000000001</v>
+        <v>88.67</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-86.43000000000001</v>
+        <v>-84.67</v>
       </c>
       <c r="K34" t="n">
-        <v>-20.36</v>
+        <v>-19.95</v>
       </c>
       <c r="L34" t="n">
-        <v>88.79000000000001</v>
+        <v>86.98999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-134.41</v>
+        <v>-135.33</v>
       </c>
       <c r="K35" t="n">
-        <v>13.22</v>
+        <v>13.31</v>
       </c>
       <c r="L35" t="n">
-        <v>135.06</v>
+        <v>135.98</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>252.99</v>
+        <v>236.83</v>
       </c>
       <c r="K36" t="n">
-        <v>-36.64</v>
+        <v>-34.3</v>
       </c>
       <c r="L36" t="n">
-        <v>255.63</v>
+        <v>239.3</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-168.06</v>
+        <v>-161.89</v>
       </c>
       <c r="K37" t="n">
-        <v>-92.13</v>
+        <v>-88.73999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>191.66</v>
+        <v>184.62</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-126.51</v>
+        <v>-143.41</v>
       </c>
       <c r="K38" t="n">
-        <v>75.02</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>147.08</v>
+        <v>166.73</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-165.82</v>
+        <v>-182.78</v>
       </c>
       <c r="K39" t="n">
-        <v>-82.65000000000001</v>
+        <v>-91.09999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>185.28</v>
+        <v>204.22</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>131.48</v>
+        <v>125.71</v>
       </c>
       <c r="K40" t="n">
-        <v>-359.43</v>
+        <v>-343.64</v>
       </c>
       <c r="L40" t="n">
-        <v>382.72</v>
+        <v>365.91</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>224.67</v>
+        <v>243.11</v>
       </c>
       <c r="K41" t="n">
-        <v>238.49</v>
+        <v>258.06</v>
       </c>
       <c r="L41" t="n">
-        <v>327.65</v>
+        <v>354.54</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-142.41</v>
+        <v>-158.7</v>
       </c>
       <c r="K42" t="n">
-        <v>-368.09</v>
+        <v>-410.22</v>
       </c>
       <c r="L42" t="n">
-        <v>394.67</v>
+        <v>439.85</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>173.68</v>
+        <v>205.13</v>
       </c>
       <c r="K43" t="n">
-        <v>-126.92</v>
+        <v>-149.91</v>
       </c>
       <c r="L43" t="n">
-        <v>215.11</v>
+        <v>254.07</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>48.44</v>
+        <v>49.82</v>
       </c>
       <c r="K44" t="n">
-        <v>-25.16</v>
+        <v>-25.88</v>
       </c>
       <c r="L44" t="n">
-        <v>54.59</v>
+        <v>56.14</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>92.14</v>
+        <v>79.5</v>
       </c>
       <c r="K45" t="n">
-        <v>28.38</v>
+        <v>24.49</v>
       </c>
       <c r="L45" t="n">
-        <v>96.41</v>
+        <v>83.18000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>75</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>-62.18</v>
+        <v>-54.9</v>
       </c>
       <c r="L46" t="n">
-        <v>97.42</v>
+        <v>86.01000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-62.24</v>
+        <v>-56.89</v>
       </c>
       <c r="K47" t="n">
-        <v>-49.44</v>
+        <v>-45.2</v>
       </c>
       <c r="L47" t="n">
-        <v>79.48</v>
+        <v>72.66</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>29.15</v>
+        <v>25.7</v>
       </c>
       <c r="K48" t="n">
-        <v>91.31999999999999</v>
+        <v>80.53</v>
       </c>
       <c r="L48" t="n">
-        <v>95.86</v>
+        <v>84.53</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>9.27</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>76.40000000000001</v>
+        <v>73.20999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>76.95999999999999</v>
+        <v>73.75</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>101.9</v>
+        <v>102.64</v>
       </c>
       <c r="K50" t="n">
-        <v>92.77</v>
+        <v>93.45</v>
       </c>
       <c r="L50" t="n">
-        <v>137.8</v>
+        <v>138.81</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-42.27</v>
+        <v>-39.65</v>
       </c>
       <c r="K51" t="n">
-        <v>-262.15</v>
+        <v>-245.92</v>
       </c>
       <c r="L51" t="n">
-        <v>265.54</v>
+        <v>249.09</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-54.93</v>
+        <v>-51.91</v>
       </c>
       <c r="K52" t="n">
-        <v>233.18</v>
+        <v>220.36</v>
       </c>
       <c r="L52" t="n">
-        <v>239.57</v>
+        <v>226.39</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>207.56</v>
+        <v>191.7</v>
       </c>
       <c r="K53" t="n">
-        <v>38.58</v>
+        <v>35.63</v>
       </c>
       <c r="L53" t="n">
-        <v>211.11</v>
+        <v>194.99</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>232.68</v>
+        <v>249.23</v>
       </c>
       <c r="K54" t="n">
-        <v>-70.47</v>
+        <v>-75.48999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>243.12</v>
+        <v>260.41</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-202.13</v>
+        <v>-219.37</v>
       </c>
       <c r="K55" t="n">
-        <v>-137.8</v>
+        <v>-149.55</v>
       </c>
       <c r="L55" t="n">
-        <v>244.63</v>
+        <v>265.49</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-183.24</v>
+        <v>-206.14</v>
       </c>
       <c r="K56" t="n">
-        <v>-447.64</v>
+        <v>-503.58</v>
       </c>
       <c r="L56" t="n">
-        <v>483.7</v>
+        <v>544.14</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>213.01</v>
+        <v>250.58</v>
       </c>
       <c r="K57" t="n">
-        <v>129.48</v>
+        <v>152.31</v>
       </c>
       <c r="L57" t="n">
-        <v>249.27</v>
+        <v>293.24</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-214.13</v>
+        <v>-245.92</v>
       </c>
       <c r="K58" t="n">
-        <v>-319.49</v>
+        <v>-366.93</v>
       </c>
       <c r="L58" t="n">
-        <v>384.61</v>
+        <v>441.71</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-57</v>
+        <v>-53.5</v>
       </c>
       <c r="K59" t="n">
-        <v>64.09999999999999</v>
+        <v>60.16</v>
       </c>
       <c r="L59" t="n">
-        <v>85.78</v>
+        <v>80.51000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>36.9</v>
+        <v>26.74</v>
       </c>
       <c r="K60" t="n">
-        <v>-136.63</v>
+        <v>-99</v>
       </c>
       <c r="L60" t="n">
-        <v>141.53</v>
+        <v>102.55</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-98.04000000000001</v>
+        <v>-81.98999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>-28.24</v>
+        <v>-23.62</v>
       </c>
       <c r="L61" t="n">
-        <v>102.03</v>
+        <v>85.31999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>123.12</v>
+        <v>109.31</v>
       </c>
       <c r="K62" t="n">
-        <v>-97.84</v>
+        <v>-86.86</v>
       </c>
       <c r="L62" t="n">
-        <v>157.26</v>
+        <v>139.62</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-58.95</v>
+        <v>-51.26</v>
       </c>
       <c r="K63" t="n">
-        <v>85.87</v>
+        <v>74.67</v>
       </c>
       <c r="L63" t="n">
-        <v>104.16</v>
+        <v>90.56999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-80.5</v>
+        <v>-70.64</v>
       </c>
       <c r="K64" t="n">
-        <v>59.75</v>
+        <v>52.42</v>
       </c>
       <c r="L64" t="n">
-        <v>100.25</v>
+        <v>87.95999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-118.52</v>
+        <v>-112.65</v>
       </c>
       <c r="K65" t="n">
-        <v>-205.74</v>
+        <v>-195.56</v>
       </c>
       <c r="L65" t="n">
-        <v>237.44</v>
+        <v>225.68</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>53.12</v>
+        <v>49.81</v>
       </c>
       <c r="K66" t="n">
-        <v>-176.32</v>
+        <v>-165.32</v>
       </c>
       <c r="L66" t="n">
-        <v>184.15</v>
+        <v>172.66</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>301.75</v>
+        <v>279.85</v>
       </c>
       <c r="K67" t="n">
-        <v>-64.17</v>
+        <v>-59.51</v>
       </c>
       <c r="L67" t="n">
-        <v>308.49</v>
+        <v>286.11</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>68.97</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>-224.65</v>
+        <v>-229.51</v>
       </c>
       <c r="L68" t="n">
-        <v>235</v>
+        <v>240.09</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>-207.58</v>
+        <v>-214.94</v>
       </c>
       <c r="K69" t="n">
-        <v>-313.02</v>
+        <v>-324.12</v>
       </c>
       <c r="L69" t="n">
-        <v>375.6</v>
+        <v>388.92</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>169.36</v>
+        <v>191.96</v>
       </c>
       <c r="K70" t="n">
-        <v>34.18</v>
+        <v>38.74</v>
       </c>
       <c r="L70" t="n">
-        <v>172.77</v>
+        <v>195.83</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-137.9</v>
+        <v>-169.65</v>
       </c>
       <c r="K71" t="n">
-        <v>-147.23</v>
+        <v>-181.13</v>
       </c>
       <c r="L71" t="n">
-        <v>201.72</v>
+        <v>248.17</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>74.16</v>
+        <v>85.39</v>
       </c>
       <c r="K72" t="n">
-        <v>-265.15</v>
+        <v>-305.31</v>
       </c>
       <c r="L72" t="n">
-        <v>275.33</v>
+        <v>317.03</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>242.52</v>
+        <v>283.98</v>
       </c>
       <c r="K73" t="n">
-        <v>119.25</v>
+        <v>139.64</v>
       </c>
       <c r="L73" t="n">
-        <v>270.26</v>
+        <v>316.45</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-61.27</v>
+        <v>-49.94</v>
       </c>
       <c r="K74" t="n">
-        <v>-62.48</v>
+        <v>-50.93</v>
       </c>
       <c r="L74" t="n">
-        <v>87.51000000000001</v>
+        <v>71.33</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-81.89</v>
+        <v>-65.15000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>-81.38</v>
+        <v>-64.75</v>
       </c>
       <c r="L75" t="n">
-        <v>115.45</v>
+        <v>91.84999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-80.26000000000001</v>
+        <v>-65.95999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>-78.34999999999999</v>
+        <v>-64.39</v>
       </c>
       <c r="L76" t="n">
-        <v>112.16</v>
+        <v>92.18000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-29.14</v>
+        <v>-22.78</v>
       </c>
       <c r="K77" t="n">
-        <v>-166.79</v>
+        <v>-130.4</v>
       </c>
       <c r="L77" t="n">
-        <v>169.32</v>
+        <v>132.37</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-158.93</v>
+        <v>-138.4</v>
       </c>
       <c r="K78" t="n">
-        <v>-108.69</v>
+        <v>-94.64</v>
       </c>
       <c r="L78" t="n">
-        <v>192.54</v>
+        <v>167.66</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>9.789999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="K79" t="n">
-        <v>76.37</v>
+        <v>71.34</v>
       </c>
       <c r="L79" t="n">
-        <v>77</v>
+        <v>71.92</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-270.12</v>
+        <v>-251.69</v>
       </c>
       <c r="K80" t="n">
-        <v>103.05</v>
+        <v>96.02</v>
       </c>
       <c r="L80" t="n">
-        <v>289.1</v>
+        <v>269.38</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-68.51000000000001</v>
+        <v>-67</v>
       </c>
       <c r="K81" t="n">
-        <v>-175.47</v>
+        <v>-171.61</v>
       </c>
       <c r="L81" t="n">
-        <v>188.37</v>
+        <v>184.22</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-143.84</v>
+        <v>-140.27</v>
       </c>
       <c r="K82" t="n">
-        <v>107.42</v>
+        <v>104.75</v>
       </c>
       <c r="L82" t="n">
-        <v>179.52</v>
+        <v>175.07</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-331.53</v>
+        <v>-349.4</v>
       </c>
       <c r="K83" t="n">
-        <v>-23.54</v>
+        <v>-24.81</v>
       </c>
       <c r="L83" t="n">
-        <v>332.36</v>
+        <v>350.28</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>241.86</v>
+        <v>259.1</v>
       </c>
       <c r="K84" t="n">
-        <v>-33.41</v>
+        <v>-35.79</v>
       </c>
       <c r="L84" t="n">
-        <v>244.16</v>
+        <v>261.56</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>311.43</v>
+        <v>326.23</v>
       </c>
       <c r="K85" t="n">
-        <v>117.2</v>
+        <v>122.76</v>
       </c>
       <c r="L85" t="n">
-        <v>332.75</v>
+        <v>348.56</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-200.56</v>
+        <v>-230.49</v>
       </c>
       <c r="K86" t="n">
-        <v>-393.69</v>
+        <v>-452.46</v>
       </c>
       <c r="L86" t="n">
-        <v>441.83</v>
+        <v>507.79</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>-6.28</v>
+        <v>-7.49</v>
       </c>
       <c r="K87" t="n">
-        <v>-336.69</v>
+        <v>-401.47</v>
       </c>
       <c r="L87" t="n">
-        <v>336.75</v>
+        <v>401.54</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-325.54</v>
+        <v>-372.45</v>
       </c>
       <c r="K88" t="n">
-        <v>-138.69</v>
+        <v>-158.67</v>
       </c>
       <c r="L88" t="n">
-        <v>353.85</v>
+        <v>404.84</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-01.xlsx
+++ b/output/2024-04-01.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-23.24</v>
+        <v>-24.82</v>
       </c>
       <c r="K14" t="n">
-        <v>-55.66</v>
+        <v>-59.45</v>
       </c>
       <c r="L14" t="n">
-        <v>60.32</v>
+        <v>64.42</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-27.91</v>
+        <v>-30.26</v>
       </c>
       <c r="K15" t="n">
-        <v>49.03</v>
+        <v>53.17</v>
       </c>
       <c r="L15" t="n">
-        <v>56.41</v>
+        <v>61.18</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-78.66</v>
+        <v>-77</v>
       </c>
       <c r="K16" t="n">
-        <v>-59.46</v>
+        <v>-58.2</v>
       </c>
       <c r="L16" t="n">
-        <v>98.61</v>
+        <v>96.52</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>42.15</v>
+        <v>41.64</v>
       </c>
       <c r="K17" t="n">
-        <v>100.72</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>109.19</v>
+        <v>107.85</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>15.52</v>
+        <v>16.86</v>
       </c>
       <c r="K18" t="n">
-        <v>32.13</v>
+        <v>34.91</v>
       </c>
       <c r="L18" t="n">
-        <v>35.68</v>
+        <v>38.77</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>103.92</v>
+        <v>100.79</v>
       </c>
       <c r="K19" t="n">
-        <v>-68.42</v>
+        <v>-66.36</v>
       </c>
       <c r="L19" t="n">
-        <v>124.42</v>
+        <v>120.68</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>140.71</v>
+        <v>141.51</v>
       </c>
       <c r="K20" t="n">
-        <v>-25.44</v>
+        <v>-25.59</v>
       </c>
       <c r="L20" t="n">
-        <v>142.99</v>
+        <v>143.81</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-136.89</v>
+        <v>-136.74</v>
       </c>
       <c r="K21" t="n">
-        <v>-54.91</v>
+        <v>-54.85</v>
       </c>
       <c r="L21" t="n">
-        <v>147.49</v>
+        <v>147.33</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-94.75</v>
+        <v>-101.54</v>
       </c>
       <c r="K22" t="n">
-        <v>-62.67</v>
+        <v>-67.16</v>
       </c>
       <c r="L22" t="n">
-        <v>113.6</v>
+        <v>121.75</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>123.55</v>
+        <v>135.51</v>
       </c>
       <c r="K23" t="n">
-        <v>-43.35</v>
+        <v>-47.55</v>
       </c>
       <c r="L23" t="n">
-        <v>130.93</v>
+        <v>143.61</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>72.90000000000001</v>
+        <v>74.58</v>
       </c>
       <c r="K24" t="n">
-        <v>-184.79</v>
+        <v>-189.03</v>
       </c>
       <c r="L24" t="n">
-        <v>198.65</v>
+        <v>203.21</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-174.58</v>
+        <v>-174.69</v>
       </c>
       <c r="K25" t="n">
-        <v>-101.36</v>
+        <v>-101.42</v>
       </c>
       <c r="L25" t="n">
-        <v>201.87</v>
+        <v>201.99</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>294.54</v>
+        <v>277.5</v>
       </c>
       <c r="K26" t="n">
-        <v>-570.1900000000001</v>
+        <v>-537.2</v>
       </c>
       <c r="L26" t="n">
-        <v>641.78</v>
+        <v>604.64</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-365.8</v>
+        <v>-362.23</v>
       </c>
       <c r="K27" t="n">
-        <v>154.38</v>
+        <v>152.88</v>
       </c>
       <c r="L27" t="n">
-        <v>397.04</v>
+        <v>393.17</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>383.68</v>
+        <v>374.26</v>
       </c>
       <c r="K28" t="n">
-        <v>210.97</v>
+        <v>205.79</v>
       </c>
       <c r="L28" t="n">
-        <v>437.86</v>
+        <v>427.11</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>61.55</v>
+        <v>60.12</v>
       </c>
       <c r="K29" t="n">
-        <v>-75.77</v>
+        <v>-74.01000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>97.62</v>
+        <v>95.34999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>42.08</v>
+        <v>40.7</v>
       </c>
       <c r="K30" t="n">
-        <v>-93.95</v>
+        <v>-90.86</v>
       </c>
       <c r="L30" t="n">
-        <v>102.94</v>
+        <v>99.56</v>
       </c>
     </row>
     <row r="31">
@@ -1357,10 +1357,10 @@
         <v>1.79</v>
       </c>
       <c r="K31" t="n">
-        <v>-86.31999999999999</v>
+        <v>-85.89</v>
       </c>
       <c r="L31" t="n">
-        <v>86.34</v>
+        <v>85.91</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>60.49</v>
+        <v>66.25</v>
       </c>
       <c r="K32" t="n">
-        <v>3.44</v>
+        <v>3.77</v>
       </c>
       <c r="L32" t="n">
-        <v>60.59</v>
+        <v>66.34999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>36.72</v>
+        <v>37.6</v>
       </c>
       <c r="K33" t="n">
-        <v>80.70999999999999</v>
+        <v>82.64</v>
       </c>
       <c r="L33" t="n">
-        <v>88.67</v>
+        <v>90.79000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-84.67</v>
+        <v>-86.54000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-19.95</v>
+        <v>-20.39</v>
       </c>
       <c r="L34" t="n">
-        <v>86.98999999999999</v>
+        <v>88.91</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-135.33</v>
+        <v>-139.35</v>
       </c>
       <c r="K35" t="n">
-        <v>13.31</v>
+        <v>13.71</v>
       </c>
       <c r="L35" t="n">
-        <v>135.98</v>
+        <v>140.02</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>236.83</v>
+        <v>224.92</v>
       </c>
       <c r="K36" t="n">
-        <v>-34.3</v>
+        <v>-32.57</v>
       </c>
       <c r="L36" t="n">
-        <v>239.3</v>
+        <v>227.27</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-161.89</v>
+        <v>-156.68</v>
       </c>
       <c r="K37" t="n">
-        <v>-88.73999999999999</v>
+        <v>-85.89</v>
       </c>
       <c r="L37" t="n">
-        <v>184.62</v>
+        <v>178.68</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-143.41</v>
+        <v>-153.76</v>
       </c>
       <c r="K38" t="n">
-        <v>85.04000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>166.73</v>
+        <v>178.76</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-182.78</v>
+        <v>-189.94</v>
       </c>
       <c r="K39" t="n">
-        <v>-91.09999999999999</v>
+        <v>-94.67</v>
       </c>
       <c r="L39" t="n">
-        <v>204.22</v>
+        <v>212.22</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>125.71</v>
+        <v>120.46</v>
       </c>
       <c r="K40" t="n">
-        <v>-343.64</v>
+        <v>-329.29</v>
       </c>
       <c r="L40" t="n">
-        <v>365.91</v>
+        <v>350.63</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>243.11</v>
+        <v>241.84</v>
       </c>
       <c r="K41" t="n">
-        <v>258.06</v>
+        <v>256.71</v>
       </c>
       <c r="L41" t="n">
-        <v>354.54</v>
+        <v>352.68</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-158.7</v>
+        <v>-155.81</v>
       </c>
       <c r="K42" t="n">
-        <v>-410.22</v>
+        <v>-402.73</v>
       </c>
       <c r="L42" t="n">
-        <v>439.85</v>
+        <v>431.81</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>205.13</v>
+        <v>218.77</v>
       </c>
       <c r="K43" t="n">
-        <v>-149.91</v>
+        <v>-159.88</v>
       </c>
       <c r="L43" t="n">
-        <v>254.07</v>
+        <v>270.96</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>49.82</v>
+        <v>53.17</v>
       </c>
       <c r="K44" t="n">
-        <v>-25.88</v>
+        <v>-27.62</v>
       </c>
       <c r="L44" t="n">
-        <v>56.14</v>
+        <v>59.92</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>79.5</v>
+        <v>79.44</v>
       </c>
       <c r="K45" t="n">
-        <v>24.49</v>
+        <v>24.47</v>
       </c>
       <c r="L45" t="n">
-        <v>83.18000000000001</v>
+        <v>83.12</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>66.20999999999999</v>
+        <v>65.34</v>
       </c>
       <c r="K46" t="n">
-        <v>-54.9</v>
+        <v>-54.17</v>
       </c>
       <c r="L46" t="n">
-        <v>86.01000000000001</v>
+        <v>84.87</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-56.89</v>
+        <v>-59.9</v>
       </c>
       <c r="K47" t="n">
-        <v>-45.2</v>
+        <v>-47.59</v>
       </c>
       <c r="L47" t="n">
-        <v>72.66</v>
+        <v>76.51000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>25.7</v>
+        <v>26.7</v>
       </c>
       <c r="K48" t="n">
-        <v>80.53</v>
+        <v>83.65000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>84.53</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>8.890000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="K49" t="n">
-        <v>73.20999999999999</v>
+        <v>77.55</v>
       </c>
       <c r="L49" t="n">
-        <v>73.75</v>
+        <v>78.12</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>102.64</v>
+        <v>106</v>
       </c>
       <c r="K50" t="n">
-        <v>93.45</v>
+        <v>96.5</v>
       </c>
       <c r="L50" t="n">
-        <v>138.81</v>
+        <v>143.35</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-39.65</v>
+        <v>-37.86</v>
       </c>
       <c r="K51" t="n">
-        <v>-245.92</v>
+        <v>-234.83</v>
       </c>
       <c r="L51" t="n">
-        <v>249.09</v>
+        <v>237.87</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-51.91</v>
+        <v>-49.28</v>
       </c>
       <c r="K52" t="n">
-        <v>220.36</v>
+        <v>209.19</v>
       </c>
       <c r="L52" t="n">
-        <v>226.39</v>
+        <v>214.92</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>191.7</v>
+        <v>199.97</v>
       </c>
       <c r="K53" t="n">
-        <v>35.63</v>
+        <v>37.17</v>
       </c>
       <c r="L53" t="n">
-        <v>194.99</v>
+        <v>203.39</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>249.23</v>
+        <v>249.82</v>
       </c>
       <c r="K54" t="n">
-        <v>-75.48999999999999</v>
+        <v>-75.67</v>
       </c>
       <c r="L54" t="n">
-        <v>260.41</v>
+        <v>261.03</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-219.37</v>
+        <v>-222.15</v>
       </c>
       <c r="K55" t="n">
-        <v>-149.55</v>
+        <v>-151.44</v>
       </c>
       <c r="L55" t="n">
-        <v>265.49</v>
+        <v>268.86</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-206.14</v>
+        <v>-200.67</v>
       </c>
       <c r="K56" t="n">
-        <v>-503.58</v>
+        <v>-490.2</v>
       </c>
       <c r="L56" t="n">
-        <v>544.14</v>
+        <v>529.6799999999999</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>250.58</v>
+        <v>262.51</v>
       </c>
       <c r="K57" t="n">
-        <v>152.31</v>
+        <v>159.56</v>
       </c>
       <c r="L57" t="n">
-        <v>293.24</v>
+        <v>307.2</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-245.92</v>
+        <v>-245.52</v>
       </c>
       <c r="K58" t="n">
-        <v>-366.93</v>
+        <v>-366.34</v>
       </c>
       <c r="L58" t="n">
-        <v>441.71</v>
+        <v>441</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-53.5</v>
+        <v>-53.58</v>
       </c>
       <c r="K59" t="n">
-        <v>60.16</v>
+        <v>60.25</v>
       </c>
       <c r="L59" t="n">
-        <v>80.51000000000001</v>
+        <v>80.62</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>26.74</v>
+        <v>26.41</v>
       </c>
       <c r="K60" t="n">
-        <v>-99</v>
+        <v>-97.8</v>
       </c>
       <c r="L60" t="n">
-        <v>102.55</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-81.98999999999999</v>
+        <v>-81.7</v>
       </c>
       <c r="K61" t="n">
-        <v>-23.62</v>
+        <v>-23.54</v>
       </c>
       <c r="L61" t="n">
-        <v>85.31999999999999</v>
+        <v>85.02</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>109.31</v>
+        <v>104.5</v>
       </c>
       <c r="K62" t="n">
-        <v>-86.86</v>
+        <v>-83.04000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>139.62</v>
+        <v>133.47</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-51.26</v>
+        <v>-51.72</v>
       </c>
       <c r="K63" t="n">
-        <v>74.67</v>
+        <v>75.34</v>
       </c>
       <c r="L63" t="n">
-        <v>90.56999999999999</v>
+        <v>91.38</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-70.64</v>
+        <v>-71.95999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>52.42</v>
+        <v>53.41</v>
       </c>
       <c r="L64" t="n">
-        <v>87.95999999999999</v>
+        <v>89.61</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-112.65</v>
+        <v>-109.8</v>
       </c>
       <c r="K65" t="n">
-        <v>-195.56</v>
+        <v>-190.61</v>
       </c>
       <c r="L65" t="n">
-        <v>225.68</v>
+        <v>219.97</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>49.81</v>
+        <v>51.48</v>
       </c>
       <c r="K66" t="n">
-        <v>-165.32</v>
+        <v>-170.87</v>
       </c>
       <c r="L66" t="n">
-        <v>172.66</v>
+        <v>178.46</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>279.85</v>
+        <v>263.37</v>
       </c>
       <c r="K67" t="n">
-        <v>-59.51</v>
+        <v>-56.01</v>
       </c>
       <c r="L67" t="n">
-        <v>286.11</v>
+        <v>269.26</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>70.45999999999999</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>-229.51</v>
+        <v>-224.71</v>
       </c>
       <c r="L68" t="n">
-        <v>240.09</v>
+        <v>235.07</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>-214.94</v>
+        <v>-206.1</v>
       </c>
       <c r="K69" t="n">
-        <v>-324.12</v>
+        <v>-310.8</v>
       </c>
       <c r="L69" t="n">
-        <v>388.92</v>
+        <v>372.93</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>191.96</v>
+        <v>204.59</v>
       </c>
       <c r="K70" t="n">
-        <v>38.74</v>
+        <v>41.29</v>
       </c>
       <c r="L70" t="n">
-        <v>195.83</v>
+        <v>208.72</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-169.65</v>
+        <v>-184.79</v>
       </c>
       <c r="K71" t="n">
-        <v>-181.13</v>
+        <v>-197.29</v>
       </c>
       <c r="L71" t="n">
-        <v>248.17</v>
+        <v>270.32</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>85.39</v>
+        <v>88.03</v>
       </c>
       <c r="K72" t="n">
-        <v>-305.31</v>
+        <v>-314.73</v>
       </c>
       <c r="L72" t="n">
-        <v>317.03</v>
+        <v>326.8</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>283.98</v>
+        <v>295.87</v>
       </c>
       <c r="K73" t="n">
-        <v>139.64</v>
+        <v>145.49</v>
       </c>
       <c r="L73" t="n">
-        <v>316.45</v>
+        <v>329.71</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-49.94</v>
+        <v>-50.95</v>
       </c>
       <c r="K74" t="n">
-        <v>-50.93</v>
+        <v>-51.96</v>
       </c>
       <c r="L74" t="n">
-        <v>71.33</v>
+        <v>72.77</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-65.15000000000001</v>
+        <v>-64.26000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>-64.75</v>
+        <v>-63.87</v>
       </c>
       <c r="L75" t="n">
-        <v>91.84999999999999</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-65.95999999999999</v>
+        <v>-65.08</v>
       </c>
       <c r="K76" t="n">
-        <v>-64.39</v>
+        <v>-63.54</v>
       </c>
       <c r="L76" t="n">
-        <v>92.18000000000001</v>
+        <v>90.95</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-22.78</v>
+        <v>-22.28</v>
       </c>
       <c r="K77" t="n">
-        <v>-130.4</v>
+        <v>-127.49</v>
       </c>
       <c r="L77" t="n">
-        <v>132.37</v>
+        <v>129.43</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-138.4</v>
+        <v>-129.41</v>
       </c>
       <c r="K78" t="n">
-        <v>-94.64</v>
+        <v>-88.5</v>
       </c>
       <c r="L78" t="n">
-        <v>167.66</v>
+        <v>156.77</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>9.15</v>
+        <v>9.73</v>
       </c>
       <c r="K79" t="n">
-        <v>71.34</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>71.92</v>
+        <v>76.53</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-251.69</v>
+        <v>-238.13</v>
       </c>
       <c r="K80" t="n">
-        <v>96.02</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>269.38</v>
+        <v>254.88</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-67</v>
+        <v>-67.41</v>
       </c>
       <c r="K81" t="n">
-        <v>-171.61</v>
+        <v>-172.67</v>
       </c>
       <c r="L81" t="n">
-        <v>184.22</v>
+        <v>185.36</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-140.27</v>
+        <v>-140.23</v>
       </c>
       <c r="K82" t="n">
-        <v>104.75</v>
+        <v>104.72</v>
       </c>
       <c r="L82" t="n">
-        <v>175.07</v>
+        <v>175.02</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-349.4</v>
+        <v>-341.47</v>
       </c>
       <c r="K83" t="n">
-        <v>-24.81</v>
+        <v>-24.25</v>
       </c>
       <c r="L83" t="n">
-        <v>350.28</v>
+        <v>342.33</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>259.1</v>
+        <v>260.18</v>
       </c>
       <c r="K84" t="n">
-        <v>-35.79</v>
+        <v>-35.94</v>
       </c>
       <c r="L84" t="n">
-        <v>261.56</v>
+        <v>262.65</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>326.23</v>
+        <v>317.32</v>
       </c>
       <c r="K85" t="n">
-        <v>122.76</v>
+        <v>119.41</v>
       </c>
       <c r="L85" t="n">
-        <v>348.56</v>
+        <v>339.04</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-230.49</v>
+        <v>-228.41</v>
       </c>
       <c r="K86" t="n">
-        <v>-452.46</v>
+        <v>-448.38</v>
       </c>
       <c r="L86" t="n">
-        <v>507.79</v>
+        <v>503.2</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>-7.49</v>
+        <v>-7.69</v>
       </c>
       <c r="K87" t="n">
-        <v>-401.47</v>
+        <v>-412.22</v>
       </c>
       <c r="L87" t="n">
-        <v>401.54</v>
+        <v>412.29</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-372.45</v>
+        <v>-373.51</v>
       </c>
       <c r="K88" t="n">
-        <v>-158.67</v>
+        <v>-159.12</v>
       </c>
       <c r="L88" t="n">
-        <v>404.84</v>
+        <v>405.99</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-01.xlsx
+++ b/output/2024-04-01.xlsx
@@ -628,25 +628,25 @@
         <v>5.23</v>
       </c>
       <c r="F14" t="n">
-        <v>12.96</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>174.8</v>
+        <v>198.9</v>
       </c>
       <c r="H14" t="n">
-        <v>85.7</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-24.82</v>
+        <v>-29.03</v>
       </c>
       <c r="K14" t="n">
-        <v>-59.45</v>
+        <v>-64.43000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>64.42</v>
+        <v>70.66</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>5.21</v>
       </c>
       <c r="F15" t="n">
-        <v>12.14</v>
+        <v>13.63</v>
       </c>
       <c r="G15" t="n">
-        <v>190.8</v>
+        <v>182.5</v>
       </c>
       <c r="H15" t="n">
-        <v>87</v>
+        <v>93.2</v>
       </c>
       <c r="I15" t="n">
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-30.26</v>
+        <v>-37.36</v>
       </c>
       <c r="K15" t="n">
-        <v>53.17</v>
+        <v>60.78</v>
       </c>
       <c r="L15" t="n">
-        <v>61.18</v>
+        <v>71.34</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>5.2</v>
       </c>
       <c r="F16" t="n">
-        <v>12.28</v>
+        <v>12.53</v>
       </c>
       <c r="G16" t="n">
-        <v>169.3</v>
+        <v>185.3</v>
       </c>
       <c r="H16" t="n">
-        <v>93.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I16" t="n">
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-77</v>
+        <v>-82.02</v>
       </c>
       <c r="K16" t="n">
-        <v>-58.2</v>
+        <v>-63.26</v>
       </c>
       <c r="L16" t="n">
-        <v>96.52</v>
+        <v>103.59</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>4.54</v>
       </c>
       <c r="F17" t="n">
-        <v>12.17</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>181.8</v>
+        <v>183.1</v>
       </c>
       <c r="H17" t="n">
-        <v>90.7</v>
+        <v>88.7</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>41.64</v>
+        <v>41.86</v>
       </c>
       <c r="K17" t="n">
-        <v>99.48999999999999</v>
+        <v>96.31</v>
       </c>
       <c r="L17" t="n">
-        <v>107.85</v>
+        <v>105.02</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>4.63</v>
       </c>
       <c r="F18" t="n">
-        <v>12.37</v>
+        <v>10.07</v>
       </c>
       <c r="G18" t="n">
-        <v>187.6</v>
+        <v>187.1</v>
       </c>
       <c r="H18" t="n">
-        <v>89.7</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>16.86</v>
+        <v>15.27</v>
       </c>
       <c r="K18" t="n">
-        <v>34.91</v>
+        <v>22.72</v>
       </c>
       <c r="L18" t="n">
-        <v>38.77</v>
+        <v>27.38</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>5.69</v>
       </c>
       <c r="F19" t="n">
-        <v>12.06</v>
+        <v>11.58</v>
       </c>
       <c r="G19" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H19" t="n">
-        <v>89.5</v>
+        <v>84.7</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>100.79</v>
+        <v>98.97</v>
       </c>
       <c r="K19" t="n">
-        <v>-66.36</v>
+        <v>-71.65000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>120.68</v>
+        <v>122.18</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>4.47</v>
       </c>
       <c r="F20" t="n">
-        <v>12.09</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>177.2</v>
+        <v>181.5</v>
       </c>
       <c r="H20" t="n">
-        <v>89.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>141.51</v>
+        <v>150.09</v>
       </c>
       <c r="K20" t="n">
-        <v>-25.59</v>
+        <v>-49.63</v>
       </c>
       <c r="L20" t="n">
-        <v>143.81</v>
+        <v>158.08</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>4.05</v>
       </c>
       <c r="F21" t="n">
-        <v>13.03</v>
+        <v>12.21</v>
       </c>
       <c r="G21" t="n">
-        <v>176.9</v>
+        <v>200.4</v>
       </c>
       <c r="H21" t="n">
-        <v>85.5</v>
+        <v>86.2</v>
       </c>
       <c r="I21" t="n">
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-136.74</v>
+        <v>-159.42</v>
       </c>
       <c r="K21" t="n">
-        <v>-54.85</v>
+        <v>-76.23999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>147.33</v>
+        <v>176.72</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>4.89</v>
       </c>
       <c r="F22" t="n">
-        <v>12.61</v>
+        <v>9.67</v>
       </c>
       <c r="G22" t="n">
-        <v>183.7</v>
+        <v>191.9</v>
       </c>
       <c r="H22" t="n">
-        <v>86.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I22" t="n">
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-101.54</v>
+        <v>-101.13</v>
       </c>
       <c r="K22" t="n">
-        <v>-67.16</v>
+        <v>-98.84</v>
       </c>
       <c r="L22" t="n">
-        <v>121.75</v>
+        <v>141.41</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>4.58</v>
       </c>
       <c r="F23" t="n">
-        <v>12.71</v>
+        <v>10.75</v>
       </c>
       <c r="G23" t="n">
-        <v>189.5</v>
+        <v>193.8</v>
       </c>
       <c r="H23" t="n">
-        <v>88.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>135.51</v>
+        <v>99.72</v>
       </c>
       <c r="K23" t="n">
-        <v>-47.55</v>
+        <v>-130.44</v>
       </c>
       <c r="L23" t="n">
-        <v>143.61</v>
+        <v>164.19</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>4.8</v>
       </c>
       <c r="F24" t="n">
-        <v>13.14</v>
+        <v>11.4</v>
       </c>
       <c r="G24" t="n">
-        <v>184.9</v>
+        <v>202.4</v>
       </c>
       <c r="H24" t="n">
-        <v>91.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="I24" t="n">
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>74.58</v>
+        <v>47.06</v>
       </c>
       <c r="K24" t="n">
-        <v>-189.03</v>
+        <v>-228.42</v>
       </c>
       <c r="L24" t="n">
-        <v>203.21</v>
+        <v>233.21</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>4.37</v>
       </c>
       <c r="F25" t="n">
-        <v>12.67</v>
+        <v>10.35</v>
       </c>
       <c r="G25" t="n">
-        <v>171.7</v>
+        <v>193.1</v>
       </c>
       <c r="H25" t="n">
-        <v>92.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-174.69</v>
+        <v>-187.78</v>
       </c>
       <c r="K25" t="n">
-        <v>-101.42</v>
+        <v>-134.63</v>
       </c>
       <c r="L25" t="n">
-        <v>201.99</v>
+        <v>231.05</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>4.93</v>
       </c>
       <c r="F26" t="n">
-        <v>12.2</v>
+        <v>10.86</v>
       </c>
       <c r="G26" t="n">
-        <v>184.9</v>
+        <v>183.7</v>
       </c>
       <c r="H26" t="n">
-        <v>89.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="I26" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>277.5</v>
+        <v>263.38</v>
       </c>
       <c r="K26" t="n">
-        <v>-537.2</v>
+        <v>-540.3200000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>604.64</v>
+        <v>601.1</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>4.74</v>
       </c>
       <c r="F27" t="n">
-        <v>12.43</v>
+        <v>11.29</v>
       </c>
       <c r="G27" t="n">
-        <v>171.6</v>
+        <v>188.3</v>
       </c>
       <c r="H27" t="n">
-        <v>89.09999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I27" t="n">
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-362.23</v>
+        <v>-405.39</v>
       </c>
       <c r="K27" t="n">
-        <v>152.88</v>
+        <v>119.21</v>
       </c>
       <c r="L27" t="n">
-        <v>393.17</v>
+        <v>422.56</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>4.71</v>
       </c>
       <c r="F28" t="n">
-        <v>12.82</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>183</v>
+        <v>196.1</v>
       </c>
       <c r="H28" t="n">
-        <v>86.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="I28" t="n">
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>374.26</v>
+        <v>378.9</v>
       </c>
       <c r="K28" t="n">
-        <v>205.79</v>
+        <v>185.34</v>
       </c>
       <c r="L28" t="n">
-        <v>427.11</v>
+        <v>421.81</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>5.06</v>
       </c>
       <c r="F29" t="n">
-        <v>12.33</v>
+        <v>12.31</v>
       </c>
       <c r="G29" t="n">
-        <v>183.3</v>
+        <v>186.2</v>
       </c>
       <c r="H29" t="n">
-        <v>93.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I29" t="n">
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>60.12</v>
+        <v>63.85</v>
       </c>
       <c r="K29" t="n">
-        <v>-74.01000000000001</v>
+        <v>-80.78</v>
       </c>
       <c r="L29" t="n">
-        <v>95.34999999999999</v>
+        <v>102.97</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>5.21</v>
       </c>
       <c r="F30" t="n">
-        <v>12.6</v>
+        <v>12.14</v>
       </c>
       <c r="G30" t="n">
-        <v>195.1</v>
+        <v>191.7</v>
       </c>
       <c r="H30" t="n">
-        <v>90.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="I30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>40.7</v>
+        <v>42.26</v>
       </c>
       <c r="K30" t="n">
-        <v>-90.86</v>
+        <v>-96.51000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>99.56</v>
+        <v>105.36</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>4.88</v>
       </c>
       <c r="F31" t="n">
-        <v>12.02</v>
+        <v>10.55</v>
       </c>
       <c r="G31" t="n">
-        <v>190.8</v>
+        <v>180.1</v>
       </c>
       <c r="H31" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="I31" t="n">
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="K31" t="n">
-        <v>-85.89</v>
+        <v>-91.91</v>
       </c>
       <c r="L31" t="n">
-        <v>85.91</v>
+        <v>91.94</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>4.67</v>
       </c>
       <c r="F32" t="n">
-        <v>12.54</v>
+        <v>9.91</v>
       </c>
       <c r="G32" t="n">
-        <v>194.9</v>
+        <v>190.6</v>
       </c>
       <c r="H32" t="n">
-        <v>88</v>
+        <v>95.2</v>
       </c>
       <c r="I32" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>66.25</v>
+        <v>75.55</v>
       </c>
       <c r="K32" t="n">
-        <v>3.77</v>
+        <v>-11.4</v>
       </c>
       <c r="L32" t="n">
-        <v>66.34999999999999</v>
+        <v>76.41</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>5.11</v>
       </c>
       <c r="F33" t="n">
-        <v>11.67</v>
+        <v>8.92</v>
       </c>
       <c r="G33" t="n">
-        <v>190.4</v>
+        <v>173</v>
       </c>
       <c r="H33" t="n">
-        <v>88.2</v>
+        <v>93</v>
       </c>
       <c r="I33" t="n">
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>37.6</v>
+        <v>44.15</v>
       </c>
       <c r="K33" t="n">
-        <v>82.64</v>
+        <v>82.78</v>
       </c>
       <c r="L33" t="n">
-        <v>90.79000000000001</v>
+        <v>93.81999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>4.73</v>
       </c>
       <c r="F34" t="n">
-        <v>12.39</v>
+        <v>12.54</v>
       </c>
       <c r="G34" t="n">
         <v>187.6</v>
       </c>
       <c r="H34" t="n">
-        <v>94.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="I34" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-86.54000000000001</v>
+        <v>-93.38</v>
       </c>
       <c r="K34" t="n">
-        <v>-20.39</v>
+        <v>-28.12</v>
       </c>
       <c r="L34" t="n">
-        <v>88.91</v>
+        <v>97.52</v>
       </c>
     </row>
     <row r="35">
@@ -1513,22 +1513,22 @@
         <v>12.89</v>
       </c>
       <c r="G35" t="n">
-        <v>184.7</v>
+        <v>197.6</v>
       </c>
       <c r="H35" t="n">
-        <v>86.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I35" t="n">
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-139.35</v>
+        <v>-163.23</v>
       </c>
       <c r="K35" t="n">
-        <v>13.71</v>
+        <v>-15.31</v>
       </c>
       <c r="L35" t="n">
-        <v>140.02</v>
+        <v>163.95</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>5.32</v>
       </c>
       <c r="F36" t="n">
-        <v>12.64</v>
+        <v>14.14</v>
       </c>
       <c r="G36" t="n">
-        <v>192.6</v>
+        <v>192.4</v>
       </c>
       <c r="H36" t="n">
-        <v>95.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>224.92</v>
+        <v>251.35</v>
       </c>
       <c r="K36" t="n">
-        <v>-32.57</v>
+        <v>-58.45</v>
       </c>
       <c r="L36" t="n">
-        <v>227.27</v>
+        <v>258.05</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>4.21</v>
       </c>
       <c r="F37" t="n">
-        <v>11.66</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>196.2</v>
+        <v>172.9</v>
       </c>
       <c r="H37" t="n">
-        <v>91</v>
+        <v>95.8</v>
       </c>
       <c r="I37" t="n">
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-156.68</v>
+        <v>-157.58</v>
       </c>
       <c r="K37" t="n">
-        <v>-85.89</v>
+        <v>-105.56</v>
       </c>
       <c r="L37" t="n">
-        <v>178.68</v>
+        <v>189.67</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>5.19</v>
       </c>
       <c r="F38" t="n">
-        <v>11.38</v>
+        <v>12.58</v>
       </c>
       <c r="G38" t="n">
-        <v>174.4</v>
+        <v>167.2</v>
       </c>
       <c r="H38" t="n">
-        <v>91.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-153.76</v>
+        <v>-190.82</v>
       </c>
       <c r="K38" t="n">
-        <v>91.18000000000001</v>
+        <v>34.52</v>
       </c>
       <c r="L38" t="n">
-        <v>178.76</v>
+        <v>193.91</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>5.3</v>
       </c>
       <c r="F39" t="n">
-        <v>12.39</v>
+        <v>11.51</v>
       </c>
       <c r="G39" t="n">
-        <v>191.8</v>
+        <v>187.5</v>
       </c>
       <c r="H39" t="n">
-        <v>91.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I39" t="n">
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-189.94</v>
+        <v>-191.72</v>
       </c>
       <c r="K39" t="n">
-        <v>-94.67</v>
+        <v>-145.95</v>
       </c>
       <c r="L39" t="n">
-        <v>212.22</v>
+        <v>240.95</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>5.11</v>
       </c>
       <c r="F40" t="n">
-        <v>12.19</v>
+        <v>11.46</v>
       </c>
       <c r="G40" t="n">
-        <v>189.9</v>
+        <v>183.6</v>
       </c>
       <c r="H40" t="n">
-        <v>89</v>
+        <v>92.7</v>
       </c>
       <c r="I40" t="n">
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>120.46</v>
+        <v>122.2</v>
       </c>
       <c r="K40" t="n">
-        <v>-329.29</v>
+        <v>-363.42</v>
       </c>
       <c r="L40" t="n">
-        <v>350.63</v>
+        <v>383.42</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>4.56</v>
       </c>
       <c r="F41" t="n">
-        <v>12.19</v>
+        <v>7.43</v>
       </c>
       <c r="G41" t="n">
-        <v>191.7</v>
+        <v>183.4</v>
       </c>
       <c r="H41" t="n">
-        <v>87.90000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I41" t="n">
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>241.84</v>
+        <v>260.71</v>
       </c>
       <c r="K41" t="n">
-        <v>256.71</v>
+        <v>227.17</v>
       </c>
       <c r="L41" t="n">
-        <v>352.68</v>
+        <v>345.8</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>5.05</v>
       </c>
       <c r="F42" t="n">
-        <v>12.34</v>
+        <v>11.8</v>
       </c>
       <c r="G42" t="n">
-        <v>196.5</v>
+        <v>186.4</v>
       </c>
       <c r="H42" t="n">
-        <v>90.2</v>
+        <v>96</v>
       </c>
       <c r="I42" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-155.81</v>
+        <v>-159.67</v>
       </c>
       <c r="K42" t="n">
-        <v>-402.73</v>
+        <v>-469.29</v>
       </c>
       <c r="L42" t="n">
-        <v>431.81</v>
+        <v>495.71</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>4.73</v>
       </c>
       <c r="F43" t="n">
-        <v>12.46</v>
+        <v>12.35</v>
       </c>
       <c r="G43" t="n">
-        <v>174.6</v>
+        <v>188.8</v>
       </c>
       <c r="H43" t="n">
-        <v>97.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I43" t="n">
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>218.77</v>
+        <v>192.62</v>
       </c>
       <c r="K43" t="n">
-        <v>-159.88</v>
+        <v>-245.2</v>
       </c>
       <c r="L43" t="n">
-        <v>270.96</v>
+        <v>311.81</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>4.42</v>
       </c>
       <c r="F44" t="n">
-        <v>11.87</v>
+        <v>9.68</v>
       </c>
       <c r="G44" t="n">
-        <v>181.4</v>
+        <v>177.1</v>
       </c>
       <c r="H44" t="n">
-        <v>88.2</v>
+        <v>88.5</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>53.17</v>
+        <v>56.24</v>
       </c>
       <c r="K44" t="n">
-        <v>-27.62</v>
+        <v>-32.12</v>
       </c>
       <c r="L44" t="n">
-        <v>59.92</v>
+        <v>64.77</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>5.28</v>
       </c>
       <c r="F45" t="n">
-        <v>12.73</v>
+        <v>14.14</v>
       </c>
       <c r="G45" t="n">
-        <v>173.9</v>
+        <v>194.2</v>
       </c>
       <c r="H45" t="n">
-        <v>89.2</v>
+        <v>84.7</v>
       </c>
       <c r="I45" t="n">
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>79.44</v>
+        <v>88.28</v>
       </c>
       <c r="K45" t="n">
-        <v>24.47</v>
+        <v>25.53</v>
       </c>
       <c r="L45" t="n">
-        <v>83.12</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>5.1</v>
       </c>
       <c r="F46" t="n">
-        <v>12.33</v>
+        <v>14.14</v>
       </c>
       <c r="G46" t="n">
-        <v>202.3</v>
+        <v>186.3</v>
       </c>
       <c r="H46" t="n">
-        <v>98.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>65.34</v>
+        <v>77.02</v>
       </c>
       <c r="K46" t="n">
-        <v>-54.17</v>
+        <v>-65.62</v>
       </c>
       <c r="L46" t="n">
-        <v>84.87</v>
+        <v>101.18</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>5.31</v>
       </c>
       <c r="F47" t="n">
-        <v>11.47</v>
+        <v>13.19</v>
       </c>
       <c r="G47" t="n">
-        <v>173</v>
+        <v>169.1</v>
       </c>
       <c r="H47" t="n">
-        <v>87.3</v>
+        <v>84.2</v>
       </c>
       <c r="I47" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-59.9</v>
+        <v>-66.08</v>
       </c>
       <c r="K47" t="n">
-        <v>-47.59</v>
+        <v>-64.54000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>76.51000000000001</v>
+        <v>92.37</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>5.95</v>
       </c>
       <c r="F48" t="n">
-        <v>12.14</v>
+        <v>12.91</v>
       </c>
       <c r="G48" t="n">
-        <v>188.5</v>
+        <v>182.4</v>
       </c>
       <c r="H48" t="n">
-        <v>86.8</v>
+        <v>92</v>
       </c>
       <c r="I48" t="n">
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>26.7</v>
+        <v>33.83</v>
       </c>
       <c r="K48" t="n">
-        <v>83.65000000000001</v>
+        <v>88.88</v>
       </c>
       <c r="L48" t="n">
-        <v>87.8</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>5.06</v>
       </c>
       <c r="F49" t="n">
-        <v>12.39</v>
+        <v>10.52</v>
       </c>
       <c r="G49" t="n">
-        <v>206.5</v>
+        <v>187.5</v>
       </c>
       <c r="H49" t="n">
-        <v>90.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I49" t="n">
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>9.41</v>
+        <v>13.76</v>
       </c>
       <c r="K49" t="n">
-        <v>77.55</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>78.12</v>
+        <v>84.66</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>5.2</v>
       </c>
       <c r="F50" t="n">
-        <v>11.96</v>
+        <v>11.41</v>
       </c>
       <c r="G50" t="n">
-        <v>189.1</v>
+        <v>178.9</v>
       </c>
       <c r="H50" t="n">
-        <v>87.5</v>
+        <v>92.3</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>106</v>
+        <v>130.92</v>
       </c>
       <c r="K50" t="n">
-        <v>96.5</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>143.35</v>
+        <v>149.97</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>5.65</v>
       </c>
       <c r="F51" t="n">
-        <v>12.67</v>
+        <v>13.22</v>
       </c>
       <c r="G51" t="n">
-        <v>183.2</v>
+        <v>193.2</v>
       </c>
       <c r="H51" t="n">
-        <v>92.40000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I51" t="n">
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-37.86</v>
+        <v>-45.93</v>
       </c>
       <c r="K51" t="n">
-        <v>-234.83</v>
+        <v>-257.81</v>
       </c>
       <c r="L51" t="n">
-        <v>237.87</v>
+        <v>261.87</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>4.64</v>
       </c>
       <c r="F52" t="n">
-        <v>11.7</v>
+        <v>12.48</v>
       </c>
       <c r="G52" t="n">
-        <v>179.9</v>
+        <v>173.7</v>
       </c>
       <c r="H52" t="n">
-        <v>94.2</v>
+        <v>87.7</v>
       </c>
       <c r="I52" t="n">
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-49.28</v>
+        <v>-51.72</v>
       </c>
       <c r="K52" t="n">
-        <v>209.19</v>
+        <v>215.77</v>
       </c>
       <c r="L52" t="n">
-        <v>214.92</v>
+        <v>221.89</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>5.42</v>
       </c>
       <c r="F53" t="n">
-        <v>12.34</v>
+        <v>13.78</v>
       </c>
       <c r="G53" t="n">
-        <v>183.3</v>
+        <v>186.5</v>
       </c>
       <c r="H53" t="n">
-        <v>84.40000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>199.97</v>
+        <v>234.97</v>
       </c>
       <c r="K53" t="n">
-        <v>37.17</v>
+        <v>-16.64</v>
       </c>
       <c r="L53" t="n">
-        <v>203.39</v>
+        <v>235.55</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>5.53</v>
       </c>
       <c r="F54" t="n">
-        <v>11.91</v>
+        <v>14.14</v>
       </c>
       <c r="G54" t="n">
-        <v>198.7</v>
+        <v>177.9</v>
       </c>
       <c r="H54" t="n">
-        <v>94.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I54" t="n">
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>249.82</v>
+        <v>275.87</v>
       </c>
       <c r="K54" t="n">
-        <v>-75.67</v>
+        <v>-120.75</v>
       </c>
       <c r="L54" t="n">
-        <v>261.03</v>
+        <v>301.14</v>
       </c>
     </row>
     <row r="55">
@@ -2350,25 +2350,25 @@
         <v>5.82</v>
       </c>
       <c r="F55" t="n">
-        <v>12.93</v>
+        <v>14.14</v>
       </c>
       <c r="G55" t="n">
-        <v>187.8</v>
+        <v>198.2</v>
       </c>
       <c r="H55" t="n">
-        <v>91.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-222.15</v>
+        <v>-236.84</v>
       </c>
       <c r="K55" t="n">
-        <v>-151.44</v>
+        <v>-184.08</v>
       </c>
       <c r="L55" t="n">
-        <v>268.86</v>
+        <v>299.97</v>
       </c>
     </row>
     <row r="56">
@@ -2392,25 +2392,25 @@
         <v>5.48</v>
       </c>
       <c r="F56" t="n">
-        <v>12.76</v>
+        <v>14.14</v>
       </c>
       <c r="G56" t="n">
-        <v>181.4</v>
+        <v>194.9</v>
       </c>
       <c r="H56" t="n">
-        <v>93.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>-200.67</v>
+        <v>-224.6</v>
       </c>
       <c r="K56" t="n">
-        <v>-490.2</v>
+        <v>-523.5</v>
       </c>
       <c r="L56" t="n">
-        <v>529.6799999999999</v>
+        <v>569.65</v>
       </c>
     </row>
     <row r="57">
@@ -2434,25 +2434,25 @@
         <v>4.98</v>
       </c>
       <c r="F57" t="n">
-        <v>12.38</v>
+        <v>11.88</v>
       </c>
       <c r="G57" t="n">
-        <v>184.4</v>
+        <v>187.3</v>
       </c>
       <c r="H57" t="n">
-        <v>89.59999999999999</v>
+        <v>90</v>
       </c>
       <c r="I57" t="n">
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>262.51</v>
+        <v>306.12</v>
       </c>
       <c r="K57" t="n">
-        <v>159.56</v>
+        <v>124.08</v>
       </c>
       <c r="L57" t="n">
-        <v>307.2</v>
+        <v>330.31</v>
       </c>
     </row>
     <row r="58">
@@ -2476,25 +2476,25 @@
         <v>5.47</v>
       </c>
       <c r="F58" t="n">
-        <v>12.27</v>
+        <v>13.77</v>
       </c>
       <c r="G58" t="n">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="H58" t="n">
-        <v>91.8</v>
+        <v>98.7</v>
       </c>
       <c r="I58" t="n">
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-245.52</v>
+        <v>-241.47</v>
       </c>
       <c r="K58" t="n">
-        <v>-366.34</v>
+        <v>-438.21</v>
       </c>
       <c r="L58" t="n">
-        <v>441</v>
+        <v>500.33</v>
       </c>
     </row>
     <row r="59">
@@ -2518,25 +2518,25 @@
         <v>4.86</v>
       </c>
       <c r="F59" t="n">
-        <v>12.43</v>
+        <v>11.18</v>
       </c>
       <c r="G59" t="n">
-        <v>185.1</v>
+        <v>188.4</v>
       </c>
       <c r="H59" t="n">
-        <v>87</v>
+        <v>90.3</v>
       </c>
       <c r="I59" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-53.58</v>
+        <v>-61.43</v>
       </c>
       <c r="K59" t="n">
-        <v>60.25</v>
+        <v>66.48</v>
       </c>
       <c r="L59" t="n">
-        <v>80.62</v>
+        <v>90.52</v>
       </c>
     </row>
     <row r="60">
@@ -2560,25 +2560,25 @@
         <v>6.56</v>
       </c>
       <c r="F60" t="n">
-        <v>11.72</v>
+        <v>14.14</v>
       </c>
       <c r="G60" t="n">
-        <v>187.2</v>
+        <v>174.1</v>
       </c>
       <c r="H60" t="n">
-        <v>92.8</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I60" t="n">
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>26.41</v>
+        <v>29.29</v>
       </c>
       <c r="K60" t="n">
-        <v>-97.8</v>
+        <v>-106.42</v>
       </c>
       <c r="L60" t="n">
-        <v>101.3</v>
+        <v>110.37</v>
       </c>
     </row>
     <row r="61">
@@ -2602,25 +2602,25 @@
         <v>5.44</v>
       </c>
       <c r="F61" t="n">
-        <v>12.45</v>
+        <v>14.14</v>
       </c>
       <c r="G61" t="n">
-        <v>183.7</v>
+        <v>188.6</v>
       </c>
       <c r="H61" t="n">
-        <v>95.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-81.7</v>
+        <v>-88.39</v>
       </c>
       <c r="K61" t="n">
-        <v>-23.54</v>
+        <v>-27.5</v>
       </c>
       <c r="L61" t="n">
-        <v>85.02</v>
+        <v>92.56999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2644,25 +2644,25 @@
         <v>4.97</v>
       </c>
       <c r="F62" t="n">
-        <v>11.97</v>
+        <v>14.14</v>
       </c>
       <c r="G62" t="n">
-        <v>176.3</v>
+        <v>179</v>
       </c>
       <c r="H62" t="n">
-        <v>98.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>104.5</v>
+        <v>114.41</v>
       </c>
       <c r="K62" t="n">
-        <v>-83.04000000000001</v>
+        <v>-95.5</v>
       </c>
       <c r="L62" t="n">
-        <v>133.47</v>
+        <v>149.03</v>
       </c>
     </row>
     <row r="63">
@@ -2686,25 +2686,25 @@
         <v>5.5</v>
       </c>
       <c r="F63" t="n">
-        <v>11.79</v>
+        <v>11.19</v>
       </c>
       <c r="G63" t="n">
-        <v>172.5</v>
+        <v>181.5</v>
       </c>
       <c r="H63" t="n">
         <v>88.90000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-51.72</v>
+        <v>17.03</v>
       </c>
       <c r="K63" t="n">
-        <v>75.34</v>
+        <v>-136.78</v>
       </c>
       <c r="L63" t="n">
-        <v>91.38</v>
+        <v>137.84</v>
       </c>
     </row>
     <row r="64">
@@ -2725,28 +2725,28 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>5.5</v>
+        <v>5.61</v>
       </c>
       <c r="F64" t="n">
-        <v>12.81</v>
+        <v>14.14</v>
       </c>
       <c r="G64" t="n">
-        <v>181.1</v>
+        <v>180.6</v>
       </c>
       <c r="H64" t="n">
-        <v>92.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-71.95999999999999</v>
+        <v>98.92</v>
       </c>
       <c r="K64" t="n">
-        <v>53.41</v>
+        <v>40</v>
       </c>
       <c r="L64" t="n">
-        <v>89.61</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="65">
@@ -2767,28 +2767,28 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>6.27</v>
+        <v>4.76</v>
       </c>
       <c r="F65" t="n">
-        <v>11.73</v>
+        <v>10.29</v>
       </c>
       <c r="G65" t="n">
-        <v>187.6</v>
+        <v>189.3</v>
       </c>
       <c r="H65" t="n">
-        <v>86.5</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I65" t="n">
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-109.8</v>
+        <v>-162.46</v>
       </c>
       <c r="K65" t="n">
-        <v>-190.61</v>
+        <v>51.88</v>
       </c>
       <c r="L65" t="n">
-        <v>219.97</v>
+        <v>170.54</v>
       </c>
     </row>
     <row r="66">
@@ -2809,28 +2809,28 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.71</v>
+        <v>5.53</v>
       </c>
       <c r="F66" t="n">
-        <v>12.12</v>
+        <v>14.14</v>
       </c>
       <c r="G66" t="n">
-        <v>197.3</v>
+        <v>186</v>
       </c>
       <c r="H66" t="n">
-        <v>88.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J66" t="n">
-        <v>51.48</v>
+        <v>-162.01</v>
       </c>
       <c r="K66" t="n">
-        <v>-170.87</v>
+        <v>32.81</v>
       </c>
       <c r="L66" t="n">
-        <v>178.46</v>
+        <v>165.3</v>
       </c>
     </row>
     <row r="67">
@@ -2851,28 +2851,28 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5.62</v>
+        <v>5.23</v>
       </c>
       <c r="F67" t="n">
-        <v>11.33</v>
+        <v>14.14</v>
       </c>
       <c r="G67" t="n">
-        <v>177.4</v>
+        <v>198.6</v>
       </c>
       <c r="H67" t="n">
-        <v>96.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>263.37</v>
+        <v>-56.2</v>
       </c>
       <c r="K67" t="n">
-        <v>-56.01</v>
+        <v>-248.06</v>
       </c>
       <c r="L67" t="n">
-        <v>269.26</v>
+        <v>254.34</v>
       </c>
     </row>
     <row r="68">
@@ -2893,28 +2893,28 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.69</v>
+        <v>5.33</v>
       </c>
       <c r="F68" t="n">
-        <v>11.85</v>
+        <v>12.96</v>
       </c>
       <c r="G68" t="n">
-        <v>184.2</v>
+        <v>190.3</v>
       </c>
       <c r="H68" t="n">
-        <v>89.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>68.98999999999999</v>
+        <v>-297.31</v>
       </c>
       <c r="K68" t="n">
-        <v>-224.71</v>
+        <v>58.03</v>
       </c>
       <c r="L68" t="n">
-        <v>235.07</v>
+        <v>302.92</v>
       </c>
     </row>
     <row r="69">
@@ -2935,28 +2935,28 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.74</v>
+        <v>6.27</v>
       </c>
       <c r="F69" t="n">
-        <v>12.55</v>
+        <v>14.14</v>
       </c>
       <c r="G69" t="n">
-        <v>184.6</v>
+        <v>171.9</v>
       </c>
       <c r="H69" t="n">
-        <v>89.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-206.1</v>
+        <v>-81.22</v>
       </c>
       <c r="K69" t="n">
-        <v>-310.8</v>
+        <v>352.93</v>
       </c>
       <c r="L69" t="n">
-        <v>372.93</v>
+        <v>362.15</v>
       </c>
     </row>
     <row r="70">
@@ -2977,28 +2977,28 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.54</v>
+        <v>5.4</v>
       </c>
       <c r="F70" t="n">
-        <v>12.97</v>
+        <v>11.85</v>
       </c>
       <c r="G70" t="n">
-        <v>184.3</v>
+        <v>188.3</v>
       </c>
       <c r="H70" t="n">
-        <v>98</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I70" t="n">
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>204.59</v>
+        <v>35</v>
       </c>
       <c r="K70" t="n">
-        <v>41.29</v>
+        <v>238.89</v>
       </c>
       <c r="L70" t="n">
-        <v>208.72</v>
+        <v>241.44</v>
       </c>
     </row>
     <row r="71">
@@ -3019,28 +3019,28 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.15</v>
+        <v>5.37</v>
       </c>
       <c r="F71" t="n">
-        <v>12.29</v>
+        <v>13.37</v>
       </c>
       <c r="G71" t="n">
-        <v>172.2</v>
+        <v>185</v>
       </c>
       <c r="H71" t="n">
-        <v>89.3</v>
+        <v>89.2</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-184.79</v>
+        <v>-506.15</v>
       </c>
       <c r="K71" t="n">
-        <v>-197.29</v>
+        <v>25.63</v>
       </c>
       <c r="L71" t="n">
-        <v>270.32</v>
+        <v>506.8</v>
       </c>
     </row>
     <row r="72">
@@ -3061,28 +3061,28 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.83</v>
+        <v>5.3</v>
       </c>
       <c r="F72" t="n">
-        <v>11.27</v>
+        <v>14.14</v>
       </c>
       <c r="G72" t="n">
-        <v>181.5</v>
+        <v>180</v>
       </c>
       <c r="H72" t="n">
-        <v>92.5</v>
+        <v>91.7</v>
       </c>
       <c r="I72" t="n">
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>88.03</v>
+        <v>397.62</v>
       </c>
       <c r="K72" t="n">
-        <v>-314.73</v>
+        <v>-24.1</v>
       </c>
       <c r="L72" t="n">
-        <v>326.8</v>
+        <v>398.35</v>
       </c>
     </row>
     <row r="73">
@@ -3103,28 +3103,28 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.99</v>
+        <v>6.45</v>
       </c>
       <c r="F73" t="n">
-        <v>12.46</v>
+        <v>14.14</v>
       </c>
       <c r="G73" t="n">
-        <v>189.1</v>
+        <v>190.7</v>
       </c>
       <c r="H73" t="n">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>295.87</v>
+        <v>-302.77</v>
       </c>
       <c r="K73" t="n">
-        <v>145.49</v>
+        <v>-421.14</v>
       </c>
       <c r="L73" t="n">
-        <v>329.71</v>
+        <v>518.6799999999999</v>
       </c>
     </row>
     <row r="74">
@@ -3145,28 +3145,28 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>6.05</v>
+        <v>5.36</v>
       </c>
       <c r="F74" t="n">
-        <v>12.62</v>
+        <v>14.14</v>
       </c>
       <c r="G74" t="n">
-        <v>181.9</v>
+        <v>182.3</v>
       </c>
       <c r="H74" t="n">
-        <v>88.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-50.95</v>
+        <v>-22.88</v>
       </c>
       <c r="K74" t="n">
-        <v>-51.96</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>72.77</v>
+        <v>84.48</v>
       </c>
     </row>
     <row r="75">
@@ -3187,28 +3187,28 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.68</v>
+        <v>4.67</v>
       </c>
       <c r="F75" t="n">
-        <v>11.99</v>
+        <v>10.62</v>
       </c>
       <c r="G75" t="n">
-        <v>179.1</v>
+        <v>178.4</v>
       </c>
       <c r="H75" t="n">
-        <v>81.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="I75" t="n">
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-64.26000000000001</v>
+        <v>85.19</v>
       </c>
       <c r="K75" t="n">
-        <v>-63.87</v>
+        <v>-23.32</v>
       </c>
       <c r="L75" t="n">
-        <v>90.59999999999999</v>
+        <v>88.31999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3229,28 +3229,28 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.49</v>
+        <v>5.16</v>
       </c>
       <c r="F76" t="n">
-        <v>12.28</v>
+        <v>14.14</v>
       </c>
       <c r="G76" t="n">
-        <v>177.5</v>
+        <v>178.4</v>
       </c>
       <c r="H76" t="n">
-        <v>89.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="I76" t="n">
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-65.08</v>
+        <v>-27.87</v>
       </c>
       <c r="K76" t="n">
-        <v>-63.54</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>90.95</v>
+        <v>78.83</v>
       </c>
     </row>
     <row r="77">
@@ -3271,28 +3271,28 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.81</v>
+        <v>5.58</v>
       </c>
       <c r="F77" t="n">
-        <v>11.89</v>
+        <v>12.6</v>
       </c>
       <c r="G77" t="n">
-        <v>191.3</v>
+        <v>176</v>
       </c>
       <c r="H77" t="n">
-        <v>90.5</v>
+        <v>89.8</v>
       </c>
       <c r="I77" t="n">
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-22.28</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-127.49</v>
+        <v>-59.61</v>
       </c>
       <c r="L77" t="n">
-        <v>129.43</v>
+        <v>103.49</v>
       </c>
     </row>
     <row r="78">
@@ -3313,28 +3313,28 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.98</v>
+        <v>5.19</v>
       </c>
       <c r="F78" t="n">
-        <v>12.26</v>
+        <v>14.14</v>
       </c>
       <c r="G78" t="n">
-        <v>177.5</v>
+        <v>173.7</v>
       </c>
       <c r="H78" t="n">
-        <v>89.2</v>
+        <v>81.5</v>
       </c>
       <c r="I78" t="n">
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-129.41</v>
+        <v>124.63</v>
       </c>
       <c r="K78" t="n">
-        <v>-88.5</v>
+        <v>12.98</v>
       </c>
       <c r="L78" t="n">
-        <v>156.77</v>
+        <v>125.3</v>
       </c>
     </row>
     <row r="79">
@@ -3355,28 +3355,28 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.24</v>
+        <v>5.9</v>
       </c>
       <c r="F79" t="n">
-        <v>11.85</v>
+        <v>13.31</v>
       </c>
       <c r="G79" t="n">
-        <v>176.6</v>
+        <v>190.1</v>
       </c>
       <c r="H79" t="n">
-        <v>93.7</v>
+        <v>90.8</v>
       </c>
       <c r="I79" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>9.73</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>75.90000000000001</v>
+        <v>3.76</v>
       </c>
       <c r="L79" t="n">
-        <v>76.53</v>
+        <v>73.36</v>
       </c>
     </row>
     <row r="80">
@@ -3397,28 +3397,28 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.55</v>
+        <v>6.3</v>
       </c>
       <c r="F80" t="n">
-        <v>12.62</v>
+        <v>12.75</v>
       </c>
       <c r="G80" t="n">
-        <v>191.9</v>
+        <v>195.2</v>
       </c>
       <c r="H80" t="n">
-        <v>91.2</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>-238.13</v>
+        <v>-254.6</v>
       </c>
       <c r="K80" t="n">
-        <v>90.84999999999999</v>
+        <v>-35.71</v>
       </c>
       <c r="L80" t="n">
-        <v>254.88</v>
+        <v>257.09</v>
       </c>
     </row>
     <row r="81">
@@ -3439,28 +3439,28 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>6.09</v>
+        <v>5.99</v>
       </c>
       <c r="F81" t="n">
-        <v>13.02</v>
+        <v>14.14</v>
       </c>
       <c r="G81" t="n">
-        <v>193.1</v>
+        <v>185.8</v>
       </c>
       <c r="H81" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I81" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-67.41</v>
+        <v>-128.76</v>
       </c>
       <c r="K81" t="n">
-        <v>-172.67</v>
+        <v>205.81</v>
       </c>
       <c r="L81" t="n">
-        <v>185.36</v>
+        <v>242.77</v>
       </c>
     </row>
     <row r="82">
@@ -3481,28 +3481,28 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.63</v>
+        <v>6.33</v>
       </c>
       <c r="F82" t="n">
-        <v>13.01</v>
+        <v>14.14</v>
       </c>
       <c r="G82" t="n">
-        <v>202.1</v>
+        <v>190.8</v>
       </c>
       <c r="H82" t="n">
-        <v>86.5</v>
+        <v>94</v>
       </c>
       <c r="I82" t="n">
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-140.23</v>
+        <v>204.99</v>
       </c>
       <c r="K82" t="n">
-        <v>104.72</v>
+        <v>44.03</v>
       </c>
       <c r="L82" t="n">
-        <v>175.02</v>
+        <v>209.66</v>
       </c>
     </row>
     <row r="83">
@@ -3523,28 +3523,28 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.9</v>
+        <v>5.94</v>
       </c>
       <c r="F83" t="n">
-        <v>12.55</v>
+        <v>14.14</v>
       </c>
       <c r="G83" t="n">
-        <v>191.6</v>
+        <v>181.3</v>
       </c>
       <c r="H83" t="n">
-        <v>93.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>-341.47</v>
+        <v>299.11</v>
       </c>
       <c r="K83" t="n">
-        <v>-24.25</v>
+        <v>237.66</v>
       </c>
       <c r="L83" t="n">
-        <v>342.33</v>
+        <v>382.03</v>
       </c>
     </row>
     <row r="84">
@@ -3565,28 +3565,28 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>5.44</v>
+        <v>6.19</v>
       </c>
       <c r="F84" t="n">
-        <v>12.84</v>
+        <v>14.14</v>
       </c>
       <c r="G84" t="n">
-        <v>199.5</v>
+        <v>187.3</v>
       </c>
       <c r="H84" t="n">
-        <v>97.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I84" t="n">
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>260.18</v>
+        <v>181.85</v>
       </c>
       <c r="K84" t="n">
-        <v>-35.94</v>
+        <v>-176.71</v>
       </c>
       <c r="L84" t="n">
-        <v>262.65</v>
+        <v>253.57</v>
       </c>
     </row>
     <row r="85">
@@ -3607,28 +3607,28 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.74</v>
+        <v>5.46</v>
       </c>
       <c r="F85" t="n">
-        <v>12.28</v>
+        <v>14.14</v>
       </c>
       <c r="G85" t="n">
-        <v>175.3</v>
+        <v>187.7</v>
       </c>
       <c r="H85" t="n">
-        <v>90.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>317.32</v>
+        <v>-51.56</v>
       </c>
       <c r="K85" t="n">
-        <v>119.41</v>
+        <v>-297.24</v>
       </c>
       <c r="L85" t="n">
-        <v>339.04</v>
+        <v>301.68</v>
       </c>
     </row>
     <row r="86">
@@ -3649,28 +3649,28 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>5.68</v>
+        <v>5.62</v>
       </c>
       <c r="F86" t="n">
-        <v>11.87</v>
+        <v>12.55</v>
       </c>
       <c r="G86" t="n">
-        <v>184.1</v>
+        <v>188.8</v>
       </c>
       <c r="H86" t="n">
-        <v>90.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J86" t="n">
-        <v>-228.41</v>
+        <v>-109.47</v>
       </c>
       <c r="K86" t="n">
-        <v>-448.38</v>
+        <v>357.46</v>
       </c>
       <c r="L86" t="n">
-        <v>503.2</v>
+        <v>373.85</v>
       </c>
     </row>
     <row r="87">
@@ -3691,28 +3691,28 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.88</v>
+        <v>6.1</v>
       </c>
       <c r="F87" t="n">
-        <v>12.72</v>
+        <v>14.14</v>
       </c>
       <c r="G87" t="n">
-        <v>193.7</v>
+        <v>188.5</v>
       </c>
       <c r="H87" t="n">
-        <v>90.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="I87" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>-7.69</v>
+        <v>464.78</v>
       </c>
       <c r="K87" t="n">
-        <v>-412.22</v>
+        <v>266.55</v>
       </c>
       <c r="L87" t="n">
-        <v>412.29</v>
+        <v>535.79</v>
       </c>
     </row>
     <row r="88">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.26</v>
+        <v>5.63</v>
       </c>
       <c r="F88" t="n">
-        <v>12.74</v>
+        <v>13.92</v>
       </c>
       <c r="G88" t="n">
-        <v>196</v>
+        <v>184.1</v>
       </c>
       <c r="H88" t="n">
-        <v>92.09999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="I88" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>-373.51</v>
+        <v>102.32</v>
       </c>
       <c r="K88" t="n">
-        <v>-159.12</v>
+        <v>-411.91</v>
       </c>
       <c r="L88" t="n">
-        <v>405.99</v>
+        <v>424.43</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-01.xlsx
+++ b/output/2024-04-01.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-29.03</v>
+        <v>-32.73</v>
       </c>
       <c r="K14" t="n">
-        <v>-64.43000000000001</v>
+        <v>-72.65000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>70.66</v>
+        <v>79.68000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-37.36</v>
+        <v>-42.13</v>
       </c>
       <c r="K15" t="n">
-        <v>60.78</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>71.34</v>
+        <v>80.45</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-82.02</v>
+        <v>-92.5</v>
       </c>
       <c r="K16" t="n">
-        <v>-63.26</v>
+        <v>-71.34</v>
       </c>
       <c r="L16" t="n">
-        <v>103.59</v>
+        <v>116.82</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>41.86</v>
+        <v>46.06</v>
       </c>
       <c r="K17" t="n">
-        <v>96.31</v>
+        <v>105.99</v>
       </c>
       <c r="L17" t="n">
-        <v>105.02</v>
+        <v>115.57</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>15.27</v>
+        <v>17.26</v>
       </c>
       <c r="K18" t="n">
-        <v>22.72</v>
+        <v>25.69</v>
       </c>
       <c r="L18" t="n">
-        <v>27.38</v>
+        <v>30.95</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>98.97</v>
+        <v>106.47</v>
       </c>
       <c r="K19" t="n">
-        <v>-71.65000000000001</v>
+        <v>-77.09</v>
       </c>
       <c r="L19" t="n">
-        <v>122.18</v>
+        <v>131.45</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>150.09</v>
+        <v>165.85</v>
       </c>
       <c r="K20" t="n">
-        <v>-49.63</v>
+        <v>-54.84</v>
       </c>
       <c r="L20" t="n">
-        <v>158.08</v>
+        <v>174.68</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-159.42</v>
+        <v>-181.17</v>
       </c>
       <c r="K21" t="n">
-        <v>-76.23999999999999</v>
+        <v>-86.64</v>
       </c>
       <c r="L21" t="n">
-        <v>176.72</v>
+        <v>200.82</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-101.13</v>
+        <v>-114.74</v>
       </c>
       <c r="K22" t="n">
-        <v>-98.84</v>
+        <v>-112.14</v>
       </c>
       <c r="L22" t="n">
-        <v>141.41</v>
+        <v>160.43</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>99.72</v>
+        <v>111.25</v>
       </c>
       <c r="K23" t="n">
-        <v>-130.44</v>
+        <v>-145.52</v>
       </c>
       <c r="L23" t="n">
-        <v>164.19</v>
+        <v>183.18</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>47.06</v>
+        <v>54.01</v>
       </c>
       <c r="K24" t="n">
-        <v>-228.42</v>
+        <v>-262.12</v>
       </c>
       <c r="L24" t="n">
-        <v>233.21</v>
+        <v>267.62</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-187.78</v>
+        <v>-213.95</v>
       </c>
       <c r="K25" t="n">
-        <v>-134.63</v>
+        <v>-153.39</v>
       </c>
       <c r="L25" t="n">
-        <v>231.05</v>
+        <v>263.26</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>263.38</v>
+        <v>292.48</v>
       </c>
       <c r="K26" t="n">
-        <v>-540.3200000000001</v>
+        <v>-600.03</v>
       </c>
       <c r="L26" t="n">
-        <v>601.1</v>
+        <v>667.52</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-405.39</v>
+        <v>-469.03</v>
       </c>
       <c r="K27" t="n">
-        <v>119.21</v>
+        <v>137.92</v>
       </c>
       <c r="L27" t="n">
-        <v>422.56</v>
+        <v>488.89</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>378.9</v>
+        <v>438.3</v>
       </c>
       <c r="K28" t="n">
-        <v>185.34</v>
+        <v>214.39</v>
       </c>
       <c r="L28" t="n">
-        <v>421.81</v>
+        <v>487.92</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>63.85</v>
+        <v>72.05</v>
       </c>
       <c r="K29" t="n">
-        <v>-80.78</v>
+        <v>-91.16</v>
       </c>
       <c r="L29" t="n">
-        <v>102.97</v>
+        <v>116.19</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>42.26</v>
+        <v>46.37</v>
       </c>
       <c r="K30" t="n">
-        <v>-96.51000000000001</v>
+        <v>-105.89</v>
       </c>
       <c r="L30" t="n">
-        <v>105.36</v>
+        <v>115.6</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="K31" t="n">
-        <v>-91.91</v>
+        <v>-103.79</v>
       </c>
       <c r="L31" t="n">
-        <v>91.94</v>
+        <v>103.82</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>75.55</v>
+        <v>84.28</v>
       </c>
       <c r="K32" t="n">
-        <v>-11.4</v>
+        <v>-12.72</v>
       </c>
       <c r="L32" t="n">
-        <v>76.41</v>
+        <v>85.23</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>44.15</v>
+        <v>49.82</v>
       </c>
       <c r="K33" t="n">
-        <v>82.78</v>
+        <v>93.41</v>
       </c>
       <c r="L33" t="n">
-        <v>93.81999999999999</v>
+        <v>105.87</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-93.38</v>
+        <v>-101.18</v>
       </c>
       <c r="K34" t="n">
-        <v>-28.12</v>
+        <v>-30.47</v>
       </c>
       <c r="L34" t="n">
-        <v>97.52</v>
+        <v>105.67</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-163.23</v>
+        <v>-185.14</v>
       </c>
       <c r="K35" t="n">
-        <v>-15.31</v>
+        <v>-17.37</v>
       </c>
       <c r="L35" t="n">
-        <v>163.95</v>
+        <v>185.95</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>251.35</v>
+        <v>284.92</v>
       </c>
       <c r="K36" t="n">
-        <v>-58.45</v>
+        <v>-66.25</v>
       </c>
       <c r="L36" t="n">
-        <v>258.05</v>
+        <v>292.53</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-157.58</v>
+        <v>-179.03</v>
       </c>
       <c r="K37" t="n">
-        <v>-105.56</v>
+        <v>-119.93</v>
       </c>
       <c r="L37" t="n">
-        <v>189.67</v>
+        <v>215.49</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-190.82</v>
+        <v>-219.22</v>
       </c>
       <c r="K38" t="n">
-        <v>34.52</v>
+        <v>39.66</v>
       </c>
       <c r="L38" t="n">
-        <v>193.91</v>
+        <v>222.78</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-191.72</v>
+        <v>-220.32</v>
       </c>
       <c r="K39" t="n">
-        <v>-145.95</v>
+        <v>-167.72</v>
       </c>
       <c r="L39" t="n">
-        <v>240.95</v>
+        <v>276.89</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>122.2</v>
+        <v>138.5</v>
       </c>
       <c r="K40" t="n">
-        <v>-363.42</v>
+        <v>-411.88</v>
       </c>
       <c r="L40" t="n">
-        <v>383.42</v>
+        <v>434.54</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>260.71</v>
+        <v>301.26</v>
       </c>
       <c r="K41" t="n">
-        <v>227.17</v>
+        <v>262.5</v>
       </c>
       <c r="L41" t="n">
-        <v>345.8</v>
+        <v>399.58</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-159.67</v>
+        <v>-185.09</v>
       </c>
       <c r="K42" t="n">
-        <v>-469.29</v>
+        <v>-543.99</v>
       </c>
       <c r="L42" t="n">
-        <v>495.71</v>
+        <v>574.61</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>192.62</v>
+        <v>222.85</v>
       </c>
       <c r="K43" t="n">
-        <v>-245.2</v>
+        <v>-283.68</v>
       </c>
       <c r="L43" t="n">
-        <v>311.81</v>
+        <v>360.74</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>56.24</v>
+        <v>61.01</v>
       </c>
       <c r="K44" t="n">
-        <v>-32.12</v>
+        <v>-34.85</v>
       </c>
       <c r="L44" t="n">
-        <v>64.77</v>
+        <v>70.26000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>88.28</v>
+        <v>99.53</v>
       </c>
       <c r="K45" t="n">
-        <v>25.53</v>
+        <v>28.78</v>
       </c>
       <c r="L45" t="n">
-        <v>91.90000000000001</v>
+        <v>103.61</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>77.02</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-65.62</v>
+        <v>-74.04000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>101.18</v>
+        <v>114.16</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-66.08</v>
+        <v>-74.5</v>
       </c>
       <c r="K47" t="n">
-        <v>-64.54000000000001</v>
+        <v>-72.77</v>
       </c>
       <c r="L47" t="n">
-        <v>92.37</v>
+        <v>104.15</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>33.83</v>
+        <v>37.34</v>
       </c>
       <c r="K48" t="n">
-        <v>88.88</v>
+        <v>98.11</v>
       </c>
       <c r="L48" t="n">
-        <v>95.09999999999999</v>
+        <v>104.97</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>13.76</v>
+        <v>15.53</v>
       </c>
       <c r="K49" t="n">
-        <v>83.54000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>84.66</v>
+        <v>95.56</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>130.92</v>
+        <v>146.46</v>
       </c>
       <c r="K50" t="n">
-        <v>73.15000000000001</v>
+        <v>81.83</v>
       </c>
       <c r="L50" t="n">
-        <v>149.97</v>
+        <v>167.77</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-45.93</v>
+        <v>-52.05</v>
       </c>
       <c r="K51" t="n">
-        <v>-257.81</v>
+        <v>-292.14</v>
       </c>
       <c r="L51" t="n">
-        <v>261.87</v>
+        <v>296.74</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-51.72</v>
+        <v>-58.73</v>
       </c>
       <c r="K52" t="n">
-        <v>215.77</v>
+        <v>245</v>
       </c>
       <c r="L52" t="n">
-        <v>221.89</v>
+        <v>251.94</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>234.97</v>
+        <v>270.1</v>
       </c>
       <c r="K53" t="n">
-        <v>-16.64</v>
+        <v>-19.12</v>
       </c>
       <c r="L53" t="n">
-        <v>235.55</v>
+        <v>270.78</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>275.87</v>
+        <v>312.99</v>
       </c>
       <c r="K54" t="n">
-        <v>-120.75</v>
+        <v>-136.99</v>
       </c>
       <c r="L54" t="n">
-        <v>301.14</v>
+        <v>341.66</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-236.84</v>
+        <v>-265.12</v>
       </c>
       <c r="K55" t="n">
-        <v>-184.08</v>
+        <v>-206.06</v>
       </c>
       <c r="L55" t="n">
-        <v>299.97</v>
+        <v>335.78</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>-224.6</v>
+        <v>-253.86</v>
       </c>
       <c r="K56" t="n">
-        <v>-523.5</v>
+        <v>-591.7</v>
       </c>
       <c r="L56" t="n">
-        <v>569.65</v>
+        <v>643.86</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>306.12</v>
+        <v>354.7</v>
       </c>
       <c r="K57" t="n">
-        <v>124.08</v>
+        <v>143.77</v>
       </c>
       <c r="L57" t="n">
-        <v>330.31</v>
+        <v>382.73</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-241.47</v>
+        <v>-276.77</v>
       </c>
       <c r="K58" t="n">
-        <v>-438.21</v>
+        <v>-502.28</v>
       </c>
       <c r="L58" t="n">
-        <v>500.33</v>
+        <v>573.48</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-61.43</v>
+        <v>-69.38</v>
       </c>
       <c r="K59" t="n">
-        <v>66.48</v>
+        <v>75.08</v>
       </c>
       <c r="L59" t="n">
-        <v>90.52</v>
+        <v>102.23</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>29.29</v>
+        <v>31.73</v>
       </c>
       <c r="K60" t="n">
-        <v>-106.42</v>
+        <v>-115.28</v>
       </c>
       <c r="L60" t="n">
-        <v>110.37</v>
+        <v>119.56</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-88.39</v>
+        <v>-95.47</v>
       </c>
       <c r="K61" t="n">
-        <v>-27.5</v>
+        <v>-29.7</v>
       </c>
       <c r="L61" t="n">
-        <v>92.56999999999999</v>
+        <v>99.98</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>114.41</v>
+        <v>129.18</v>
       </c>
       <c r="K62" t="n">
-        <v>-95.5</v>
+        <v>-107.82</v>
       </c>
       <c r="L62" t="n">
-        <v>149.03</v>
+        <v>168.26</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>17.03</v>
+        <v>19.18</v>
       </c>
       <c r="K63" t="n">
-        <v>-136.78</v>
+        <v>-154.12</v>
       </c>
       <c r="L63" t="n">
-        <v>137.84</v>
+        <v>155.3</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>98.92</v>
+        <v>110.21</v>
       </c>
       <c r="K64" t="n">
-        <v>40</v>
+        <v>44.56</v>
       </c>
       <c r="L64" t="n">
-        <v>106.7</v>
+        <v>118.88</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-162.46</v>
+        <v>-176.82</v>
       </c>
       <c r="K65" t="n">
-        <v>51.88</v>
+        <v>56.47</v>
       </c>
       <c r="L65" t="n">
-        <v>170.54</v>
+        <v>185.62</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>17</v>
       </c>
       <c r="J66" t="n">
-        <v>-162.01</v>
+        <v>-181.17</v>
       </c>
       <c r="K66" t="n">
-        <v>32.81</v>
+        <v>36.69</v>
       </c>
       <c r="L66" t="n">
-        <v>165.3</v>
+        <v>184.85</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-56.2</v>
+        <v>-63.72</v>
       </c>
       <c r="K67" t="n">
-        <v>-248.06</v>
+        <v>-281.23</v>
       </c>
       <c r="L67" t="n">
-        <v>254.34</v>
+        <v>288.36</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-297.31</v>
+        <v>-341.69</v>
       </c>
       <c r="K68" t="n">
-        <v>58.03</v>
+        <v>66.69</v>
       </c>
       <c r="L68" t="n">
-        <v>302.92</v>
+        <v>348.14</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-81.22</v>
+        <v>-93.52</v>
       </c>
       <c r="K69" t="n">
-        <v>352.93</v>
+        <v>406.39</v>
       </c>
       <c r="L69" t="n">
-        <v>362.15</v>
+        <v>417.01</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>35</v>
+        <v>40.23</v>
       </c>
       <c r="K70" t="n">
-        <v>238.89</v>
+        <v>274.6</v>
       </c>
       <c r="L70" t="n">
-        <v>241.44</v>
+        <v>277.53</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-506.15</v>
+        <v>-587.7</v>
       </c>
       <c r="K71" t="n">
-        <v>25.63</v>
+        <v>29.76</v>
       </c>
       <c r="L71" t="n">
-        <v>506.8</v>
+        <v>588.45</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>397.62</v>
+        <v>461.52</v>
       </c>
       <c r="K72" t="n">
-        <v>-24.1</v>
+        <v>-27.97</v>
       </c>
       <c r="L72" t="n">
-        <v>398.35</v>
+        <v>462.36</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>-302.77</v>
+        <v>-348.31</v>
       </c>
       <c r="K73" t="n">
-        <v>-421.14</v>
+        <v>-484.5</v>
       </c>
       <c r="L73" t="n">
-        <v>518.6799999999999</v>
+        <v>596.71</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-22.88</v>
+        <v>-25.09</v>
       </c>
       <c r="K74" t="n">
-        <v>81.31999999999999</v>
+        <v>89.17</v>
       </c>
       <c r="L74" t="n">
-        <v>84.48</v>
+        <v>92.63</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>85.19</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>-23.32</v>
+        <v>-26.36</v>
       </c>
       <c r="L75" t="n">
-        <v>88.31999999999999</v>
+        <v>99.83</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-27.87</v>
+        <v>-31.44</v>
       </c>
       <c r="K76" t="n">
-        <v>73.73999999999999</v>
+        <v>83.17</v>
       </c>
       <c r="L76" t="n">
-        <v>78.83</v>
+        <v>88.92</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>84.59999999999999</v>
+        <v>94.58</v>
       </c>
       <c r="K77" t="n">
-        <v>-59.61</v>
+        <v>-66.64</v>
       </c>
       <c r="L77" t="n">
-        <v>103.49</v>
+        <v>115.7</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>124.63</v>
+        <v>140.59</v>
       </c>
       <c r="K78" t="n">
-        <v>12.98</v>
+        <v>14.64</v>
       </c>
       <c r="L78" t="n">
-        <v>125.3</v>
+        <v>141.35</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>73.26000000000001</v>
+        <v>77.55</v>
       </c>
       <c r="K79" t="n">
-        <v>3.76</v>
+        <v>3.98</v>
       </c>
       <c r="L79" t="n">
-        <v>73.36</v>
+        <v>77.65000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>-254.6</v>
+        <v>-284.48</v>
       </c>
       <c r="K80" t="n">
-        <v>-35.71</v>
+        <v>-39.9</v>
       </c>
       <c r="L80" t="n">
-        <v>257.09</v>
+        <v>287.26</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-128.76</v>
+        <v>-139.83</v>
       </c>
       <c r="K81" t="n">
-        <v>205.81</v>
+        <v>223.5</v>
       </c>
       <c r="L81" t="n">
-        <v>242.77</v>
+        <v>263.63</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>204.99</v>
+        <v>225.85</v>
       </c>
       <c r="K82" t="n">
-        <v>44.03</v>
+        <v>48.51</v>
       </c>
       <c r="L82" t="n">
-        <v>209.66</v>
+        <v>231</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>299.11</v>
+        <v>334.9</v>
       </c>
       <c r="K83" t="n">
-        <v>237.66</v>
+        <v>266.1</v>
       </c>
       <c r="L83" t="n">
-        <v>382.03</v>
+        <v>427.74</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>181.85</v>
+        <v>209.37</v>
       </c>
       <c r="K84" t="n">
-        <v>-176.71</v>
+        <v>-203.45</v>
       </c>
       <c r="L84" t="n">
-        <v>253.57</v>
+        <v>291.94</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-51.56</v>
+        <v>-58.48</v>
       </c>
       <c r="K85" t="n">
-        <v>-297.24</v>
+        <v>-337.17</v>
       </c>
       <c r="L85" t="n">
-        <v>301.68</v>
+        <v>342.21</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>17</v>
       </c>
       <c r="J86" t="n">
-        <v>-109.47</v>
+        <v>-125.56</v>
       </c>
       <c r="K86" t="n">
-        <v>357.46</v>
+        <v>410</v>
       </c>
       <c r="L86" t="n">
-        <v>373.85</v>
+        <v>428.79</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>464.78</v>
+        <v>534.09</v>
       </c>
       <c r="K87" t="n">
-        <v>266.55</v>
+        <v>306.3</v>
       </c>
       <c r="L87" t="n">
-        <v>535.79</v>
+        <v>615.6799999999999</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>102.32</v>
+        <v>117.36</v>
       </c>
       <c r="K88" t="n">
-        <v>-411.91</v>
+        <v>-472.47</v>
       </c>
       <c r="L88" t="n">
-        <v>424.43</v>
+        <v>486.83</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-01.xlsx
+++ b/output/2024-04-01.xlsx
@@ -634,19 +634,19 @@
         <v>198.9</v>
       </c>
       <c r="H14" t="n">
-        <v>85.09999999999999</v>
+        <v>32.8</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>-32.73</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-72.65000000000001</v>
+        <v>-68.16</v>
       </c>
       <c r="L14" t="n">
-        <v>79.68000000000001</v>
+        <v>114.98</v>
       </c>
     </row>
     <row r="15">
@@ -667,28 +667,28 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>5.21</v>
+        <v>4.28</v>
       </c>
       <c r="F15" t="n">
-        <v>13.63</v>
+        <v>8.98</v>
       </c>
       <c r="G15" t="n">
-        <v>182.5</v>
+        <v>188.4</v>
       </c>
       <c r="H15" t="n">
-        <v>93.2</v>
+        <v>56.9</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-42.13</v>
+        <v>-33.44</v>
       </c>
       <c r="K15" t="n">
-        <v>68.54000000000001</v>
+        <v>-86.08</v>
       </c>
       <c r="L15" t="n">
-        <v>80.45</v>
+        <v>92.34</v>
       </c>
     </row>
     <row r="16">
@@ -709,28 +709,28 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5.2</v>
+        <v>4.16</v>
       </c>
       <c r="F16" t="n">
-        <v>12.53</v>
+        <v>8.81</v>
       </c>
       <c r="G16" t="n">
-        <v>185.3</v>
+        <v>175.1</v>
       </c>
       <c r="H16" t="n">
-        <v>82.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-92.5</v>
+        <v>66.02</v>
       </c>
       <c r="K16" t="n">
-        <v>-71.34</v>
+        <v>-53.95</v>
       </c>
       <c r="L16" t="n">
-        <v>116.82</v>
+        <v>85.26000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -751,28 +751,28 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.54</v>
+        <v>4.89</v>
       </c>
       <c r="F17" t="n">
-        <v>8.279999999999999</v>
+        <v>10.74</v>
       </c>
       <c r="G17" t="n">
-        <v>183.1</v>
+        <v>187.6</v>
       </c>
       <c r="H17" t="n">
-        <v>88.7</v>
+        <v>55.7</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>46.06</v>
+        <v>-118.89</v>
       </c>
       <c r="K17" t="n">
-        <v>105.99</v>
+        <v>-87.48</v>
       </c>
       <c r="L17" t="n">
-        <v>115.57</v>
+        <v>147.61</v>
       </c>
     </row>
     <row r="18">
@@ -793,28 +793,28 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.63</v>
+        <v>4.35</v>
       </c>
       <c r="F18" t="n">
-        <v>10.07</v>
+        <v>7.67</v>
       </c>
       <c r="G18" t="n">
-        <v>187.1</v>
+        <v>188.2</v>
       </c>
       <c r="H18" t="n">
-        <v>91.59999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>17.26</v>
+        <v>-57.81</v>
       </c>
       <c r="K18" t="n">
-        <v>25.69</v>
+        <v>-88.75</v>
       </c>
       <c r="L18" t="n">
-        <v>30.95</v>
+        <v>105.92</v>
       </c>
     </row>
     <row r="19">
@@ -835,28 +835,28 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>5.69</v>
+        <v>4.49</v>
       </c>
       <c r="F19" t="n">
-        <v>11.58</v>
+        <v>11.71</v>
       </c>
       <c r="G19" t="n">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H19" t="n">
-        <v>84.7</v>
+        <v>25</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>106.47</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-77.09</v>
+        <v>68.36</v>
       </c>
       <c r="L19" t="n">
-        <v>131.45</v>
+        <v>104.23</v>
       </c>
     </row>
     <row r="20">
@@ -877,28 +877,28 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.47</v>
+        <v>4.59</v>
       </c>
       <c r="F20" t="n">
-        <v>9.859999999999999</v>
+        <v>12.84</v>
       </c>
       <c r="G20" t="n">
-        <v>181.5</v>
+        <v>183.7</v>
       </c>
       <c r="H20" t="n">
-        <v>86.40000000000001</v>
+        <v>40.4</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>165.85</v>
+        <v>35.31</v>
       </c>
       <c r="K20" t="n">
-        <v>-54.84</v>
+        <v>-164.6</v>
       </c>
       <c r="L20" t="n">
-        <v>174.68</v>
+        <v>168.35</v>
       </c>
     </row>
     <row r="21">
@@ -919,28 +919,28 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.05</v>
+        <v>4.64</v>
       </c>
       <c r="F21" t="n">
-        <v>12.21</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>200.4</v>
+        <v>186.9</v>
       </c>
       <c r="H21" t="n">
-        <v>86.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-181.17</v>
+        <v>144.42</v>
       </c>
       <c r="K21" t="n">
-        <v>-86.64</v>
+        <v>109.35</v>
       </c>
       <c r="L21" t="n">
-        <v>200.82</v>
+        <v>181.15</v>
       </c>
     </row>
     <row r="22">
@@ -961,28 +961,28 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.89</v>
+        <v>5.86</v>
       </c>
       <c r="F22" t="n">
-        <v>9.67</v>
+        <v>14.14</v>
       </c>
       <c r="G22" t="n">
-        <v>191.9</v>
+        <v>179.6</v>
       </c>
       <c r="H22" t="n">
-        <v>89.59999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>-114.74</v>
+        <v>-171.04</v>
       </c>
       <c r="K22" t="n">
-        <v>-112.14</v>
+        <v>115.71</v>
       </c>
       <c r="L22" t="n">
-        <v>160.43</v>
+        <v>206.5</v>
       </c>
     </row>
     <row r="23">
@@ -1003,28 +1003,28 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.58</v>
+        <v>4.1</v>
       </c>
       <c r="F23" t="n">
-        <v>10.75</v>
+        <v>9.98</v>
       </c>
       <c r="G23" t="n">
-        <v>193.8</v>
+        <v>187.8</v>
       </c>
       <c r="H23" t="n">
-        <v>92.5</v>
+        <v>50.7</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>111.25</v>
+        <v>-224.26</v>
       </c>
       <c r="K23" t="n">
-        <v>-145.52</v>
+        <v>-61.19</v>
       </c>
       <c r="L23" t="n">
-        <v>183.18</v>
+        <v>232.46</v>
       </c>
     </row>
     <row r="24">
@@ -1045,28 +1045,28 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.8</v>
+        <v>3.79</v>
       </c>
       <c r="F24" t="n">
-        <v>11.4</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>202.4</v>
+        <v>182.7</v>
       </c>
       <c r="H24" t="n">
-        <v>90.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>54.01</v>
+        <v>174.75</v>
       </c>
       <c r="K24" t="n">
-        <v>-262.12</v>
+        <v>-204.42</v>
       </c>
       <c r="L24" t="n">
-        <v>267.62</v>
+        <v>268.93</v>
       </c>
     </row>
     <row r="25">
@@ -1087,28 +1087,28 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.37</v>
+        <v>4.78</v>
       </c>
       <c r="F25" t="n">
-        <v>10.35</v>
+        <v>10.43</v>
       </c>
       <c r="G25" t="n">
-        <v>193.1</v>
+        <v>199.6</v>
       </c>
       <c r="H25" t="n">
-        <v>83.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-213.95</v>
+        <v>-342.19</v>
       </c>
       <c r="K25" t="n">
-        <v>-153.39</v>
+        <v>88.05</v>
       </c>
       <c r="L25" t="n">
-        <v>263.26</v>
+        <v>353.34</v>
       </c>
     </row>
     <row r="26">
@@ -1129,28 +1129,28 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.93</v>
+        <v>4.85</v>
       </c>
       <c r="F26" t="n">
-        <v>10.86</v>
+        <v>12.51</v>
       </c>
       <c r="G26" t="n">
-        <v>183.7</v>
+        <v>192</v>
       </c>
       <c r="H26" t="n">
-        <v>90.2</v>
+        <v>36.6</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>292.48</v>
+        <v>-18.76</v>
       </c>
       <c r="K26" t="n">
-        <v>-600.03</v>
+        <v>-427.7</v>
       </c>
       <c r="L26" t="n">
-        <v>667.52</v>
+        <v>428.11</v>
       </c>
     </row>
     <row r="27">
@@ -1171,28 +1171,28 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.74</v>
+        <v>4.22</v>
       </c>
       <c r="F27" t="n">
-        <v>11.29</v>
+        <v>7.99</v>
       </c>
       <c r="G27" t="n">
-        <v>188.3</v>
+        <v>190.8</v>
       </c>
       <c r="H27" t="n">
-        <v>83.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I27" t="n">
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-469.03</v>
+        <v>-311.85</v>
       </c>
       <c r="K27" t="n">
-        <v>137.92</v>
+        <v>-18.98</v>
       </c>
       <c r="L27" t="n">
-        <v>488.89</v>
+        <v>312.42</v>
       </c>
     </row>
     <row r="28">
@@ -1213,28 +1213,28 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.71</v>
+        <v>4.59</v>
       </c>
       <c r="F28" t="n">
-        <v>9.289999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="G28" t="n">
-        <v>196.1</v>
+        <v>188.1</v>
       </c>
       <c r="H28" t="n">
-        <v>89.3</v>
+        <v>14.3</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>438.3</v>
+        <v>392.69</v>
       </c>
       <c r="K28" t="n">
-        <v>214.39</v>
+        <v>-162.85</v>
       </c>
       <c r="L28" t="n">
-        <v>487.92</v>
+        <v>425.11</v>
       </c>
     </row>
     <row r="29">
@@ -1255,28 +1255,28 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>5.06</v>
+        <v>4.27</v>
       </c>
       <c r="F29" t="n">
-        <v>12.31</v>
+        <v>10.38</v>
       </c>
       <c r="G29" t="n">
-        <v>186.2</v>
+        <v>192.2</v>
       </c>
       <c r="H29" t="n">
-        <v>89.40000000000001</v>
+        <v>48.7</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>72.05</v>
+        <v>24.66</v>
       </c>
       <c r="K29" t="n">
-        <v>-91.16</v>
+        <v>-79.41</v>
       </c>
       <c r="L29" t="n">
-        <v>116.19</v>
+        <v>83.15000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1297,28 +1297,28 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>5.21</v>
+        <v>4.84</v>
       </c>
       <c r="F30" t="n">
-        <v>12.14</v>
+        <v>12.61</v>
       </c>
       <c r="G30" t="n">
-        <v>191.7</v>
+        <v>184.7</v>
       </c>
       <c r="H30" t="n">
-        <v>95.3</v>
+        <v>39</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>46.37</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>-105.89</v>
+        <v>29.34</v>
       </c>
       <c r="L30" t="n">
-        <v>115.6</v>
+        <v>89.45999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1339,28 +1339,28 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.88</v>
+        <v>5.43</v>
       </c>
       <c r="F31" t="n">
-        <v>10.55</v>
+        <v>13.77</v>
       </c>
       <c r="G31" t="n">
-        <v>180.1</v>
+        <v>184.1</v>
       </c>
       <c r="H31" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>2.65</v>
+        <v>-10.64</v>
       </c>
       <c r="K31" t="n">
-        <v>-103.79</v>
+        <v>-115.5</v>
       </c>
       <c r="L31" t="n">
-        <v>103.82</v>
+        <v>115.98</v>
       </c>
     </row>
     <row r="32">
@@ -1381,28 +1381,28 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.67</v>
+        <v>4.44</v>
       </c>
       <c r="F32" t="n">
-        <v>9.91</v>
+        <v>9.17</v>
       </c>
       <c r="G32" t="n">
-        <v>190.6</v>
+        <v>189.9</v>
       </c>
       <c r="H32" t="n">
-        <v>95.2</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>84.28</v>
+        <v>-35.01</v>
       </c>
       <c r="K32" t="n">
-        <v>-12.72</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>85.23</v>
+        <v>76.48999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1423,28 +1423,28 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>5.11</v>
+        <v>5.22</v>
       </c>
       <c r="F33" t="n">
-        <v>8.92</v>
+        <v>11.19</v>
       </c>
       <c r="G33" t="n">
-        <v>173</v>
+        <v>187.5</v>
       </c>
       <c r="H33" t="n">
-        <v>93</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I33" t="n">
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>49.82</v>
+        <v>-133.15</v>
       </c>
       <c r="K33" t="n">
-        <v>93.41</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>105.87</v>
+        <v>151.87</v>
       </c>
     </row>
     <row r="34">
@@ -1465,28 +1465,28 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.73</v>
+        <v>5.46</v>
       </c>
       <c r="F34" t="n">
-        <v>12.54</v>
+        <v>13.9</v>
       </c>
       <c r="G34" t="n">
-        <v>187.6</v>
+        <v>175.3</v>
       </c>
       <c r="H34" t="n">
-        <v>91.5</v>
+        <v>20.3</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-101.18</v>
+        <v>-146.3</v>
       </c>
       <c r="K34" t="n">
-        <v>-30.47</v>
+        <v>37.3</v>
       </c>
       <c r="L34" t="n">
-        <v>105.67</v>
+        <v>150.98</v>
       </c>
     </row>
     <row r="35">
@@ -1507,28 +1507,28 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.91</v>
+        <v>4.94</v>
       </c>
       <c r="F35" t="n">
-        <v>12.89</v>
+        <v>11.38</v>
       </c>
       <c r="G35" t="n">
-        <v>197.6</v>
+        <v>179</v>
       </c>
       <c r="H35" t="n">
-        <v>90.09999999999999</v>
+        <v>62</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-185.14</v>
+        <v>-74.09999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>-17.37</v>
+        <v>-146.42</v>
       </c>
       <c r="L35" t="n">
-        <v>185.95</v>
+        <v>164.1</v>
       </c>
     </row>
     <row r="36">
@@ -1549,28 +1549,28 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>5.32</v>
+        <v>4.44</v>
       </c>
       <c r="F36" t="n">
-        <v>14.14</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>192.4</v>
+        <v>184.7</v>
       </c>
       <c r="H36" t="n">
-        <v>94</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>284.92</v>
+        <v>-125.77</v>
       </c>
       <c r="K36" t="n">
-        <v>-66.25</v>
+        <v>-78.62</v>
       </c>
       <c r="L36" t="n">
-        <v>292.53</v>
+        <v>148.32</v>
       </c>
     </row>
     <row r="37">
@@ -1591,28 +1591,28 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.21</v>
+        <v>5.13</v>
       </c>
       <c r="F37" t="n">
-        <v>9.199999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="G37" t="n">
-        <v>172.9</v>
+        <v>194.2</v>
       </c>
       <c r="H37" t="n">
-        <v>95.8</v>
+        <v>30.6</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-179.03</v>
+        <v>145.55</v>
       </c>
       <c r="K37" t="n">
-        <v>-119.93</v>
+        <v>-152.41</v>
       </c>
       <c r="L37" t="n">
-        <v>215.49</v>
+        <v>210.74</v>
       </c>
     </row>
     <row r="38">
@@ -1633,28 +1633,28 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>5.19</v>
+        <v>5.84</v>
       </c>
       <c r="F38" t="n">
-        <v>12.58</v>
+        <v>13.94</v>
       </c>
       <c r="G38" t="n">
-        <v>167.2</v>
+        <v>178.9</v>
       </c>
       <c r="H38" t="n">
-        <v>84.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-219.22</v>
+        <v>-227.68</v>
       </c>
       <c r="K38" t="n">
-        <v>39.66</v>
+        <v>-265.55</v>
       </c>
       <c r="L38" t="n">
-        <v>222.78</v>
+        <v>349.79</v>
       </c>
     </row>
     <row r="39">
@@ -1675,28 +1675,28 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>5.3</v>
+        <v>5.16</v>
       </c>
       <c r="F39" t="n">
-        <v>11.51</v>
+        <v>14.14</v>
       </c>
       <c r="G39" t="n">
-        <v>187.5</v>
+        <v>188.5</v>
       </c>
       <c r="H39" t="n">
-        <v>93.59999999999999</v>
+        <v>40.9</v>
       </c>
       <c r="I39" t="n">
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-220.32</v>
+        <v>-196.76</v>
       </c>
       <c r="K39" t="n">
-        <v>-167.72</v>
+        <v>-226.55</v>
       </c>
       <c r="L39" t="n">
-        <v>276.89</v>
+        <v>300.06</v>
       </c>
     </row>
     <row r="40">
@@ -1717,28 +1717,28 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.11</v>
+        <v>4.59</v>
       </c>
       <c r="F40" t="n">
-        <v>11.46</v>
+        <v>14.14</v>
       </c>
       <c r="G40" t="n">
-        <v>183.6</v>
+        <v>197.2</v>
       </c>
       <c r="H40" t="n">
-        <v>92.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>138.5</v>
+        <v>179.39</v>
       </c>
       <c r="K40" t="n">
-        <v>-411.88</v>
+        <v>-180.47</v>
       </c>
       <c r="L40" t="n">
-        <v>434.54</v>
+        <v>254.46</v>
       </c>
     </row>
     <row r="41">
@@ -1759,28 +1759,28 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.56</v>
+        <v>4.73</v>
       </c>
       <c r="F41" t="n">
-        <v>7.43</v>
+        <v>12.05</v>
       </c>
       <c r="G41" t="n">
-        <v>183.4</v>
+        <v>188.6</v>
       </c>
       <c r="H41" t="n">
-        <v>93.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I41" t="n">
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>301.26</v>
+        <v>135.37</v>
       </c>
       <c r="K41" t="n">
-        <v>262.5</v>
+        <v>-293.87</v>
       </c>
       <c r="L41" t="n">
-        <v>399.58</v>
+        <v>323.55</v>
       </c>
     </row>
     <row r="42">
@@ -1801,28 +1801,28 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5.05</v>
+        <v>4.29</v>
       </c>
       <c r="F42" t="n">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="G42" t="n">
-        <v>186.4</v>
+        <v>179.9</v>
       </c>
       <c r="H42" t="n">
-        <v>96</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I42" t="n">
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-185.09</v>
+        <v>-156.51</v>
       </c>
       <c r="K42" t="n">
-        <v>-543.99</v>
+        <v>-230.8</v>
       </c>
       <c r="L42" t="n">
-        <v>574.61</v>
+        <v>278.87</v>
       </c>
     </row>
     <row r="43">
@@ -1843,28 +1843,28 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.73</v>
+        <v>4.96</v>
       </c>
       <c r="F43" t="n">
-        <v>12.35</v>
+        <v>11.62</v>
       </c>
       <c r="G43" t="n">
-        <v>188.8</v>
+        <v>191</v>
       </c>
       <c r="H43" t="n">
-        <v>85.09999999999999</v>
+        <v>67</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>222.85</v>
+        <v>-434.26</v>
       </c>
       <c r="K43" t="n">
-        <v>-283.68</v>
+        <v>-98.65000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>360.74</v>
+        <v>445.33</v>
       </c>
     </row>
     <row r="44">
@@ -1885,28 +1885,28 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.42</v>
+        <v>5.07</v>
       </c>
       <c r="F44" t="n">
-        <v>9.68</v>
+        <v>11.46</v>
       </c>
       <c r="G44" t="n">
-        <v>177.1</v>
+        <v>186.8</v>
       </c>
       <c r="H44" t="n">
-        <v>88.5</v>
+        <v>89.3</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>61.01</v>
+        <v>19.79</v>
       </c>
       <c r="K44" t="n">
-        <v>-34.85</v>
+        <v>-100.22</v>
       </c>
       <c r="L44" t="n">
-        <v>70.26000000000001</v>
+        <v>102.16</v>
       </c>
     </row>
     <row r="45">
@@ -1927,28 +1927,28 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>5.28</v>
+        <v>4.53</v>
       </c>
       <c r="F45" t="n">
-        <v>14.14</v>
+        <v>10.04</v>
       </c>
       <c r="G45" t="n">
-        <v>194.2</v>
+        <v>179.4</v>
       </c>
       <c r="H45" t="n">
-        <v>84.7</v>
+        <v>12.3</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>99.53</v>
+        <v>-90.84999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>28.78</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>103.61</v>
+        <v>91.23</v>
       </c>
     </row>
     <row r="46">
@@ -1969,28 +1969,28 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>5.1</v>
+        <v>5.24</v>
       </c>
       <c r="F46" t="n">
-        <v>14.14</v>
+        <v>13.54</v>
       </c>
       <c r="G46" t="n">
-        <v>186.3</v>
+        <v>188.8</v>
       </c>
       <c r="H46" t="n">
-        <v>98.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>86.90000000000001</v>
+        <v>-136.02</v>
       </c>
       <c r="K46" t="n">
-        <v>-74.04000000000001</v>
+        <v>-61.4</v>
       </c>
       <c r="L46" t="n">
-        <v>114.16</v>
+        <v>149.24</v>
       </c>
     </row>
     <row r="47">
@@ -2011,28 +2011,28 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5.31</v>
+        <v>4.78</v>
       </c>
       <c r="F47" t="n">
-        <v>13.19</v>
+        <v>10.19</v>
       </c>
       <c r="G47" t="n">
-        <v>169.1</v>
+        <v>186.1</v>
       </c>
       <c r="H47" t="n">
-        <v>84.2</v>
+        <v>66.8</v>
       </c>
       <c r="I47" t="n">
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-74.5</v>
+        <v>-121.13</v>
       </c>
       <c r="K47" t="n">
-        <v>-72.77</v>
+        <v>-80.02</v>
       </c>
       <c r="L47" t="n">
-        <v>104.15</v>
+        <v>145.18</v>
       </c>
     </row>
     <row r="48">
@@ -2053,28 +2053,28 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>5.95</v>
+        <v>5.16</v>
       </c>
       <c r="F48" t="n">
-        <v>12.91</v>
+        <v>11.1</v>
       </c>
       <c r="G48" t="n">
-        <v>182.4</v>
+        <v>174.1</v>
       </c>
       <c r="H48" t="n">
-        <v>92</v>
+        <v>63.9</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>37.34</v>
+        <v>-108.39</v>
       </c>
       <c r="K48" t="n">
-        <v>98.11</v>
+        <v>94.13</v>
       </c>
       <c r="L48" t="n">
-        <v>104.97</v>
+        <v>143.56</v>
       </c>
     </row>
     <row r="49">
@@ -2095,28 +2095,28 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>5.06</v>
+        <v>4.73</v>
       </c>
       <c r="F49" t="n">
-        <v>10.52</v>
+        <v>11.7</v>
       </c>
       <c r="G49" t="n">
-        <v>187.5</v>
+        <v>187.7</v>
       </c>
       <c r="H49" t="n">
-        <v>100</v>
+        <v>35.7</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>15.53</v>
+        <v>-41.53</v>
       </c>
       <c r="K49" t="n">
-        <v>94.29000000000001</v>
+        <v>-112.68</v>
       </c>
       <c r="L49" t="n">
-        <v>95.56</v>
+        <v>120.09</v>
       </c>
     </row>
     <row r="50">
@@ -2137,28 +2137,28 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5.2</v>
+        <v>5.01</v>
       </c>
       <c r="F50" t="n">
-        <v>11.41</v>
+        <v>12.42</v>
       </c>
       <c r="G50" t="n">
-        <v>178.9</v>
+        <v>189.8</v>
       </c>
       <c r="H50" t="n">
-        <v>92.3</v>
+        <v>24.7</v>
       </c>
       <c r="I50" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>146.46</v>
+        <v>154.81</v>
       </c>
       <c r="K50" t="n">
-        <v>81.83</v>
+        <v>71.25</v>
       </c>
       <c r="L50" t="n">
-        <v>167.77</v>
+        <v>170.42</v>
       </c>
     </row>
     <row r="51">
@@ -2179,28 +2179,28 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>5.65</v>
+        <v>5.44</v>
       </c>
       <c r="F51" t="n">
-        <v>13.22</v>
+        <v>13.46</v>
       </c>
       <c r="G51" t="n">
-        <v>193.2</v>
+        <v>179.2</v>
       </c>
       <c r="H51" t="n">
-        <v>89.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-52.05</v>
+        <v>-82.01000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>-292.14</v>
+        <v>-201.68</v>
       </c>
       <c r="L51" t="n">
-        <v>296.74</v>
+        <v>217.71</v>
       </c>
     </row>
     <row r="52">
@@ -2221,28 +2221,28 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.64</v>
+        <v>5.24</v>
       </c>
       <c r="F52" t="n">
-        <v>12.48</v>
+        <v>11.76</v>
       </c>
       <c r="G52" t="n">
-        <v>173.7</v>
+        <v>181.4</v>
       </c>
       <c r="H52" t="n">
-        <v>87.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-58.73</v>
+        <v>-121.76</v>
       </c>
       <c r="K52" t="n">
-        <v>245</v>
+        <v>116.74</v>
       </c>
       <c r="L52" t="n">
-        <v>251.94</v>
+        <v>168.68</v>
       </c>
     </row>
     <row r="53">
@@ -2263,28 +2263,28 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.42</v>
+        <v>5.09</v>
       </c>
       <c r="F53" t="n">
-        <v>13.78</v>
+        <v>11.87</v>
       </c>
       <c r="G53" t="n">
-        <v>186.5</v>
+        <v>176.8</v>
       </c>
       <c r="H53" t="n">
-        <v>89.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="I53" t="n">
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>270.1</v>
+        <v>120.3</v>
       </c>
       <c r="K53" t="n">
-        <v>-19.12</v>
+        <v>-181.23</v>
       </c>
       <c r="L53" t="n">
-        <v>270.78</v>
+        <v>217.52</v>
       </c>
     </row>
     <row r="54">
@@ -2305,28 +2305,28 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>5.53</v>
+        <v>5.5</v>
       </c>
       <c r="F54" t="n">
-        <v>14.14</v>
+        <v>11.51</v>
       </c>
       <c r="G54" t="n">
-        <v>177.9</v>
+        <v>187</v>
       </c>
       <c r="H54" t="n">
-        <v>97.09999999999999</v>
+        <v>25.5</v>
       </c>
       <c r="I54" t="n">
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>312.99</v>
+        <v>150.16</v>
       </c>
       <c r="K54" t="n">
-        <v>-136.99</v>
+        <v>-256.41</v>
       </c>
       <c r="L54" t="n">
-        <v>341.66</v>
+        <v>297.15</v>
       </c>
     </row>
     <row r="55">
@@ -2347,28 +2347,28 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>5.82</v>
+        <v>5.39</v>
       </c>
       <c r="F55" t="n">
-        <v>14.14</v>
+        <v>13.32</v>
       </c>
       <c r="G55" t="n">
-        <v>198.2</v>
+        <v>172.2</v>
       </c>
       <c r="H55" t="n">
-        <v>91.59999999999999</v>
+        <v>53.7</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-265.12</v>
+        <v>126.75</v>
       </c>
       <c r="K55" t="n">
-        <v>-206.06</v>
+        <v>253.19</v>
       </c>
       <c r="L55" t="n">
-        <v>335.78</v>
+        <v>283.15</v>
       </c>
     </row>
     <row r="56">
@@ -2389,28 +2389,28 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.48</v>
+        <v>5.49</v>
       </c>
       <c r="F56" t="n">
-        <v>14.14</v>
+        <v>9.69</v>
       </c>
       <c r="G56" t="n">
-        <v>194.9</v>
+        <v>187.9</v>
       </c>
       <c r="H56" t="n">
-        <v>88.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="I56" t="n">
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>-253.86</v>
+        <v>53.24</v>
       </c>
       <c r="K56" t="n">
-        <v>-591.7</v>
+        <v>-436.46</v>
       </c>
       <c r="L56" t="n">
-        <v>643.86</v>
+        <v>439.69</v>
       </c>
     </row>
     <row r="57">
@@ -2431,28 +2431,28 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.98</v>
+        <v>5.47</v>
       </c>
       <c r="F57" t="n">
-        <v>11.88</v>
+        <v>13.09</v>
       </c>
       <c r="G57" t="n">
-        <v>187.3</v>
+        <v>195.7</v>
       </c>
       <c r="H57" t="n">
-        <v>90</v>
+        <v>72.7</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>354.7</v>
+        <v>-280.71</v>
       </c>
       <c r="K57" t="n">
-        <v>143.77</v>
+        <v>225.22</v>
       </c>
       <c r="L57" t="n">
-        <v>382.73</v>
+        <v>359.89</v>
       </c>
     </row>
     <row r="58">
@@ -2473,28 +2473,28 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>5.47</v>
+        <v>5.91</v>
       </c>
       <c r="F58" t="n">
-        <v>13.77</v>
+        <v>13.81</v>
       </c>
       <c r="G58" t="n">
-        <v>185</v>
+        <v>183.7</v>
       </c>
       <c r="H58" t="n">
-        <v>98.7</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>-276.77</v>
+        <v>0.33</v>
       </c>
       <c r="K58" t="n">
-        <v>-502.28</v>
+        <v>-371.3</v>
       </c>
       <c r="L58" t="n">
-        <v>573.48</v>
+        <v>371.3</v>
       </c>
     </row>
     <row r="59">
@@ -2515,28 +2515,28 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.86</v>
+        <v>4.99</v>
       </c>
       <c r="F59" t="n">
-        <v>11.18</v>
+        <v>13.83</v>
       </c>
       <c r="G59" t="n">
-        <v>188.4</v>
+        <v>185.2</v>
       </c>
       <c r="H59" t="n">
-        <v>90.3</v>
+        <v>39.5</v>
       </c>
       <c r="I59" t="n">
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-69.38</v>
+        <v>42.34</v>
       </c>
       <c r="K59" t="n">
-        <v>75.08</v>
+        <v>-86.54000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>102.23</v>
+        <v>96.34999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2557,28 +2557,28 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>6.56</v>
+        <v>5.35</v>
       </c>
       <c r="F60" t="n">
-        <v>14.14</v>
+        <v>11.64</v>
       </c>
       <c r="G60" t="n">
-        <v>174.1</v>
+        <v>184</v>
       </c>
       <c r="H60" t="n">
-        <v>91.40000000000001</v>
+        <v>59.9</v>
       </c>
       <c r="I60" t="n">
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>31.73</v>
+        <v>51.59</v>
       </c>
       <c r="K60" t="n">
-        <v>-115.28</v>
+        <v>-128.79</v>
       </c>
       <c r="L60" t="n">
-        <v>119.56</v>
+        <v>138.73</v>
       </c>
     </row>
     <row r="61">
@@ -2599,28 +2599,28 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>5.44</v>
+        <v>4.78</v>
       </c>
       <c r="F61" t="n">
-        <v>14.14</v>
+        <v>13.83</v>
       </c>
       <c r="G61" t="n">
-        <v>188.6</v>
+        <v>176.6</v>
       </c>
       <c r="H61" t="n">
-        <v>89.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="I61" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-95.47</v>
+        <v>-2.43</v>
       </c>
       <c r="K61" t="n">
-        <v>-29.7</v>
+        <v>-104.17</v>
       </c>
       <c r="L61" t="n">
-        <v>99.98</v>
+        <v>104.2</v>
       </c>
     </row>
     <row r="62">
@@ -2641,28 +2641,28 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.97</v>
+        <v>5.45</v>
       </c>
       <c r="F62" t="n">
         <v>14.14</v>
       </c>
       <c r="G62" t="n">
-        <v>179</v>
+        <v>167.7</v>
       </c>
       <c r="H62" t="n">
-        <v>85.90000000000001</v>
+        <v>27.8</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>129.18</v>
+        <v>-129.3</v>
       </c>
       <c r="K62" t="n">
-        <v>-107.82</v>
+        <v>69.84</v>
       </c>
       <c r="L62" t="n">
-        <v>168.26</v>
+        <v>146.96</v>
       </c>
     </row>
     <row r="63">
@@ -2683,28 +2683,28 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>5.5</v>
+        <v>6.11</v>
       </c>
       <c r="F63" t="n">
-        <v>11.19</v>
+        <v>14.14</v>
       </c>
       <c r="G63" t="n">
-        <v>181.5</v>
+        <v>183.3</v>
       </c>
       <c r="H63" t="n">
-        <v>88.90000000000001</v>
+        <v>60.4</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>19.18</v>
+        <v>139.38</v>
       </c>
       <c r="K63" t="n">
-        <v>-154.12</v>
+        <v>-222.64</v>
       </c>
       <c r="L63" t="n">
-        <v>155.3</v>
+        <v>262.67</v>
       </c>
     </row>
     <row r="64">
@@ -2725,28 +2725,28 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>5.61</v>
+        <v>5.66</v>
       </c>
       <c r="F64" t="n">
         <v>14.14</v>
       </c>
       <c r="G64" t="n">
-        <v>180.6</v>
+        <v>191.6</v>
       </c>
       <c r="H64" t="n">
-        <v>88.09999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>110.21</v>
+        <v>-288.18</v>
       </c>
       <c r="K64" t="n">
-        <v>44.56</v>
+        <v>-113.2</v>
       </c>
       <c r="L64" t="n">
-        <v>118.88</v>
+        <v>309.62</v>
       </c>
     </row>
     <row r="65">
@@ -2767,28 +2767,28 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.76</v>
+        <v>5.21</v>
       </c>
       <c r="F65" t="n">
-        <v>10.29</v>
+        <v>14.14</v>
       </c>
       <c r="G65" t="n">
-        <v>189.3</v>
+        <v>187.7</v>
       </c>
       <c r="H65" t="n">
-        <v>84.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="I65" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>-176.82</v>
+        <v>-214.44</v>
       </c>
       <c r="K65" t="n">
-        <v>56.47</v>
+        <v>33.89</v>
       </c>
       <c r="L65" t="n">
-        <v>185.62</v>
+        <v>217.1</v>
       </c>
     </row>
     <row r="66">
@@ -2809,28 +2809,28 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.53</v>
+        <v>5.23</v>
       </c>
       <c r="F66" t="n">
         <v>14.14</v>
       </c>
       <c r="G66" t="n">
-        <v>186</v>
+        <v>185.8</v>
       </c>
       <c r="H66" t="n">
-        <v>88.8</v>
+        <v>78</v>
       </c>
       <c r="I66" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-181.17</v>
+        <v>194</v>
       </c>
       <c r="K66" t="n">
-        <v>36.69</v>
+        <v>-67.26000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>184.85</v>
+        <v>205.33</v>
       </c>
     </row>
     <row r="67">
@@ -2851,28 +2851,28 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5.23</v>
+        <v>4.94</v>
       </c>
       <c r="F67" t="n">
-        <v>14.14</v>
+        <v>12.8</v>
       </c>
       <c r="G67" t="n">
-        <v>198.6</v>
+        <v>193.7</v>
       </c>
       <c r="H67" t="n">
-        <v>80.90000000000001</v>
+        <v>57.7</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-63.72</v>
+        <v>174.51</v>
       </c>
       <c r="K67" t="n">
-        <v>-281.23</v>
+        <v>-91.8</v>
       </c>
       <c r="L67" t="n">
-        <v>288.36</v>
+        <v>197.18</v>
       </c>
     </row>
     <row r="68">
@@ -2893,28 +2893,28 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.33</v>
+        <v>5.6</v>
       </c>
       <c r="F68" t="n">
-        <v>12.96</v>
+        <v>14.14</v>
       </c>
       <c r="G68" t="n">
-        <v>190.3</v>
+        <v>175.7</v>
       </c>
       <c r="H68" t="n">
-        <v>86.09999999999999</v>
+        <v>57.5</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-341.69</v>
+        <v>280.06</v>
       </c>
       <c r="K68" t="n">
-        <v>66.69</v>
+        <v>155.84</v>
       </c>
       <c r="L68" t="n">
-        <v>348.14</v>
+        <v>320.5</v>
       </c>
     </row>
     <row r="69">
@@ -2935,28 +2935,28 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>6.27</v>
+        <v>5.22</v>
       </c>
       <c r="F69" t="n">
-        <v>14.14</v>
+        <v>12.4</v>
       </c>
       <c r="G69" t="n">
-        <v>171.9</v>
+        <v>176.6</v>
       </c>
       <c r="H69" t="n">
-        <v>93.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I69" t="n">
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-93.52</v>
+        <v>-189.2</v>
       </c>
       <c r="K69" t="n">
-        <v>406.39</v>
+        <v>-167.64</v>
       </c>
       <c r="L69" t="n">
-        <v>417.01</v>
+        <v>252.78</v>
       </c>
     </row>
     <row r="70">
@@ -2977,28 +2977,28 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.4</v>
+        <v>5.48</v>
       </c>
       <c r="F70" t="n">
-        <v>11.85</v>
+        <v>14.14</v>
       </c>
       <c r="G70" t="n">
-        <v>188.3</v>
+        <v>188.9</v>
       </c>
       <c r="H70" t="n">
-        <v>92.90000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>40.23</v>
+        <v>-95.94</v>
       </c>
       <c r="K70" t="n">
-        <v>274.6</v>
+        <v>-288.92</v>
       </c>
       <c r="L70" t="n">
-        <v>277.53</v>
+        <v>304.43</v>
       </c>
     </row>
     <row r="71">
@@ -3019,28 +3019,28 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.37</v>
+        <v>5.36</v>
       </c>
       <c r="F71" t="n">
-        <v>13.37</v>
+        <v>13.42</v>
       </c>
       <c r="G71" t="n">
-        <v>185</v>
+        <v>186.7</v>
       </c>
       <c r="H71" t="n">
-        <v>89.2</v>
+        <v>58.3</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-587.7</v>
+        <v>-348.54</v>
       </c>
       <c r="K71" t="n">
-        <v>29.76</v>
+        <v>-293.61</v>
       </c>
       <c r="L71" t="n">
-        <v>588.45</v>
+        <v>455.72</v>
       </c>
     </row>
     <row r="72">
@@ -3061,28 +3061,28 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>5.3</v>
+        <v>5.31</v>
       </c>
       <c r="F72" t="n">
-        <v>14.14</v>
+        <v>13.3</v>
       </c>
       <c r="G72" t="n">
-        <v>180</v>
+        <v>185.8</v>
       </c>
       <c r="H72" t="n">
-        <v>91.7</v>
+        <v>65.7</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>461.52</v>
+        <v>101.82</v>
       </c>
       <c r="K72" t="n">
-        <v>-27.97</v>
+        <v>264.83</v>
       </c>
       <c r="L72" t="n">
-        <v>462.36</v>
+        <v>283.73</v>
       </c>
     </row>
     <row r="73">
@@ -3103,28 +3103,28 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>6.45</v>
+        <v>5.49</v>
       </c>
       <c r="F73" t="n">
-        <v>14.14</v>
+        <v>12.73</v>
       </c>
       <c r="G73" t="n">
-        <v>190.7</v>
+        <v>182.4</v>
       </c>
       <c r="H73" t="n">
-        <v>93.90000000000001</v>
+        <v>33.3</v>
       </c>
       <c r="I73" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-348.31</v>
+        <v>-353.97</v>
       </c>
       <c r="K73" t="n">
-        <v>-484.5</v>
+        <v>-248.31</v>
       </c>
       <c r="L73" t="n">
-        <v>596.71</v>
+        <v>432.38</v>
       </c>
     </row>
     <row r="74">
@@ -3145,28 +3145,28 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.36</v>
+        <v>4.81</v>
       </c>
       <c r="F74" t="n">
-        <v>14.14</v>
+        <v>12.07</v>
       </c>
       <c r="G74" t="n">
-        <v>182.3</v>
+        <v>184.9</v>
       </c>
       <c r="H74" t="n">
-        <v>88.8</v>
+        <v>55.7</v>
       </c>
       <c r="I74" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-25.09</v>
+        <v>4.61</v>
       </c>
       <c r="K74" t="n">
-        <v>89.17</v>
+        <v>-116.12</v>
       </c>
       <c r="L74" t="n">
-        <v>92.63</v>
+        <v>116.21</v>
       </c>
     </row>
     <row r="75">
@@ -3187,28 +3187,28 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.67</v>
+        <v>5.39</v>
       </c>
       <c r="F75" t="n">
-        <v>10.62</v>
+        <v>11.11</v>
       </c>
       <c r="G75" t="n">
-        <v>178.4</v>
+        <v>182.4</v>
       </c>
       <c r="H75" t="n">
-        <v>86.7</v>
+        <v>49</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>96.29000000000001</v>
+        <v>131.91</v>
       </c>
       <c r="K75" t="n">
-        <v>-26.36</v>
+        <v>-56.65</v>
       </c>
       <c r="L75" t="n">
-        <v>99.83</v>
+        <v>143.56</v>
       </c>
     </row>
     <row r="76">
@@ -3229,28 +3229,28 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.16</v>
+        <v>4.96</v>
       </c>
       <c r="F76" t="n">
-        <v>14.14</v>
+        <v>12.63</v>
       </c>
       <c r="G76" t="n">
-        <v>178.4</v>
+        <v>198.4</v>
       </c>
       <c r="H76" t="n">
-        <v>86.7</v>
+        <v>57.2</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-31.44</v>
+        <v>-49.3</v>
       </c>
       <c r="K76" t="n">
-        <v>83.17</v>
+        <v>-91.44</v>
       </c>
       <c r="L76" t="n">
-        <v>88.92</v>
+        <v>103.88</v>
       </c>
     </row>
     <row r="77">
@@ -3271,28 +3271,28 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.58</v>
+        <v>5.29</v>
       </c>
       <c r="F77" t="n">
-        <v>12.6</v>
+        <v>14.14</v>
       </c>
       <c r="G77" t="n">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="H77" t="n">
-        <v>89.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I77" t="n">
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>94.58</v>
+        <v>29.17</v>
       </c>
       <c r="K77" t="n">
-        <v>-66.64</v>
+        <v>-171.22</v>
       </c>
       <c r="L77" t="n">
-        <v>115.7</v>
+        <v>173.69</v>
       </c>
     </row>
     <row r="78">
@@ -3313,28 +3313,28 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.19</v>
+        <v>5.25</v>
       </c>
       <c r="F78" t="n">
-        <v>14.14</v>
+        <v>12.44</v>
       </c>
       <c r="G78" t="n">
-        <v>173.7</v>
+        <v>200.8</v>
       </c>
       <c r="H78" t="n">
-        <v>81.5</v>
+        <v>56.8</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>140.59</v>
+        <v>-84.81999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>14.64</v>
+        <v>-127.76</v>
       </c>
       <c r="L78" t="n">
-        <v>141.35</v>
+        <v>153.36</v>
       </c>
     </row>
     <row r="79">
@@ -3355,28 +3355,28 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.9</v>
+        <v>6.06</v>
       </c>
       <c r="F79" t="n">
-        <v>13.31</v>
+        <v>14.14</v>
       </c>
       <c r="G79" t="n">
-        <v>190.1</v>
+        <v>185</v>
       </c>
       <c r="H79" t="n">
-        <v>90.8</v>
+        <v>37.1</v>
       </c>
       <c r="I79" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>77.55</v>
+        <v>90.28</v>
       </c>
       <c r="K79" t="n">
-        <v>3.98</v>
+        <v>-185.27</v>
       </c>
       <c r="L79" t="n">
-        <v>77.65000000000001</v>
+        <v>206.09</v>
       </c>
     </row>
     <row r="80">
@@ -3397,28 +3397,28 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>6.3</v>
+        <v>5.74</v>
       </c>
       <c r="F80" t="n">
-        <v>12.75</v>
+        <v>14.14</v>
       </c>
       <c r="G80" t="n">
-        <v>195.2</v>
+        <v>188.8</v>
       </c>
       <c r="H80" t="n">
-        <v>94.59999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="I80" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>-284.48</v>
+        <v>147.16</v>
       </c>
       <c r="K80" t="n">
-        <v>-39.9</v>
+        <v>200.85</v>
       </c>
       <c r="L80" t="n">
-        <v>287.26</v>
+        <v>248.99</v>
       </c>
     </row>
     <row r="81">
@@ -3439,28 +3439,28 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>5.99</v>
+        <v>6.17</v>
       </c>
       <c r="F81" t="n">
         <v>14.14</v>
       </c>
       <c r="G81" t="n">
-        <v>185.8</v>
+        <v>198.6</v>
       </c>
       <c r="H81" t="n">
-        <v>87</v>
+        <v>68.3</v>
       </c>
       <c r="I81" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-139.83</v>
+        <v>33.81</v>
       </c>
       <c r="K81" t="n">
-        <v>223.5</v>
+        <v>-245.75</v>
       </c>
       <c r="L81" t="n">
-        <v>263.63</v>
+        <v>248.06</v>
       </c>
     </row>
     <row r="82">
@@ -3481,28 +3481,28 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>6.33</v>
+        <v>5.64</v>
       </c>
       <c r="F82" t="n">
         <v>14.14</v>
       </c>
       <c r="G82" t="n">
-        <v>190.8</v>
+        <v>190.6</v>
       </c>
       <c r="H82" t="n">
-        <v>94</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>225.85</v>
+        <v>252.28</v>
       </c>
       <c r="K82" t="n">
-        <v>48.51</v>
+        <v>-83.27</v>
       </c>
       <c r="L82" t="n">
-        <v>231</v>
+        <v>265.67</v>
       </c>
     </row>
     <row r="83">
@@ -3523,28 +3523,28 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.94</v>
+        <v>5.83</v>
       </c>
       <c r="F83" t="n">
         <v>14.14</v>
       </c>
       <c r="G83" t="n">
-        <v>181.3</v>
+        <v>190.8</v>
       </c>
       <c r="H83" t="n">
-        <v>90.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>334.9</v>
+        <v>-320.71</v>
       </c>
       <c r="K83" t="n">
-        <v>266.1</v>
+        <v>13.02</v>
       </c>
       <c r="L83" t="n">
-        <v>427.74</v>
+        <v>320.97</v>
       </c>
     </row>
     <row r="84">
@@ -3565,28 +3565,28 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>6.19</v>
+        <v>6.36</v>
       </c>
       <c r="F84" t="n">
         <v>14.14</v>
       </c>
       <c r="G84" t="n">
-        <v>187.3</v>
+        <v>191.8</v>
       </c>
       <c r="H84" t="n">
-        <v>90.59999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>209.37</v>
+        <v>359.52</v>
       </c>
       <c r="K84" t="n">
-        <v>-203.45</v>
+        <v>-167.75</v>
       </c>
       <c r="L84" t="n">
-        <v>291.94</v>
+        <v>396.73</v>
       </c>
     </row>
     <row r="85">
@@ -3607,28 +3607,28 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.46</v>
+        <v>5.91</v>
       </c>
       <c r="F85" t="n">
         <v>14.14</v>
       </c>
       <c r="G85" t="n">
-        <v>187.7</v>
+        <v>191.7</v>
       </c>
       <c r="H85" t="n">
-        <v>90.59999999999999</v>
+        <v>52.7</v>
       </c>
       <c r="I85" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-58.48</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="K85" t="n">
-        <v>-337.17</v>
+        <v>-406.47</v>
       </c>
       <c r="L85" t="n">
-        <v>342.21</v>
+        <v>415.05</v>
       </c>
     </row>
     <row r="86">
@@ -3649,28 +3649,28 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>5.62</v>
+        <v>5.57</v>
       </c>
       <c r="F86" t="n">
-        <v>12.55</v>
+        <v>14.14</v>
       </c>
       <c r="G86" t="n">
-        <v>188.8</v>
+        <v>188.2</v>
       </c>
       <c r="H86" t="n">
-        <v>92.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-125.56</v>
+        <v>116.09</v>
       </c>
       <c r="K86" t="n">
-        <v>410</v>
+        <v>255.72</v>
       </c>
       <c r="L86" t="n">
-        <v>428.79</v>
+        <v>280.84</v>
       </c>
     </row>
     <row r="87">
@@ -3691,28 +3691,28 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>6.1</v>
+        <v>5.68</v>
       </c>
       <c r="F87" t="n">
         <v>14.14</v>
       </c>
       <c r="G87" t="n">
-        <v>188.5</v>
+        <v>189.6</v>
       </c>
       <c r="H87" t="n">
-        <v>86.3</v>
+        <v>50.1</v>
       </c>
       <c r="I87" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>534.09</v>
+        <v>-400.92</v>
       </c>
       <c r="K87" t="n">
-        <v>306.3</v>
+        <v>-267.12</v>
       </c>
       <c r="L87" t="n">
-        <v>615.6799999999999</v>
+        <v>481.76</v>
       </c>
     </row>
     <row r="88">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.63</v>
+        <v>5.31</v>
       </c>
       <c r="F88" t="n">
-        <v>13.92</v>
+        <v>14.14</v>
       </c>
       <c r="G88" t="n">
-        <v>184.1</v>
+        <v>179.6</v>
       </c>
       <c r="H88" t="n">
-        <v>91.5</v>
+        <v>62.2</v>
       </c>
       <c r="I88" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>117.36</v>
+        <v>-411.28</v>
       </c>
       <c r="K88" t="n">
-        <v>-472.47</v>
+        <v>90.69</v>
       </c>
       <c r="L88" t="n">
-        <v>486.83</v>
+        <v>421.16</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-01.xlsx
+++ b/output/2024-04-01.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>92.59999999999999</v>
+        <v>111.16</v>
       </c>
       <c r="K14" t="n">
-        <v>-68.16</v>
+        <v>-36.27</v>
       </c>
       <c r="L14" t="n">
-        <v>114.98</v>
+        <v>116.93</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-33.44</v>
+        <v>-40.6</v>
       </c>
       <c r="K15" t="n">
-        <v>-86.08</v>
+        <v>-85.06</v>
       </c>
       <c r="L15" t="n">
-        <v>92.34</v>
+        <v>94.25</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>66.02</v>
+        <v>78.27</v>
       </c>
       <c r="K16" t="n">
-        <v>-53.95</v>
+        <v>-38.67</v>
       </c>
       <c r="L16" t="n">
-        <v>85.26000000000001</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-118.89</v>
+        <v>-137.96</v>
       </c>
       <c r="K17" t="n">
-        <v>-87.48</v>
+        <v>-55.86</v>
       </c>
       <c r="L17" t="n">
-        <v>147.61</v>
+        <v>148.84</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-57.81</v>
+        <v>-70.26000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-88.75</v>
+        <v>-80.29000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>105.92</v>
+        <v>106.69</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>78.68000000000001</v>
+        <v>63.27</v>
       </c>
       <c r="K19" t="n">
-        <v>68.36</v>
+        <v>86.45</v>
       </c>
       <c r="L19" t="n">
-        <v>104.23</v>
+        <v>107.13</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>35.31</v>
+        <v>51.5</v>
       </c>
       <c r="K20" t="n">
-        <v>-164.6</v>
+        <v>-162.41</v>
       </c>
       <c r="L20" t="n">
-        <v>168.35</v>
+        <v>170.38</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>144.42</v>
+        <v>123.6</v>
       </c>
       <c r="K21" t="n">
-        <v>109.35</v>
+        <v>139.11</v>
       </c>
       <c r="L21" t="n">
-        <v>181.15</v>
+        <v>186.08</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>-171.04</v>
+        <v>-139.3</v>
       </c>
       <c r="K22" t="n">
-        <v>115.71</v>
+        <v>157.79</v>
       </c>
       <c r="L22" t="n">
-        <v>206.5</v>
+        <v>210.48</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>-224.26</v>
+        <v>-259.28</v>
       </c>
       <c r="K23" t="n">
-        <v>-61.19</v>
+        <v>1.91</v>
       </c>
       <c r="L23" t="n">
-        <v>232.46</v>
+        <v>259.29</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>174.75</v>
+        <v>234.21</v>
       </c>
       <c r="K24" t="n">
-        <v>-204.42</v>
+        <v>-181.47</v>
       </c>
       <c r="L24" t="n">
-        <v>268.93</v>
+        <v>296.29</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-342.19</v>
+        <v>-316.81</v>
       </c>
       <c r="K25" t="n">
-        <v>88.05</v>
+        <v>198.54</v>
       </c>
       <c r="L25" t="n">
-        <v>353.34</v>
+        <v>373.88</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>-18.76</v>
+        <v>7.17</v>
       </c>
       <c r="K26" t="n">
-        <v>-427.7</v>
+        <v>-437.75</v>
       </c>
       <c r="L26" t="n">
-        <v>428.11</v>
+        <v>437.8</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-311.85</v>
+        <v>-325.51</v>
       </c>
       <c r="K27" t="n">
-        <v>-18.98</v>
+        <v>74.87</v>
       </c>
       <c r="L27" t="n">
-        <v>312.42</v>
+        <v>334.01</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>392.69</v>
+        <v>433.51</v>
       </c>
       <c r="K28" t="n">
-        <v>-162.85</v>
+        <v>-40.23</v>
       </c>
       <c r="L28" t="n">
-        <v>425.11</v>
+        <v>435.37</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>24.66</v>
+        <v>37.56</v>
       </c>
       <c r="K29" t="n">
-        <v>-79.41</v>
+        <v>-75.14</v>
       </c>
       <c r="L29" t="n">
-        <v>83.15000000000001</v>
+        <v>84.01000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>84.51000000000001</v>
+        <v>75.44</v>
       </c>
       <c r="K30" t="n">
-        <v>29.34</v>
+        <v>51.48</v>
       </c>
       <c r="L30" t="n">
-        <v>89.45999999999999</v>
+        <v>91.33</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.64</v>
+        <v>-11.91</v>
       </c>
       <c r="K31" t="n">
-        <v>-115.5</v>
+        <v>-118.9</v>
       </c>
       <c r="L31" t="n">
-        <v>115.98</v>
+        <v>119.49</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-35.01</v>
+        <v>-24.6</v>
       </c>
       <c r="K32" t="n">
-        <v>68.01000000000001</v>
+        <v>75.22</v>
       </c>
       <c r="L32" t="n">
-        <v>76.48999999999999</v>
+        <v>79.14</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-133.15</v>
+        <v>-111.53</v>
       </c>
       <c r="K33" t="n">
-        <v>73.04000000000001</v>
+        <v>110.89</v>
       </c>
       <c r="L33" t="n">
-        <v>151.87</v>
+        <v>157.27</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-146.3</v>
+        <v>-120.82</v>
       </c>
       <c r="K34" t="n">
-        <v>37.3</v>
+        <v>92.8</v>
       </c>
       <c r="L34" t="n">
-        <v>150.98</v>
+        <v>152.35</v>
       </c>
     </row>
     <row r="35">
@@ -1507,28 +1507,28 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.94</v>
+        <v>5.4</v>
       </c>
       <c r="F35" t="n">
-        <v>11.38</v>
+        <v>12.5</v>
       </c>
       <c r="G35" t="n">
-        <v>179</v>
+        <v>196.5</v>
       </c>
       <c r="H35" t="n">
-        <v>62</v>
+        <v>58.2</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-74.09999999999999</v>
+        <v>197</v>
       </c>
       <c r="K35" t="n">
-        <v>-146.42</v>
+        <v>38.9</v>
       </c>
       <c r="L35" t="n">
-        <v>164.1</v>
+        <v>200.81</v>
       </c>
     </row>
     <row r="36">
@@ -1549,28 +1549,28 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.44</v>
+        <v>5.3</v>
       </c>
       <c r="F36" t="n">
-        <v>8.890000000000001</v>
+        <v>10.41</v>
       </c>
       <c r="G36" t="n">
-        <v>184.7</v>
+        <v>177.4</v>
       </c>
       <c r="H36" t="n">
-        <v>69.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-125.77</v>
+        <v>67.98</v>
       </c>
       <c r="K36" t="n">
-        <v>-78.62</v>
+        <v>-140.65</v>
       </c>
       <c r="L36" t="n">
-        <v>148.32</v>
+        <v>156.22</v>
       </c>
     </row>
     <row r="37">
@@ -1591,28 +1591,28 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5.13</v>
+        <v>4.58</v>
       </c>
       <c r="F37" t="n">
-        <v>13.9</v>
+        <v>11.33</v>
       </c>
       <c r="G37" t="n">
-        <v>194.2</v>
+        <v>188.6</v>
       </c>
       <c r="H37" t="n">
-        <v>30.6</v>
+        <v>66.7</v>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>145.55</v>
+        <v>-117.08</v>
       </c>
       <c r="K37" t="n">
-        <v>-152.41</v>
+        <v>70.84</v>
       </c>
       <c r="L37" t="n">
-        <v>210.74</v>
+        <v>136.84</v>
       </c>
     </row>
     <row r="38">
@@ -1633,28 +1633,28 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>5.84</v>
+        <v>5.17</v>
       </c>
       <c r="F38" t="n">
-        <v>13.94</v>
+        <v>12.64</v>
       </c>
       <c r="G38" t="n">
-        <v>178.9</v>
+        <v>202.3</v>
       </c>
       <c r="H38" t="n">
-        <v>81.7</v>
+        <v>99.2</v>
       </c>
       <c r="I38" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>-227.68</v>
+        <v>-355.02</v>
       </c>
       <c r="K38" t="n">
-        <v>-265.55</v>
+        <v>-41.41</v>
       </c>
       <c r="L38" t="n">
-        <v>349.79</v>
+        <v>357.43</v>
       </c>
     </row>
     <row r="39">
@@ -1675,28 +1675,28 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>5.16</v>
+        <v>5.15</v>
       </c>
       <c r="F39" t="n">
-        <v>14.14</v>
+        <v>9.83</v>
       </c>
       <c r="G39" t="n">
-        <v>188.5</v>
+        <v>182</v>
       </c>
       <c r="H39" t="n">
-        <v>40.9</v>
+        <v>37.8</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J39" t="n">
-        <v>-196.76</v>
+        <v>-351.99</v>
       </c>
       <c r="K39" t="n">
-        <v>-226.55</v>
+        <v>-12.05</v>
       </c>
       <c r="L39" t="n">
-        <v>300.06</v>
+        <v>352.2</v>
       </c>
     </row>
     <row r="40">
@@ -1717,28 +1717,28 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.59</v>
+        <v>4.93</v>
       </c>
       <c r="F40" t="n">
-        <v>14.14</v>
+        <v>12.49</v>
       </c>
       <c r="G40" t="n">
-        <v>197.2</v>
+        <v>194.2</v>
       </c>
       <c r="H40" t="n">
-        <v>64.59999999999999</v>
+        <v>53.4</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>179.39</v>
+        <v>-408.26</v>
       </c>
       <c r="K40" t="n">
-        <v>-180.47</v>
+        <v>1.24</v>
       </c>
       <c r="L40" t="n">
-        <v>254.46</v>
+        <v>408.26</v>
       </c>
     </row>
     <row r="41">
@@ -1759,28 +1759,28 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.73</v>
+        <v>5.3</v>
       </c>
       <c r="F41" t="n">
-        <v>12.05</v>
+        <v>12.28</v>
       </c>
       <c r="G41" t="n">
-        <v>188.6</v>
+        <v>178.9</v>
       </c>
       <c r="H41" t="n">
-        <v>81.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>135.37</v>
+        <v>265.15</v>
       </c>
       <c r="K41" t="n">
-        <v>-293.87</v>
+        <v>353.13</v>
       </c>
       <c r="L41" t="n">
-        <v>323.55</v>
+        <v>441.59</v>
       </c>
     </row>
     <row r="42">
@@ -1801,28 +1801,28 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.29</v>
+        <v>5.25</v>
       </c>
       <c r="F42" t="n">
-        <v>12.1</v>
+        <v>13.76</v>
       </c>
       <c r="G42" t="n">
-        <v>179.9</v>
+        <v>183</v>
       </c>
       <c r="H42" t="n">
-        <v>78.09999999999999</v>
+        <v>23.5</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-156.51</v>
+        <v>140.75</v>
       </c>
       <c r="K42" t="n">
-        <v>-230.8</v>
+        <v>-444.14</v>
       </c>
       <c r="L42" t="n">
-        <v>278.87</v>
+        <v>465.9</v>
       </c>
     </row>
     <row r="43">
@@ -1843,28 +1843,28 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.96</v>
+        <v>3.91</v>
       </c>
       <c r="F43" t="n">
-        <v>11.62</v>
+        <v>12.72</v>
       </c>
       <c r="G43" t="n">
-        <v>191</v>
+        <v>189.4</v>
       </c>
       <c r="H43" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-434.26</v>
+        <v>-55.44</v>
       </c>
       <c r="K43" t="n">
-        <v>-98.65000000000001</v>
+        <v>-287.05</v>
       </c>
       <c r="L43" t="n">
-        <v>445.33</v>
+        <v>292.36</v>
       </c>
     </row>
     <row r="44">
@@ -1885,28 +1885,28 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.07</v>
+        <v>5.4</v>
       </c>
       <c r="F44" t="n">
-        <v>11.46</v>
+        <v>14.14</v>
       </c>
       <c r="G44" t="n">
-        <v>186.8</v>
+        <v>177.9</v>
       </c>
       <c r="H44" t="n">
-        <v>89.3</v>
+        <v>92.7</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>19.79</v>
+        <v>108.09</v>
       </c>
       <c r="K44" t="n">
-        <v>-100.22</v>
+        <v>-48.46</v>
       </c>
       <c r="L44" t="n">
-        <v>102.16</v>
+        <v>118.45</v>
       </c>
     </row>
     <row r="45">
@@ -1927,28 +1927,28 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.53</v>
+        <v>5.2</v>
       </c>
       <c r="F45" t="n">
-        <v>10.04</v>
+        <v>14.14</v>
       </c>
       <c r="G45" t="n">
-        <v>179.4</v>
+        <v>182.1</v>
       </c>
       <c r="H45" t="n">
-        <v>12.3</v>
+        <v>41.3</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>-90.84999999999999</v>
+        <v>116.3</v>
       </c>
       <c r="K45" t="n">
-        <v>-8.279999999999999</v>
+        <v>-44.17</v>
       </c>
       <c r="L45" t="n">
-        <v>91.23</v>
+        <v>124.41</v>
       </c>
     </row>
     <row r="46">
@@ -1969,28 +1969,28 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>5.24</v>
+        <v>4.85</v>
       </c>
       <c r="F46" t="n">
-        <v>13.54</v>
+        <v>10.41</v>
       </c>
       <c r="G46" t="n">
-        <v>188.8</v>
+        <v>184.3</v>
       </c>
       <c r="H46" t="n">
-        <v>73.40000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-136.02</v>
+        <v>78.86</v>
       </c>
       <c r="K46" t="n">
-        <v>-61.4</v>
+        <v>-71.42</v>
       </c>
       <c r="L46" t="n">
-        <v>149.24</v>
+        <v>106.39</v>
       </c>
     </row>
     <row r="47">
@@ -2011,28 +2011,28 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.78</v>
+        <v>5.33</v>
       </c>
       <c r="F47" t="n">
-        <v>10.19</v>
+        <v>13.21</v>
       </c>
       <c r="G47" t="n">
-        <v>186.1</v>
+        <v>183.2</v>
       </c>
       <c r="H47" t="n">
-        <v>66.8</v>
+        <v>58.4</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-121.13</v>
+        <v>121.54</v>
       </c>
       <c r="K47" t="n">
-        <v>-80.02</v>
+        <v>-46.13</v>
       </c>
       <c r="L47" t="n">
-        <v>145.18</v>
+        <v>130</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>5.16</v>
       </c>
       <c r="F48" t="n">
-        <v>11.1</v>
+        <v>12.46</v>
       </c>
       <c r="G48" t="n">
-        <v>174.1</v>
+        <v>192.9</v>
       </c>
       <c r="H48" t="n">
-        <v>63.9</v>
+        <v>44.8</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-108.39</v>
+        <v>-86.75</v>
       </c>
       <c r="K48" t="n">
-        <v>94.13</v>
+        <v>28.63</v>
       </c>
       <c r="L48" t="n">
-        <v>143.56</v>
+        <v>91.36</v>
       </c>
     </row>
     <row r="49">
@@ -2095,28 +2095,28 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.73</v>
+        <v>5.27</v>
       </c>
       <c r="F49" t="n">
-        <v>11.7</v>
+        <v>12.56</v>
       </c>
       <c r="G49" t="n">
-        <v>187.7</v>
+        <v>187.2</v>
       </c>
       <c r="H49" t="n">
-        <v>35.7</v>
+        <v>42.2</v>
       </c>
       <c r="I49" t="n">
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-41.53</v>
+        <v>-141.4</v>
       </c>
       <c r="K49" t="n">
-        <v>-112.68</v>
+        <v>123.05</v>
       </c>
       <c r="L49" t="n">
-        <v>120.09</v>
+        <v>187.45</v>
       </c>
     </row>
     <row r="50">
@@ -2137,28 +2137,28 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5.01</v>
+        <v>4.76</v>
       </c>
       <c r="F50" t="n">
-        <v>12.42</v>
+        <v>9.93</v>
       </c>
       <c r="G50" t="n">
-        <v>189.8</v>
+        <v>201.7</v>
       </c>
       <c r="H50" t="n">
-        <v>24.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>154.81</v>
+        <v>-165.7</v>
       </c>
       <c r="K50" t="n">
-        <v>71.25</v>
+        <v>-87.61</v>
       </c>
       <c r="L50" t="n">
-        <v>170.42</v>
+        <v>187.44</v>
       </c>
     </row>
     <row r="51">
@@ -2179,28 +2179,28 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>5.44</v>
+        <v>5.06</v>
       </c>
       <c r="F51" t="n">
-        <v>13.46</v>
+        <v>10.37</v>
       </c>
       <c r="G51" t="n">
-        <v>179.2</v>
+        <v>192.2</v>
       </c>
       <c r="H51" t="n">
-        <v>69.09999999999999</v>
+        <v>49.7</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-82.01000000000001</v>
+        <v>-124.09</v>
       </c>
       <c r="K51" t="n">
-        <v>-201.68</v>
+        <v>168.73</v>
       </c>
       <c r="L51" t="n">
-        <v>217.71</v>
+        <v>209.44</v>
       </c>
     </row>
     <row r="52">
@@ -2221,28 +2221,28 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.24</v>
+        <v>4.98</v>
       </c>
       <c r="F52" t="n">
-        <v>11.76</v>
+        <v>13.11</v>
       </c>
       <c r="G52" t="n">
-        <v>181.4</v>
+        <v>172.2</v>
       </c>
       <c r="H52" t="n">
-        <v>69.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-121.76</v>
+        <v>-187.19</v>
       </c>
       <c r="K52" t="n">
-        <v>116.74</v>
+        <v>55.3</v>
       </c>
       <c r="L52" t="n">
-        <v>168.68</v>
+        <v>195.19</v>
       </c>
     </row>
     <row r="53">
@@ -2263,28 +2263,28 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.09</v>
+        <v>4.75</v>
       </c>
       <c r="F53" t="n">
-        <v>11.87</v>
+        <v>11.84</v>
       </c>
       <c r="G53" t="n">
-        <v>176.8</v>
+        <v>182.2</v>
       </c>
       <c r="H53" t="n">
-        <v>56.4</v>
+        <v>89.2</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>120.3</v>
+        <v>-38.09</v>
       </c>
       <c r="K53" t="n">
-        <v>-181.23</v>
+        <v>-348.43</v>
       </c>
       <c r="L53" t="n">
-        <v>217.52</v>
+        <v>350.51</v>
       </c>
     </row>
     <row r="54">
@@ -2305,28 +2305,28 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="F54" t="n">
-        <v>11.51</v>
+        <v>10.6</v>
       </c>
       <c r="G54" t="n">
-        <v>187</v>
+        <v>206.1</v>
       </c>
       <c r="H54" t="n">
-        <v>25.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I54" t="n">
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>150.16</v>
+        <v>58.53</v>
       </c>
       <c r="K54" t="n">
-        <v>-256.41</v>
+        <v>-316.39</v>
       </c>
       <c r="L54" t="n">
-        <v>297.15</v>
+        <v>321.76</v>
       </c>
     </row>
     <row r="55">
@@ -2347,28 +2347,28 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>5.39</v>
+        <v>5.49</v>
       </c>
       <c r="F55" t="n">
-        <v>13.32</v>
+        <v>11.17</v>
       </c>
       <c r="G55" t="n">
-        <v>172.2</v>
+        <v>187.1</v>
       </c>
       <c r="H55" t="n">
-        <v>53.7</v>
+        <v>100</v>
       </c>
       <c r="I55" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>126.75</v>
+        <v>39.53</v>
       </c>
       <c r="K55" t="n">
-        <v>253.19</v>
+        <v>346.8</v>
       </c>
       <c r="L55" t="n">
-        <v>283.15</v>
+        <v>349.04</v>
       </c>
     </row>
     <row r="56">
@@ -2389,28 +2389,28 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.49</v>
+        <v>5.36</v>
       </c>
       <c r="F56" t="n">
-        <v>9.69</v>
+        <v>14.14</v>
       </c>
       <c r="G56" t="n">
-        <v>187.9</v>
+        <v>199</v>
       </c>
       <c r="H56" t="n">
-        <v>75.8</v>
+        <v>56.7</v>
       </c>
       <c r="I56" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>53.24</v>
+        <v>290.27</v>
       </c>
       <c r="K56" t="n">
-        <v>-436.46</v>
+        <v>-283.42</v>
       </c>
       <c r="L56" t="n">
-        <v>439.69</v>
+        <v>405.69</v>
       </c>
     </row>
     <row r="57">
@@ -2431,28 +2431,28 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.47</v>
+        <v>5.18</v>
       </c>
       <c r="F57" t="n">
-        <v>13.09</v>
+        <v>12.6</v>
       </c>
       <c r="G57" t="n">
-        <v>195.7</v>
+        <v>185</v>
       </c>
       <c r="H57" t="n">
-        <v>72.7</v>
+        <v>53.3</v>
       </c>
       <c r="I57" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-280.71</v>
+        <v>-402.43</v>
       </c>
       <c r="K57" t="n">
-        <v>225.22</v>
+        <v>-47.99</v>
       </c>
       <c r="L57" t="n">
-        <v>359.89</v>
+        <v>405.28</v>
       </c>
     </row>
     <row r="58">
@@ -2473,28 +2473,28 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>5.91</v>
+        <v>5.42</v>
       </c>
       <c r="F58" t="n">
-        <v>13.81</v>
+        <v>11.34</v>
       </c>
       <c r="G58" t="n">
-        <v>183.7</v>
+        <v>188.5</v>
       </c>
       <c r="H58" t="n">
-        <v>66.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>0.33</v>
+        <v>358.17</v>
       </c>
       <c r="K58" t="n">
-        <v>-371.3</v>
+        <v>221.89</v>
       </c>
       <c r="L58" t="n">
-        <v>371.3</v>
+        <v>421.33</v>
       </c>
     </row>
     <row r="59">
@@ -2515,28 +2515,28 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.99</v>
+        <v>5.6</v>
       </c>
       <c r="F59" t="n">
-        <v>13.83</v>
+        <v>12.98</v>
       </c>
       <c r="G59" t="n">
-        <v>185.2</v>
+        <v>182.2</v>
       </c>
       <c r="H59" t="n">
-        <v>39.5</v>
+        <v>50.1</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>42.34</v>
+        <v>-166.96</v>
       </c>
       <c r="K59" t="n">
-        <v>-86.54000000000001</v>
+        <v>36.56</v>
       </c>
       <c r="L59" t="n">
-        <v>96.34999999999999</v>
+        <v>170.91</v>
       </c>
     </row>
     <row r="60">
@@ -2557,28 +2557,28 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.35</v>
+        <v>6.19</v>
       </c>
       <c r="F60" t="n">
-        <v>11.64</v>
+        <v>14</v>
       </c>
       <c r="G60" t="n">
-        <v>184</v>
+        <v>167.1</v>
       </c>
       <c r="H60" t="n">
-        <v>59.9</v>
+        <v>44.5</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>51.59</v>
+        <v>122.95</v>
       </c>
       <c r="K60" t="n">
-        <v>-128.79</v>
+        <v>-88.87</v>
       </c>
       <c r="L60" t="n">
-        <v>138.73</v>
+        <v>151.71</v>
       </c>
     </row>
     <row r="61">
@@ -2599,28 +2599,28 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.78</v>
+        <v>5.35</v>
       </c>
       <c r="F61" t="n">
-        <v>13.83</v>
+        <v>11.74</v>
       </c>
       <c r="G61" t="n">
-        <v>176.6</v>
+        <v>183.9</v>
       </c>
       <c r="H61" t="n">
-        <v>75.5</v>
+        <v>71.3</v>
       </c>
       <c r="I61" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-2.43</v>
+        <v>69.94</v>
       </c>
       <c r="K61" t="n">
-        <v>-104.17</v>
+        <v>-140.4</v>
       </c>
       <c r="L61" t="n">
-        <v>104.2</v>
+        <v>156.85</v>
       </c>
     </row>
     <row r="62">
@@ -2641,28 +2641,28 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>5.45</v>
+        <v>5.39</v>
       </c>
       <c r="F62" t="n">
-        <v>14.14</v>
+        <v>11.53</v>
       </c>
       <c r="G62" t="n">
-        <v>167.7</v>
+        <v>191.2</v>
       </c>
       <c r="H62" t="n">
-        <v>27.8</v>
+        <v>28.9</v>
       </c>
       <c r="I62" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-129.3</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>69.84</v>
+        <v>-144.8</v>
       </c>
       <c r="L62" t="n">
-        <v>146.96</v>
+        <v>172.73</v>
       </c>
     </row>
     <row r="63">
@@ -2683,28 +2683,28 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>6.11</v>
+        <v>5.04</v>
       </c>
       <c r="F63" t="n">
-        <v>14.14</v>
+        <v>12.83</v>
       </c>
       <c r="G63" t="n">
-        <v>183.3</v>
+        <v>176.7</v>
       </c>
       <c r="H63" t="n">
-        <v>60.4</v>
+        <v>37.3</v>
       </c>
       <c r="I63" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>139.38</v>
+        <v>63.36</v>
       </c>
       <c r="K63" t="n">
-        <v>-222.64</v>
+        <v>-156.91</v>
       </c>
       <c r="L63" t="n">
-        <v>262.67</v>
+        <v>169.22</v>
       </c>
     </row>
     <row r="64">
@@ -2725,28 +2725,28 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>5.66</v>
+        <v>6.09</v>
       </c>
       <c r="F64" t="n">
-        <v>14.14</v>
+        <v>11.81</v>
       </c>
       <c r="G64" t="n">
-        <v>191.6</v>
+        <v>195.2</v>
       </c>
       <c r="H64" t="n">
-        <v>72.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="I64" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-288.18</v>
+        <v>167.01</v>
       </c>
       <c r="K64" t="n">
-        <v>-113.2</v>
+        <v>131.01</v>
       </c>
       <c r="L64" t="n">
-        <v>309.62</v>
+        <v>212.26</v>
       </c>
     </row>
     <row r="65">
@@ -2767,28 +2767,28 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.21</v>
+        <v>5.28</v>
       </c>
       <c r="F65" t="n">
-        <v>14.14</v>
+        <v>13.08</v>
       </c>
       <c r="G65" t="n">
-        <v>187.7</v>
+        <v>202.1</v>
       </c>
       <c r="H65" t="n">
-        <v>87.3</v>
+        <v>39.8</v>
       </c>
       <c r="I65" t="n">
         <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>-214.44</v>
+        <v>-173.4</v>
       </c>
       <c r="K65" t="n">
-        <v>33.89</v>
+        <v>-77.34999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>217.1</v>
+        <v>189.87</v>
       </c>
     </row>
     <row r="66">
@@ -2809,28 +2809,28 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.23</v>
+        <v>5.92</v>
       </c>
       <c r="F66" t="n">
         <v>14.14</v>
       </c>
       <c r="G66" t="n">
-        <v>185.8</v>
+        <v>188.4</v>
       </c>
       <c r="H66" t="n">
-        <v>78</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>194</v>
+        <v>-122.51</v>
       </c>
       <c r="K66" t="n">
-        <v>-67.26000000000001</v>
+        <v>-329.73</v>
       </c>
       <c r="L66" t="n">
-        <v>205.33</v>
+        <v>351.75</v>
       </c>
     </row>
     <row r="67">
@@ -2851,28 +2851,28 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.94</v>
+        <v>6.1</v>
       </c>
       <c r="F67" t="n">
-        <v>12.8</v>
+        <v>14.14</v>
       </c>
       <c r="G67" t="n">
-        <v>193.7</v>
+        <v>185.8</v>
       </c>
       <c r="H67" t="n">
-        <v>57.7</v>
+        <v>87.2</v>
       </c>
       <c r="I67" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>174.51</v>
+        <v>259.97</v>
       </c>
       <c r="K67" t="n">
-        <v>-91.8</v>
+        <v>-115.99</v>
       </c>
       <c r="L67" t="n">
-        <v>197.18</v>
+        <v>284.67</v>
       </c>
     </row>
     <row r="68">
@@ -2893,28 +2893,28 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.6</v>
+        <v>5.42</v>
       </c>
       <c r="F68" t="n">
         <v>14.14</v>
       </c>
       <c r="G68" t="n">
-        <v>175.7</v>
+        <v>187.7</v>
       </c>
       <c r="H68" t="n">
-        <v>57.5</v>
+        <v>60.4</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>280.06</v>
+        <v>-193.65</v>
       </c>
       <c r="K68" t="n">
-        <v>155.84</v>
+        <v>-195.64</v>
       </c>
       <c r="L68" t="n">
-        <v>320.5</v>
+        <v>275.27</v>
       </c>
     </row>
     <row r="69">
@@ -2935,28 +2935,28 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.22</v>
+        <v>5.67</v>
       </c>
       <c r="F69" t="n">
-        <v>12.4</v>
+        <v>11.54</v>
       </c>
       <c r="G69" t="n">
-        <v>176.6</v>
+        <v>194.2</v>
       </c>
       <c r="H69" t="n">
-        <v>65.59999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I69" t="n">
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-189.2</v>
+        <v>-305.7</v>
       </c>
       <c r="K69" t="n">
-        <v>-167.64</v>
+        <v>28.21</v>
       </c>
       <c r="L69" t="n">
-        <v>252.78</v>
+        <v>307</v>
       </c>
     </row>
     <row r="70">
@@ -2977,28 +2977,28 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.48</v>
+        <v>5.98</v>
       </c>
       <c r="F70" t="n">
         <v>14.14</v>
       </c>
       <c r="G70" t="n">
-        <v>188.9</v>
+        <v>183.1</v>
       </c>
       <c r="H70" t="n">
-        <v>6.7</v>
+        <v>35.3</v>
       </c>
       <c r="I70" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-95.94</v>
+        <v>-174.83</v>
       </c>
       <c r="K70" t="n">
-        <v>-288.92</v>
+        <v>-33.51</v>
       </c>
       <c r="L70" t="n">
-        <v>304.43</v>
+        <v>178.01</v>
       </c>
     </row>
     <row r="71">
@@ -3019,28 +3019,28 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.36</v>
+        <v>5.29</v>
       </c>
       <c r="F71" t="n">
-        <v>13.42</v>
+        <v>13.64</v>
       </c>
       <c r="G71" t="n">
-        <v>186.7</v>
+        <v>187.9</v>
       </c>
       <c r="H71" t="n">
-        <v>58.3</v>
+        <v>65</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-348.54</v>
+        <v>331.8</v>
       </c>
       <c r="K71" t="n">
-        <v>-293.61</v>
+        <v>369.65</v>
       </c>
       <c r="L71" t="n">
-        <v>455.72</v>
+        <v>496.72</v>
       </c>
     </row>
     <row r="72">
@@ -3061,28 +3061,28 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>5.31</v>
+        <v>4.67</v>
       </c>
       <c r="F72" t="n">
-        <v>13.3</v>
+        <v>11.7</v>
       </c>
       <c r="G72" t="n">
-        <v>185.8</v>
+        <v>184.8</v>
       </c>
       <c r="H72" t="n">
-        <v>65.7</v>
+        <v>60.8</v>
       </c>
       <c r="I72" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>101.82</v>
+        <v>-383.18</v>
       </c>
       <c r="K72" t="n">
-        <v>264.83</v>
+        <v>12.17</v>
       </c>
       <c r="L72" t="n">
-        <v>283.73</v>
+        <v>383.37</v>
       </c>
     </row>
     <row r="73">
@@ -3103,28 +3103,28 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>5.49</v>
+        <v>5.21</v>
       </c>
       <c r="F73" t="n">
-        <v>12.73</v>
+        <v>12.55</v>
       </c>
       <c r="G73" t="n">
-        <v>182.4</v>
+        <v>183</v>
       </c>
       <c r="H73" t="n">
-        <v>33.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-353.97</v>
+        <v>260.85</v>
       </c>
       <c r="K73" t="n">
-        <v>-248.31</v>
+        <v>449.29</v>
       </c>
       <c r="L73" t="n">
-        <v>432.38</v>
+        <v>519.52</v>
       </c>
     </row>
     <row r="74">
@@ -3145,28 +3145,28 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.81</v>
+        <v>6.8</v>
       </c>
       <c r="F74" t="n">
-        <v>12.07</v>
+        <v>14.14</v>
       </c>
       <c r="G74" t="n">
-        <v>184.9</v>
+        <v>182.8</v>
       </c>
       <c r="H74" t="n">
-        <v>55.7</v>
+        <v>79.5</v>
       </c>
       <c r="I74" t="n">
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>4.61</v>
+        <v>119.12</v>
       </c>
       <c r="K74" t="n">
-        <v>-116.12</v>
+        <v>-103.09</v>
       </c>
       <c r="L74" t="n">
-        <v>116.21</v>
+        <v>157.54</v>
       </c>
     </row>
     <row r="75">
@@ -3187,28 +3187,28 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.39</v>
+        <v>5.73</v>
       </c>
       <c r="F75" t="n">
-        <v>11.11</v>
+        <v>14.14</v>
       </c>
       <c r="G75" t="n">
-        <v>182.4</v>
+        <v>185.2</v>
       </c>
       <c r="H75" t="n">
-        <v>49</v>
+        <v>31.3</v>
       </c>
       <c r="I75" t="n">
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>131.91</v>
+        <v>51.12</v>
       </c>
       <c r="K75" t="n">
-        <v>-56.65</v>
+        <v>-146.74</v>
       </c>
       <c r="L75" t="n">
-        <v>143.56</v>
+        <v>155.39</v>
       </c>
     </row>
     <row r="76">
@@ -3229,28 +3229,28 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.96</v>
+        <v>5.55</v>
       </c>
       <c r="F76" t="n">
-        <v>12.63</v>
+        <v>12.52</v>
       </c>
       <c r="G76" t="n">
-        <v>198.4</v>
+        <v>186.2</v>
       </c>
       <c r="H76" t="n">
-        <v>57.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J76" t="n">
-        <v>-49.3</v>
+        <v>-96.63</v>
       </c>
       <c r="K76" t="n">
-        <v>-91.44</v>
+        <v>-93.06999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>103.88</v>
+        <v>134.16</v>
       </c>
     </row>
     <row r="77">
@@ -3271,28 +3271,28 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.29</v>
+        <v>5.68</v>
       </c>
       <c r="F77" t="n">
-        <v>14.14</v>
+        <v>12.74</v>
       </c>
       <c r="G77" t="n">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H77" t="n">
-        <v>79.90000000000001</v>
+        <v>38.3</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>29.17</v>
+        <v>-57.39</v>
       </c>
       <c r="K77" t="n">
-        <v>-171.22</v>
+        <v>100.24</v>
       </c>
       <c r="L77" t="n">
-        <v>173.69</v>
+        <v>115.51</v>
       </c>
     </row>
     <row r="78">
@@ -3313,28 +3313,28 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.25</v>
+        <v>5.43</v>
       </c>
       <c r="F78" t="n">
-        <v>12.44</v>
+        <v>13.27</v>
       </c>
       <c r="G78" t="n">
-        <v>200.8</v>
+        <v>180.3</v>
       </c>
       <c r="H78" t="n">
-        <v>56.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-84.81999999999999</v>
+        <v>-109.76</v>
       </c>
       <c r="K78" t="n">
-        <v>-127.76</v>
+        <v>-71.23999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>153.36</v>
+        <v>130.85</v>
       </c>
     </row>
     <row r="79">
@@ -3355,28 +3355,28 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>6.06</v>
+        <v>6.23</v>
       </c>
       <c r="F79" t="n">
         <v>14.14</v>
       </c>
       <c r="G79" t="n">
-        <v>185</v>
+        <v>186.3</v>
       </c>
       <c r="H79" t="n">
-        <v>37.1</v>
+        <v>34.6</v>
       </c>
       <c r="I79" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>90.28</v>
+        <v>-203.71</v>
       </c>
       <c r="K79" t="n">
-        <v>-185.27</v>
+        <v>-81.48999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>206.09</v>
+        <v>219.41</v>
       </c>
     </row>
     <row r="80">
@@ -3397,28 +3397,28 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.74</v>
+        <v>6.08</v>
       </c>
       <c r="F80" t="n">
-        <v>14.14</v>
+        <v>14.03</v>
       </c>
       <c r="G80" t="n">
-        <v>188.8</v>
+        <v>196.6</v>
       </c>
       <c r="H80" t="n">
-        <v>1.5</v>
+        <v>70.7</v>
       </c>
       <c r="I80" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>147.16</v>
+        <v>-44.43</v>
       </c>
       <c r="K80" t="n">
-        <v>200.85</v>
+        <v>216.29</v>
       </c>
       <c r="L80" t="n">
-        <v>248.99</v>
+        <v>220.81</v>
       </c>
     </row>
     <row r="81">
@@ -3439,28 +3439,28 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>6.17</v>
+        <v>6.37</v>
       </c>
       <c r="F81" t="n">
         <v>14.14</v>
       </c>
       <c r="G81" t="n">
-        <v>198.6</v>
+        <v>185.7</v>
       </c>
       <c r="H81" t="n">
-        <v>68.3</v>
+        <v>61.7</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>33.81</v>
+        <v>82.56</v>
       </c>
       <c r="K81" t="n">
-        <v>-245.75</v>
+        <v>-306.52</v>
       </c>
       <c r="L81" t="n">
-        <v>248.06</v>
+        <v>317.45</v>
       </c>
     </row>
     <row r="82">
@@ -3481,28 +3481,28 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.64</v>
+        <v>5.97</v>
       </c>
       <c r="F82" t="n">
         <v>14.14</v>
       </c>
       <c r="G82" t="n">
-        <v>190.6</v>
+        <v>189.6</v>
       </c>
       <c r="H82" t="n">
-        <v>64.59999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>252.28</v>
+        <v>193.97</v>
       </c>
       <c r="K82" t="n">
-        <v>-83.27</v>
+        <v>138.75</v>
       </c>
       <c r="L82" t="n">
-        <v>265.67</v>
+        <v>238.49</v>
       </c>
     </row>
     <row r="83">
@@ -3526,25 +3526,25 @@
         <v>5.83</v>
       </c>
       <c r="F83" t="n">
-        <v>14.14</v>
+        <v>13.15</v>
       </c>
       <c r="G83" t="n">
-        <v>190.8</v>
+        <v>181.8</v>
       </c>
       <c r="H83" t="n">
-        <v>67.59999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-320.71</v>
+        <v>161.3</v>
       </c>
       <c r="K83" t="n">
-        <v>13.02</v>
+        <v>-330.29</v>
       </c>
       <c r="L83" t="n">
-        <v>320.97</v>
+        <v>367.57</v>
       </c>
     </row>
     <row r="84">
@@ -3565,28 +3565,28 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>6.36</v>
+        <v>6.56</v>
       </c>
       <c r="F84" t="n">
         <v>14.14</v>
       </c>
       <c r="G84" t="n">
-        <v>191.8</v>
+        <v>193.1</v>
       </c>
       <c r="H84" t="n">
-        <v>67.2</v>
+        <v>45.3</v>
       </c>
       <c r="I84" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>359.52</v>
+        <v>226.24</v>
       </c>
       <c r="K84" t="n">
-        <v>-167.75</v>
+        <v>-277.74</v>
       </c>
       <c r="L84" t="n">
-        <v>396.73</v>
+        <v>358.23</v>
       </c>
     </row>
     <row r="85">
@@ -3607,28 +3607,28 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.91</v>
+        <v>5.25</v>
       </c>
       <c r="F85" t="n">
-        <v>14.14</v>
+        <v>12.78</v>
       </c>
       <c r="G85" t="n">
-        <v>191.7</v>
+        <v>189.4</v>
       </c>
       <c r="H85" t="n">
-        <v>52.7</v>
+        <v>69</v>
       </c>
       <c r="I85" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>83.95999999999999</v>
+        <v>251.77</v>
       </c>
       <c r="K85" t="n">
-        <v>-406.47</v>
+        <v>239.95</v>
       </c>
       <c r="L85" t="n">
-        <v>415.05</v>
+        <v>347.8</v>
       </c>
     </row>
     <row r="86">
@@ -3649,28 +3649,28 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>5.57</v>
+        <v>5.81</v>
       </c>
       <c r="F86" t="n">
         <v>14.14</v>
       </c>
       <c r="G86" t="n">
-        <v>188.2</v>
+        <v>181.8</v>
       </c>
       <c r="H86" t="n">
-        <v>66.90000000000001</v>
+        <v>54.1</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>116.09</v>
+        <v>-486.2</v>
       </c>
       <c r="K86" t="n">
-        <v>255.72</v>
+        <v>272.39</v>
       </c>
       <c r="L86" t="n">
-        <v>280.84</v>
+        <v>557.3</v>
       </c>
     </row>
     <row r="87">
@@ -3691,28 +3691,28 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.68</v>
+        <v>5.98</v>
       </c>
       <c r="F87" t="n">
         <v>14.14</v>
       </c>
       <c r="G87" t="n">
-        <v>189.6</v>
+        <v>179.9</v>
       </c>
       <c r="H87" t="n">
-        <v>50.1</v>
+        <v>59</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>-400.92</v>
+        <v>-92.52</v>
       </c>
       <c r="K87" t="n">
-        <v>-267.12</v>
+        <v>-447.51</v>
       </c>
       <c r="L87" t="n">
-        <v>481.76</v>
+        <v>456.97</v>
       </c>
     </row>
     <row r="88">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.31</v>
+        <v>6.5</v>
       </c>
       <c r="F88" t="n">
         <v>14.14</v>
       </c>
       <c r="G88" t="n">
-        <v>179.6</v>
+        <v>172.5</v>
       </c>
       <c r="H88" t="n">
-        <v>62.2</v>
+        <v>50.1</v>
       </c>
       <c r="I88" t="n">
         <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>-411.28</v>
+        <v>318.91</v>
       </c>
       <c r="K88" t="n">
-        <v>90.69</v>
+        <v>-342.36</v>
       </c>
       <c r="L88" t="n">
-        <v>421.16</v>
+        <v>467.89</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-01.xlsx
+++ b/output/2024-04-01.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-24.82</v>
+        <v>-30.91</v>
       </c>
       <c r="K14" t="n">
-        <v>-59.45</v>
+        <v>-74.05</v>
       </c>
       <c r="L14" t="n">
-        <v>64.42</v>
+        <v>80.25</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-30.26</v>
+        <v>-38.36</v>
       </c>
       <c r="K15" t="n">
-        <v>53.17</v>
+        <v>67.38</v>
       </c>
       <c r="L15" t="n">
-        <v>61.18</v>
+        <v>77.53</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-77</v>
+        <v>-87.20999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-58.2</v>
+        <v>-65.92</v>
       </c>
       <c r="L16" t="n">
-        <v>96.52</v>
+        <v>109.32</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>41.64</v>
+        <v>48.05</v>
       </c>
       <c r="K17" t="n">
-        <v>99.48999999999999</v>
+        <v>114.8</v>
       </c>
       <c r="L17" t="n">
-        <v>107.85</v>
+        <v>124.45</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>16.86</v>
+        <v>21.65</v>
       </c>
       <c r="K18" t="n">
-        <v>34.91</v>
+        <v>44.83</v>
       </c>
       <c r="L18" t="n">
-        <v>38.77</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>100.79</v>
+        <v>121.95</v>
       </c>
       <c r="K19" t="n">
-        <v>-66.36</v>
+        <v>-80.29000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>120.68</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>141.51</v>
+        <v>174.51</v>
       </c>
       <c r="K20" t="n">
-        <v>-25.59</v>
+        <v>-31.55</v>
       </c>
       <c r="L20" t="n">
-        <v>143.81</v>
+        <v>177.34</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-136.74</v>
+        <v>-165.76</v>
       </c>
       <c r="K21" t="n">
-        <v>-54.85</v>
+        <v>-66.48999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>147.33</v>
+        <v>178.6</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-101.54</v>
+        <v>-137.4</v>
       </c>
       <c r="K22" t="n">
-        <v>-67.16</v>
+        <v>-90.88</v>
       </c>
       <c r="L22" t="n">
-        <v>121.75</v>
+        <v>164.73</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>135.51</v>
+        <v>198.34</v>
       </c>
       <c r="K23" t="n">
-        <v>-47.55</v>
+        <v>-69.59999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>143.61</v>
+        <v>210.2</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>74.58</v>
+        <v>102.01</v>
       </c>
       <c r="K24" t="n">
-        <v>-189.03</v>
+        <v>-258.57</v>
       </c>
       <c r="L24" t="n">
-        <v>203.21</v>
+        <v>277.96</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-174.69</v>
+        <v>-222.76</v>
       </c>
       <c r="K25" t="n">
-        <v>-101.42</v>
+        <v>-129.34</v>
       </c>
       <c r="L25" t="n">
-        <v>201.99</v>
+        <v>257.59</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>277.5</v>
+        <v>348.26</v>
       </c>
       <c r="K26" t="n">
-        <v>-537.2</v>
+        <v>-674.1799999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>604.64</v>
+        <v>758.8099999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-362.23</v>
+        <v>-484.89</v>
       </c>
       <c r="K27" t="n">
-        <v>152.88</v>
+        <v>204.65</v>
       </c>
       <c r="L27" t="n">
-        <v>393.17</v>
+        <v>526.3099999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>374.26</v>
+        <v>489.26</v>
       </c>
       <c r="K28" t="n">
-        <v>205.79</v>
+        <v>269.03</v>
       </c>
       <c r="L28" t="n">
-        <v>427.11</v>
+        <v>558.35</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>60.12</v>
+        <v>67.86</v>
       </c>
       <c r="K29" t="n">
-        <v>-74.01000000000001</v>
+        <v>-83.54000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>95.34999999999999</v>
+        <v>107.63</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>40.7</v>
+        <v>45.2</v>
       </c>
       <c r="K30" t="n">
-        <v>-90.86</v>
+        <v>-100.92</v>
       </c>
       <c r="L30" t="n">
-        <v>99.56</v>
+        <v>110.58</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>1.79</v>
+        <v>2.07</v>
       </c>
       <c r="K31" t="n">
-        <v>-85.89</v>
+        <v>-99.34999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>85.91</v>
+        <v>99.37</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>66.25</v>
+        <v>85.62</v>
       </c>
       <c r="K32" t="n">
-        <v>3.77</v>
+        <v>4.88</v>
       </c>
       <c r="L32" t="n">
-        <v>66.34999999999999</v>
+        <v>85.76000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>37.6</v>
+        <v>45.55</v>
       </c>
       <c r="K33" t="n">
-        <v>82.64</v>
+        <v>100.13</v>
       </c>
       <c r="L33" t="n">
-        <v>90.79000000000001</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-86.54000000000001</v>
+        <v>-104.68</v>
       </c>
       <c r="K34" t="n">
-        <v>-20.39</v>
+        <v>-24.66</v>
       </c>
       <c r="L34" t="n">
-        <v>88.91</v>
+        <v>107.55</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-139.35</v>
+        <v>-180.32</v>
       </c>
       <c r="K35" t="n">
-        <v>13.71</v>
+        <v>17.74</v>
       </c>
       <c r="L35" t="n">
-        <v>140.02</v>
+        <v>181.19</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>224.92</v>
+        <v>265.89</v>
       </c>
       <c r="K36" t="n">
-        <v>-32.57</v>
+        <v>-38.51</v>
       </c>
       <c r="L36" t="n">
-        <v>227.27</v>
+        <v>268.67</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-156.68</v>
+        <v>-183.99</v>
       </c>
       <c r="K37" t="n">
-        <v>-85.89</v>
+        <v>-100.86</v>
       </c>
       <c r="L37" t="n">
-        <v>178.68</v>
+        <v>209.83</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-153.76</v>
+        <v>-223.86</v>
       </c>
       <c r="K38" t="n">
-        <v>91.18000000000001</v>
+        <v>132.75</v>
       </c>
       <c r="L38" t="n">
-        <v>178.76</v>
+        <v>260.26</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-189.94</v>
+        <v>-267.93</v>
       </c>
       <c r="K39" t="n">
-        <v>-94.67</v>
+        <v>-133.54</v>
       </c>
       <c r="L39" t="n">
-        <v>212.22</v>
+        <v>299.36</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>120.46</v>
+        <v>151.92</v>
       </c>
       <c r="K40" t="n">
-        <v>-329.29</v>
+        <v>-415.3</v>
       </c>
       <c r="L40" t="n">
-        <v>350.63</v>
+        <v>442.21</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>241.84</v>
+        <v>323.71</v>
       </c>
       <c r="K41" t="n">
-        <v>256.71</v>
+        <v>343.61</v>
       </c>
       <c r="L41" t="n">
-        <v>352.68</v>
+        <v>472.08</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-155.81</v>
+        <v>-207.33</v>
       </c>
       <c r="K42" t="n">
-        <v>-402.73</v>
+        <v>-535.89</v>
       </c>
       <c r="L42" t="n">
-        <v>431.81</v>
+        <v>574.6</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>218.77</v>
+        <v>323.01</v>
       </c>
       <c r="K43" t="n">
-        <v>-159.88</v>
+        <v>-236.05</v>
       </c>
       <c r="L43" t="n">
-        <v>270.96</v>
+        <v>400.07</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>53.17</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>-27.62</v>
+        <v>-34.14</v>
       </c>
       <c r="L44" t="n">
-        <v>59.92</v>
+        <v>74.05</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>79.44</v>
+        <v>92.05</v>
       </c>
       <c r="K45" t="n">
-        <v>24.47</v>
+        <v>28.36</v>
       </c>
       <c r="L45" t="n">
-        <v>83.12</v>
+        <v>96.31999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>65.34</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>-54.17</v>
+        <v>-61.97</v>
       </c>
       <c r="L46" t="n">
-        <v>84.87</v>
+        <v>97.08</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-59.9</v>
+        <v>-75.93000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>-47.59</v>
+        <v>-60.32</v>
       </c>
       <c r="L47" t="n">
-        <v>76.51000000000001</v>
+        <v>96.98</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>26.7</v>
+        <v>35.13</v>
       </c>
       <c r="K48" t="n">
-        <v>83.65000000000001</v>
+        <v>110.07</v>
       </c>
       <c r="L48" t="n">
-        <v>87.8</v>
+        <v>115.54</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>9.41</v>
+        <v>11.87</v>
       </c>
       <c r="K49" t="n">
-        <v>77.55</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>78.12</v>
+        <v>98.54000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>106</v>
+        <v>138.56</v>
       </c>
       <c r="K50" t="n">
-        <v>96.5</v>
+        <v>126.15</v>
       </c>
       <c r="L50" t="n">
-        <v>143.35</v>
+        <v>187.38</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-37.86</v>
+        <v>-45.4</v>
       </c>
       <c r="K51" t="n">
-        <v>-234.83</v>
+        <v>-281.57</v>
       </c>
       <c r="L51" t="n">
-        <v>237.87</v>
+        <v>285.21</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-49.28</v>
+        <v>-57.03</v>
       </c>
       <c r="K52" t="n">
-        <v>209.19</v>
+        <v>242.07</v>
       </c>
       <c r="L52" t="n">
-        <v>214.92</v>
+        <v>248.69</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>199.97</v>
+        <v>281.22</v>
       </c>
       <c r="K53" t="n">
-        <v>37.17</v>
+        <v>52.27</v>
       </c>
       <c r="L53" t="n">
-        <v>203.39</v>
+        <v>286.04</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>249.82</v>
+        <v>339.63</v>
       </c>
       <c r="K54" t="n">
-        <v>-75.67</v>
+        <v>-102.87</v>
       </c>
       <c r="L54" t="n">
-        <v>261.03</v>
+        <v>354.86</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-222.15</v>
+        <v>-307.21</v>
       </c>
       <c r="K55" t="n">
-        <v>-151.44</v>
+        <v>-209.43</v>
       </c>
       <c r="L55" t="n">
-        <v>268.86</v>
+        <v>371.81</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-200.67</v>
+        <v>-267.94</v>
       </c>
       <c r="K56" t="n">
-        <v>-490.2</v>
+        <v>-654.53</v>
       </c>
       <c r="L56" t="n">
-        <v>529.6799999999999</v>
+        <v>707.25</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>262.51</v>
+        <v>379.07</v>
       </c>
       <c r="K57" t="n">
-        <v>159.56</v>
+        <v>230.41</v>
       </c>
       <c r="L57" t="n">
-        <v>307.2</v>
+        <v>443.6</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-245.52</v>
+        <v>-338.07</v>
       </c>
       <c r="K58" t="n">
-        <v>-366.34</v>
+        <v>-504.43</v>
       </c>
       <c r="L58" t="n">
-        <v>441</v>
+        <v>607.24</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-53.58</v>
+        <v>-61.64</v>
       </c>
       <c r="K59" t="n">
-        <v>60.25</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>80.62</v>
+        <v>92.76000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>26.41</v>
+        <v>33.23</v>
       </c>
       <c r="K60" t="n">
-        <v>-97.8</v>
+        <v>-123.03</v>
       </c>
       <c r="L60" t="n">
-        <v>101.3</v>
+        <v>127.44</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-81.7</v>
+        <v>-94.83</v>
       </c>
       <c r="K61" t="n">
-        <v>-23.54</v>
+        <v>-27.32</v>
       </c>
       <c r="L61" t="n">
-        <v>85.02</v>
+        <v>98.69</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>104.5</v>
+        <v>116.92</v>
       </c>
       <c r="K62" t="n">
-        <v>-83.04000000000001</v>
+        <v>-92.91</v>
       </c>
       <c r="L62" t="n">
-        <v>133.47</v>
+        <v>149.34</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-51.72</v>
+        <v>-64.90000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>75.34</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>91.38</v>
+        <v>114.67</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-71.95999999999999</v>
+        <v>-91.83</v>
       </c>
       <c r="K64" t="n">
-        <v>53.41</v>
+        <v>68.16</v>
       </c>
       <c r="L64" t="n">
-        <v>89.61</v>
+        <v>114.36</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-109.8</v>
+        <v>-135.08</v>
       </c>
       <c r="K65" t="n">
-        <v>-190.61</v>
+        <v>-234.49</v>
       </c>
       <c r="L65" t="n">
-        <v>219.97</v>
+        <v>270.62</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>51.48</v>
+        <v>67.97</v>
       </c>
       <c r="K66" t="n">
-        <v>-170.87</v>
+        <v>-225.63</v>
       </c>
       <c r="L66" t="n">
-        <v>178.46</v>
+        <v>235.64</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>263.37</v>
+        <v>309.95</v>
       </c>
       <c r="K67" t="n">
-        <v>-56.01</v>
+        <v>-65.91</v>
       </c>
       <c r="L67" t="n">
-        <v>269.26</v>
+        <v>316.89</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>68.98999999999999</v>
+        <v>88.36</v>
       </c>
       <c r="K68" t="n">
-        <v>-224.71</v>
+        <v>-287.82</v>
       </c>
       <c r="L68" t="n">
-        <v>235.07</v>
+        <v>301.08</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>-206.1</v>
+        <v>-263.96</v>
       </c>
       <c r="K69" t="n">
-        <v>-310.8</v>
+        <v>-398.04</v>
       </c>
       <c r="L69" t="n">
-        <v>372.93</v>
+        <v>477.6</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>204.59</v>
+        <v>300.71</v>
       </c>
       <c r="K70" t="n">
-        <v>41.29</v>
+        <v>60.69</v>
       </c>
       <c r="L70" t="n">
-        <v>208.72</v>
+        <v>306.77</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-184.79</v>
+        <v>-278.4</v>
       </c>
       <c r="K71" t="n">
-        <v>-197.29</v>
+        <v>-297.24</v>
       </c>
       <c r="L71" t="n">
-        <v>270.32</v>
+        <v>407.26</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>88.03</v>
+        <v>124.64</v>
       </c>
       <c r="K72" t="n">
-        <v>-314.73</v>
+        <v>-445.64</v>
       </c>
       <c r="L72" t="n">
-        <v>326.8</v>
+        <v>462.74</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>295.87</v>
+        <v>429.18</v>
       </c>
       <c r="K73" t="n">
-        <v>145.49</v>
+        <v>211.03</v>
       </c>
       <c r="L73" t="n">
-        <v>329.71</v>
+        <v>478.26</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-50.95</v>
+        <v>-65.61</v>
       </c>
       <c r="K74" t="n">
-        <v>-51.96</v>
+        <v>-66.91</v>
       </c>
       <c r="L74" t="n">
-        <v>72.77</v>
+        <v>93.70999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-64.26000000000001</v>
+        <v>-74.41</v>
       </c>
       <c r="K75" t="n">
-        <v>-63.87</v>
+        <v>-73.95</v>
       </c>
       <c r="L75" t="n">
-        <v>90.59999999999999</v>
+        <v>104.91</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-65.08</v>
+        <v>-74.42</v>
       </c>
       <c r="K76" t="n">
-        <v>-63.54</v>
+        <v>-72.65000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>90.95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-22.28</v>
+        <v>-27.33</v>
       </c>
       <c r="K77" t="n">
-        <v>-127.49</v>
+        <v>-156.4</v>
       </c>
       <c r="L77" t="n">
-        <v>129.43</v>
+        <v>158.77</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-129.41</v>
+        <v>-139.23</v>
       </c>
       <c r="K78" t="n">
-        <v>-88.5</v>
+        <v>-95.22</v>
       </c>
       <c r="L78" t="n">
-        <v>156.77</v>
+        <v>168.68</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>9.73</v>
+        <v>12.46</v>
       </c>
       <c r="K79" t="n">
-        <v>75.90000000000001</v>
+        <v>97.19</v>
       </c>
       <c r="L79" t="n">
-        <v>76.53</v>
+        <v>97.98999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-238.13</v>
+        <v>-281.07</v>
       </c>
       <c r="K80" t="n">
-        <v>90.84999999999999</v>
+        <v>107.23</v>
       </c>
       <c r="L80" t="n">
-        <v>254.88</v>
+        <v>300.83</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-67.41</v>
+        <v>-86.81999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>-172.67</v>
+        <v>-222.39</v>
       </c>
       <c r="L81" t="n">
-        <v>185.36</v>
+        <v>238.73</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-140.23</v>
+        <v>-176.87</v>
       </c>
       <c r="K82" t="n">
-        <v>104.72</v>
+        <v>132.08</v>
       </c>
       <c r="L82" t="n">
-        <v>175.02</v>
+        <v>220.74</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-341.47</v>
+        <v>-452.74</v>
       </c>
       <c r="K83" t="n">
-        <v>-24.25</v>
+        <v>-32.15</v>
       </c>
       <c r="L83" t="n">
-        <v>342.33</v>
+        <v>453.88</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>260.18</v>
+        <v>355.45</v>
       </c>
       <c r="K84" t="n">
-        <v>-35.94</v>
+        <v>-49.1</v>
       </c>
       <c r="L84" t="n">
-        <v>262.65</v>
+        <v>358.83</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>317.32</v>
+        <v>415.74</v>
       </c>
       <c r="K85" t="n">
-        <v>119.41</v>
+        <v>156.45</v>
       </c>
       <c r="L85" t="n">
-        <v>339.04</v>
+        <v>444.2</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-228.41</v>
+        <v>-312.85</v>
       </c>
       <c r="K86" t="n">
-        <v>-448.38</v>
+        <v>-614.12</v>
       </c>
       <c r="L86" t="n">
-        <v>503.2</v>
+        <v>689.21</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>-7.69</v>
+        <v>-11</v>
       </c>
       <c r="K87" t="n">
-        <v>-412.22</v>
+        <v>-589.53</v>
       </c>
       <c r="L87" t="n">
-        <v>412.29</v>
+        <v>589.63</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-373.51</v>
+        <v>-514.42</v>
       </c>
       <c r="K88" t="n">
-        <v>-159.12</v>
+        <v>-219.16</v>
       </c>
       <c r="L88" t="n">
-        <v>405.99</v>
+        <v>559.16</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-01.xlsx
+++ b/output/2024-04-01.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-30.91</v>
+        <v>-47.57</v>
       </c>
       <c r="K14" t="n">
-        <v>-74.05</v>
+        <v>-113.95</v>
       </c>
       <c r="L14" t="n">
-        <v>80.25</v>
+        <v>123.48</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-38.36</v>
+        <v>-58.8</v>
       </c>
       <c r="K15" t="n">
-        <v>67.38</v>
+        <v>103.29</v>
       </c>
       <c r="L15" t="n">
-        <v>77.53</v>
+        <v>118.85</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-87.20999999999999</v>
+        <v>-133.44</v>
       </c>
       <c r="K16" t="n">
-        <v>-65.92</v>
+        <v>-100.87</v>
       </c>
       <c r="L16" t="n">
-        <v>109.32</v>
+        <v>167.27</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>48.05</v>
+        <v>59.9</v>
       </c>
       <c r="K17" t="n">
-        <v>114.8</v>
+        <v>143.13</v>
       </c>
       <c r="L17" t="n">
-        <v>124.45</v>
+        <v>155.16</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>21.65</v>
+        <v>27.37</v>
       </c>
       <c r="K18" t="n">
-        <v>44.83</v>
+        <v>56.67</v>
       </c>
       <c r="L18" t="n">
-        <v>49.78</v>
+        <v>62.94</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>121.95</v>
+        <v>180.72</v>
       </c>
       <c r="K19" t="n">
-        <v>-80.29000000000001</v>
+        <v>-118.99</v>
       </c>
       <c r="L19" t="n">
-        <v>146</v>
+        <v>216.38</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>67.86</v>
+        <v>101.1</v>
       </c>
       <c r="K29" t="n">
-        <v>-83.54000000000001</v>
+        <v>-124.46</v>
       </c>
       <c r="L29" t="n">
-        <v>107.63</v>
+        <v>160.35</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>45.2</v>
+        <v>69.3</v>
       </c>
       <c r="K30" t="n">
-        <v>-100.92</v>
+        <v>-154.71</v>
       </c>
       <c r="L30" t="n">
-        <v>110.58</v>
+        <v>169.52</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>2.07</v>
+        <v>2.97</v>
       </c>
       <c r="K31" t="n">
-        <v>-99.34999999999999</v>
+        <v>-142.96</v>
       </c>
       <c r="L31" t="n">
-        <v>99.37</v>
+        <v>142.99</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>85.62</v>
+        <v>108.91</v>
       </c>
       <c r="K32" t="n">
-        <v>4.88</v>
+        <v>6.2</v>
       </c>
       <c r="L32" t="n">
-        <v>85.76000000000001</v>
+        <v>109.08</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>45.55</v>
+        <v>61.96</v>
       </c>
       <c r="K33" t="n">
-        <v>100.13</v>
+        <v>136.18</v>
       </c>
       <c r="L33" t="n">
-        <v>110</v>
+        <v>149.62</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-104.68</v>
+        <v>-134.39</v>
       </c>
       <c r="K34" t="n">
-        <v>-24.66</v>
+        <v>-31.66</v>
       </c>
       <c r="L34" t="n">
-        <v>107.55</v>
+        <v>138.07</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>65.70999999999999</v>
+        <v>86.31</v>
       </c>
       <c r="K44" t="n">
-        <v>-34.14</v>
+        <v>-44.84</v>
       </c>
       <c r="L44" t="n">
-        <v>74.05</v>
+        <v>97.26000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>92.05</v>
+        <v>142.99</v>
       </c>
       <c r="K45" t="n">
-        <v>28.36</v>
+        <v>44.05</v>
       </c>
       <c r="L45" t="n">
-        <v>96.31999999999999</v>
+        <v>149.62</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>74.73999999999999</v>
+        <v>112.2</v>
       </c>
       <c r="K46" t="n">
-        <v>-61.97</v>
+        <v>-93.03</v>
       </c>
       <c r="L46" t="n">
-        <v>97.08</v>
+        <v>145.75</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-75.93000000000001</v>
+        <v>-106.42</v>
       </c>
       <c r="K47" t="n">
-        <v>-60.32</v>
+        <v>-84.54000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>96.98</v>
+        <v>135.91</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>35.13</v>
+        <v>54.04</v>
       </c>
       <c r="K48" t="n">
-        <v>110.07</v>
+        <v>169.33</v>
       </c>
       <c r="L48" t="n">
-        <v>115.54</v>
+        <v>177.74</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>11.87</v>
+        <v>16.03</v>
       </c>
       <c r="K49" t="n">
-        <v>97.81999999999999</v>
+        <v>132.05</v>
       </c>
       <c r="L49" t="n">
-        <v>98.54000000000001</v>
+        <v>133.02</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-61.64</v>
+        <v>-88.36</v>
       </c>
       <c r="K59" t="n">
-        <v>69.31999999999999</v>
+        <v>99.36</v>
       </c>
       <c r="L59" t="n">
-        <v>92.76000000000001</v>
+        <v>132.96</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>33.23</v>
+        <v>64.61</v>
       </c>
       <c r="K60" t="n">
-        <v>-123.03</v>
+        <v>-239.24</v>
       </c>
       <c r="L60" t="n">
-        <v>127.44</v>
+        <v>247.81</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-94.83</v>
+        <v>-151.75</v>
       </c>
       <c r="K61" t="n">
-        <v>-27.32</v>
+        <v>-43.72</v>
       </c>
       <c r="L61" t="n">
-        <v>98.69</v>
+        <v>157.92</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>116.92</v>
+        <v>155.69</v>
       </c>
       <c r="K62" t="n">
-        <v>-92.91</v>
+        <v>-123.72</v>
       </c>
       <c r="L62" t="n">
-        <v>149.34</v>
+        <v>198.87</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-64.90000000000001</v>
+        <v>-93.54000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>94.54000000000001</v>
+        <v>136.27</v>
       </c>
       <c r="L63" t="n">
-        <v>114.67</v>
+        <v>165.29</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-91.83</v>
+        <v>-132.37</v>
       </c>
       <c r="K64" t="n">
-        <v>68.16</v>
+        <v>98.23999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>114.36</v>
+        <v>164.84</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-65.61</v>
+        <v>-117.08</v>
       </c>
       <c r="K74" t="n">
-        <v>-66.91</v>
+        <v>-119.4</v>
       </c>
       <c r="L74" t="n">
-        <v>93.70999999999999</v>
+        <v>167.22</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-74.41</v>
+        <v>-124.39</v>
       </c>
       <c r="K75" t="n">
-        <v>-73.95</v>
+        <v>-123.63</v>
       </c>
       <c r="L75" t="n">
-        <v>104.91</v>
+        <v>175.38</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-74.42</v>
+        <v>-120.19</v>
       </c>
       <c r="K76" t="n">
-        <v>-72.65000000000001</v>
+        <v>-117.34</v>
       </c>
       <c r="L76" t="n">
-        <v>104</v>
+        <v>167.97</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-27.33</v>
+        <v>-41.21</v>
       </c>
       <c r="K77" t="n">
-        <v>-156.4</v>
+        <v>-235.83</v>
       </c>
       <c r="L77" t="n">
-        <v>158.77</v>
+        <v>239.41</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-139.23</v>
+        <v>-185.69</v>
       </c>
       <c r="K78" t="n">
-        <v>-95.22</v>
+        <v>-126.99</v>
       </c>
       <c r="L78" t="n">
-        <v>168.68</v>
+        <v>224.96</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>12.46</v>
+        <v>17.28</v>
       </c>
       <c r="K79" t="n">
-        <v>97.19</v>
+        <v>134.8</v>
       </c>
       <c r="L79" t="n">
-        <v>97.98999999999999</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="80">
